--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -6,14 +6,15 @@
   </bookViews>
   <sheets>
     <sheet name="Read Me" sheetId="1" r:id="rId1"/>
-    <sheet name="Summary" sheetId="2" r:id="rId2"/>
-    <sheet name="Personas" sheetId="3" r:id="rId3"/>
-    <sheet name="Test Cases" sheetId="4" r:id="rId4"/>
-    <sheet name="Bug Log" sheetId="5" r:id="rId5"/>
+    <sheet name="Module Guide" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="3" r:id="rId3"/>
+    <sheet name="Personas" sheetId="4" r:id="rId4"/>
+    <sheet name="Test Cases" sheetId="5" r:id="rId5"/>
+    <sheet name="Bug Log" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Test Cases'!$A$1:$N$216</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Bug Log'!$A$1:$M$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bug Log'!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -108,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -131,6 +132,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -193,6 +197,44 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="8382000" cy="7439025"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Workflow" descr="The order to test the modules in, from set up to integrations"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="8382000" cy="7439025"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
@@ -223,357 +265,1947 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">The workflow at a glance</t>
+        </is>
+      </c>
+      <c r="B4" s="2"/>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">How to use this workbook</t>
         </is>
       </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
+      <c r="B53" s="2"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B54" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Start a fresh instance with an empty database (docs/install/compose.md). Note the URL.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1">
+    <row r="55">
+      <c r="A55" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B55" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fill the yellow email and password cells on the Personas sheet.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1">
+    <row r="56">
+      <c r="A56" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B56" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Work down the Test Cases sheet in order. Each module builds on the one before it.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1">
+    <row r="57">
+      <c r="A57" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B57" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sign in as the person in "Login as". Check the Pre-condition, follow the Steps, compare with Expected result.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1">
+    <row r="58">
+      <c r="A58" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B58" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pick a Status from the dropdown. For anything other than Pass, write what you saw in "Actual result / notes".</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1">
+    <row r="59">
+      <c r="A59" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B59" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">For each Fail or Error, add a row on Bug Log with a screenshot link, and put its Bug ID on the test case.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1">
+    <row r="60">
+      <c r="A60" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B60" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Read the Summary sheet for the totals. It updates by itself.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Status</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">When to use it</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="B63" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Not tested yet. Every case starts here.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Pass</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
+      <c r="B64" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">What you saw matches Expected result.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Fail</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B65" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The screen works but the result is different from Expected result. Wrong text, wrong number, missing item, a refusal that should not happen.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Error</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B66" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The app broke: an error page, "We could not load", a blank screen, a spinner that never ends, or a crash.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Blocked</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B67" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">You could not run the test because something earlier failed, or a pre-condition cannot be met. Say which in the notes.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">N/A</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B68" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Does not apply to this instance, for example no Slack workspace or no passkey device.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9"/>
-      <c r="B20" s="9"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="9"/>
+      <c r="B69" s="9"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Before you start</t>
         </is>
       </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="B70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Browsers</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B71" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">One browser profile per persona. Two screens help for M13 and M15, where two people act at once.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Email</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B72" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Without SMTP the instance prints every mail to its log. Invitation links are also shown once on Admin, Invitations. For reset links either read the server log or run Mailpit (SMTP on localhost port 1025, inbox at http://localhost:8025).</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Server access</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B73" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A few cases need someone who can read logs, restart the instance or run a pnpm command. They say so in the hint.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">AI</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B74" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">AI is off by default and everything before M20 is tested with it off. M20 needs a provider key with a spending limit.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Integrations</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B75" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 to M26 need outside accounts (Slack, Teams, WhatsApp, Telegram, an identity provider, an MCP client). Mark N/A for any you do not have.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Never</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B76" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Paste an API key, token or password into this workbook. Write where it is kept instead.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="9"/>
+      <c r="B77" s="9"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Known risks found while writing this</t>
         </is>
       </c>
-      <c r="B29" s="2"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="B78" s="2"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Publishing</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="B79" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Code review suggests gates 2 and 5 have no field in the UI. M11-05 tests it. If they cannot turn green, publish with the override in M11-07.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
+      <c r="B80" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sessions cannot be created from the UI. The only weekly session is the one the starter template makes in M02. Quarterly reviews may not be reachable at all (M18-06).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admins</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
+      <c r="B81" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Only the first account has full access, and no screen grants it to anyone else.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Chat test</t>
         </is>
       </c>
-      <c r="B33" s="1" t="inlineStr">
+      <c r="B82" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Send me a test" on Admin, Channels sends an email, not a chat message.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2FA</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
+      <c r="B83" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">There is no button to turn one-time codes off. Use the throwaway persona Amara.</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9"/>
-      <c r="B35" s="9"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs. 189 test cases across 26 modules.</t>
-        </is>
-      </c>
-      <c r="B36" s="10"/>
+    <row r="84">
+      <c r="A84" s="9"/>
+      <c r="B84" s="9"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 189 test cases across 26 modules.</t>
+        </is>
+      </c>
+      <c r="B85" s="10"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A84:B84"/>
+    <mergeCell ref="A85:B85"/>
+  </mergeCells>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What each module is for and how it flows, in the order to test it. The Test Cases sheet has the detailed steps; this sheet is the map.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Module</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What it proves</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Screens</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Who signs in</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Workflow</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs first</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leaves ready for later</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Setup needed</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Time (min)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M01 Install and first account</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set up</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turn an empty server into an instance with one owner</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/setup, /setup/account, /sign-up</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the instance and get sent to setup
+2. Name the instance Northwind Labs
+3. Create the owner account
+4. Check that registration is now closed</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing. Start here</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An owner account. Everybody after this joins by invitation</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A fresh instance with an empty database</t>
+        </is>
+      </c>
+      <c r="J5" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" ht="71" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M02 Welcome wizard</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set up</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Give the new workspace its name, clock, rhythm and starting content</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/welcome</t>
+        </is>
+      </c>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Name the workspace and pick its timezone
+2. Choose the check-in rhythm
+3. Skip the invite
+4. Apply the OKR starter cycle template
+5. Land on the work map</t>
+        </is>
+      </c>
+      <c r="G6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M01</t>
+        </is>
+      </c>
+      <c r="H6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A current cycle, one objective with 3 key results, a KPI, a KPI tree and the weekly session M15 needs</t>
+        </is>
+      </c>
+      <c r="I6" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J6" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="71" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M03 Workspace settings</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Set up</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check that workspace settings save, reload and reset</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin: General, Branding, Rhythm and thresholds</t>
+        </is>
+      </c>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Change timezone and language
+2. Check the mail warning
+3. Set a brand colour
+4. Set the check-in rhythm
+5. Rename a concept, then set it back</t>
+        </is>
+      </c>
+      <c r="G7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M02</t>
+        </is>
+      </c>
+      <c r="H7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The rhythm every later reminder and due date follows</t>
+        </is>
+      </c>
+      <c r="I7" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J7" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" ht="97" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M04 Invitations and building the team</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Build the team</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bring the seven Northwind people into the workspace</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Invitations; /join/&lt;token&gt;; /sign-up</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then each persona</t>
+        </is>
+      </c>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Admin creates a personal invitation for Priya
+2. Priya opens the link and signs up
+3. A wrong address is refused
+4. Admin shares one link for the rest
+5. Each persona signs up in their own browser profile
+6. Revoked and made-up links are refused</t>
+        </is>
+      </c>
+      <c r="G8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M02</t>
+        </is>
+      </c>
+      <c r="H8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eight members. Every module after this signs in as one of them</t>
+        </is>
+      </c>
+      <c r="I8" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One inbox with plus-addresses, one browser profile per persona</t>
+        </is>
+      </c>
+      <c r="J8" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" ht="84" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M05 Sign-in and account security</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Build the team</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prove sign-in, password reset and the second factor protect an account</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/sign-in, /forgot-password, /reset-password, /backup-code, Account, Security</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jonas, Mei, Amara, Sara, Priya</t>
+        </is>
+      </c>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Refuse a wrong password
+2. Reset a forgotten password by mail
+3. Turn on one-time codes for Amara
+4. Sign in with a code and with a backup code
+5. Add a passkey
+6. Revoke another device</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M04</t>
+        </is>
+      </c>
+      <c r="H9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Confidence that accounts are safe before real data goes in</t>
+        </is>
+      </c>
+      <c r="I9" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mailpit or SMTP for the reset mail. An authenticator app</t>
+        </is>
+      </c>
+      <c r="J9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" ht="71" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M06 People and org chart</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Build the team</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Give everyone a title and a manager so the org chart is real</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">People, People / &lt;person&gt;</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Mei, Jonas, Tomas</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Admin sets title and manager for each persona
+2. Check the org chart
+3. A loop in the chain is refused
+4. Members edit only their own profile
+5. Suspend and restore Tomas</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M04</t>
+        </is>
+      </c>
+      <c r="H10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reporting lines, used by the org chart and by who reviews whom</t>
+        </is>
+      </c>
+      <c r="I10" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J10" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" ht="71" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M07 Spaces</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2. Build the team</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Create the team homes that own goals, boards and sessions</t>
+        </is>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spaces, Spaces / &lt;space&gt;</t>
+        </is>
+      </c>
+      <c r="E11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Priya, Amara, Jonas</t>
+        </is>
+      </c>
+      <c r="F11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Admin creates Product, Sales and Customer Success
+2. Priya adds members with roles
+3. A member joins and leaves
+4. A non-manager cannot manage
+5. Change settings, archive a spare space</t>
+        </is>
+      </c>
+      <c r="G11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M06</t>
+        </is>
+      </c>
+      <c r="H11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Spaces that goals, the board and the weekly session belong to</t>
+        </is>
+      </c>
+      <c r="I11" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J11" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" ht="84" customHeight="1">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M08 Cycle: prepare, diagnose, direction</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Plan the cycle</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Walk the first three phases so drafting has something to stand on</t>
+        </is>
+      </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle (phases 1 to 3), Cycles card</t>
+        </is>
+      </c>
+      <c r="E12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Priya</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Read the eight-phase rail
+2. Create the next cycle and set the publication deadline
+3. Phase 1: sponsor, facilitator, input pack
+4. Phase 2: rank three strategic issues
+5. Phase 3: choose a priority</t>
+        </is>
+      </c>
+      <c r="G12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M07</t>
+        </is>
+      </c>
+      <c r="H12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A priority for objectives to contribute to, and the deadline gate 6 checks</t>
+        </is>
+      </c>
+      <c r="I12" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J12" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" ht="84" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M09 Drafting OKRs and quality checks</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Plan the cycle</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Draft objectives and key results while the quality checks fire live</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cycle, phase 4; /method/&lt;rule&gt;</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Daniel, Tomas</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Draft Sara's objective with champion and reviewer
+2. Type weak wording and watch OBJ-1 and OBJ-2 fire
+3. Open a rule card and the method page
+4. Add key results, weak then measurable
+5. Record a current value
+6. Daniel and Tomas draft their own</t>
+        </is>
+      </c>
+      <c r="G13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M08</t>
+        </is>
+      </c>
+      <c r="H13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A draft set of objectives for three teams</t>
+        </is>
+      </c>
+      <c r="I13" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI off</t>
+        </is>
+      </c>
+      <c r="J13" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" ht="97" customHeight="1">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M10 Goal page and documents</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Plan the cycle</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work on one goal: values, confidence, comments, documents and files</t>
+        </is>
+      </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goals, Goals / &lt;goal&gt;, Documents / &lt;doc&gt;</t>
+        </is>
+      </c>
+      <c r="E14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Priya, Mei, Jonas</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the goal and read its header
+2. Update values and confidence
+3. Comment and watch
+4. Start a private document, then publish two versions
+5. Attach and detach a file
+6. Filter the explorer</t>
+        </is>
+      </c>
+      <c r="G14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M09</t>
+        </is>
+      </c>
+      <c r="H14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal with history, discussion and a document</t>
+        </is>
+      </c>
+      <c r="I14" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A small PDF to attach</t>
+        </is>
+      </c>
+      <c r="J14" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" ht="84" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11 Alignment and publishing</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3. Plan the cycle</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Align the set and publish it through the six gates</t>
+        </is>
+      </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goals, Alignment studio; Cycle, phase 5</t>
+        </is>
+      </c>
+      <c r="E15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya, Admin</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Look at the cascade
+2. Link a team goal to the company goal
+3. Record and confirm a dependency
+4. Read each gate and follow its fix
+5. Publish, or override with a reason
+6. Check a member cannot publish</t>
+        </is>
+      </c>
+      <c r="G15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M10</t>
+        </is>
+      </c>
+      <c r="H15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A published set. The cycle moves to phase 6 and check-ins start</t>
+        </is>
+      </c>
+      <c r="I15" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J15" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" ht="84" customHeight="1">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12 KPIs and recovery</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Run the cycle</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Track KPIs continuously and recover one that falls out of its corridor</t>
+        </is>
+      </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">KPIs grid, KPIs / &lt;kpi&gt;, Trees, Recovery board</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya, Admin</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Add a KPI
+2. Enter values and watch green, amber and red
+3. Build a formula and a tree
+4. Let a KPI drop to red
+5. Launch a recovery objective
+6. Move a threshold and see colours change</t>
+        </is>
+      </c>
+      <c r="G16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A recovering KPI with its own objective</t>
+        </is>
+      </c>
+      <c r="I16" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J16" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" ht="84" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Run the cycle</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plan the work behind key results and move it on the board</t>
+        </is>
+      </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Initiatives, Initiatives / &lt;one&gt;, Board, Tasks / &lt;task&gt;</t>
+        </is>
+      </c>
+      <c r="E17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mei, Sara, Priya, Admin</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Add an initiative and link it to a key result
+2. Add tasks on the board
+3. Drag cards between columns
+4. Watch a second browser update live
+5. Break a task into a checklist
+6. See the warning when done work moves nothing</t>
+        </is>
+      </c>
+      <c r="G17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work linked to key results, which the weekly session reads</t>
+        </is>
+      </c>
+      <c r="I17" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two browsers side by side</t>
+        </is>
+      </c>
+      <c r="J17" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="97" customHeight="1">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Run the cycle</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report progress every week and have the reviewer acknowledge it</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check in, Review, Inbox</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Priya, Mei, Jonas</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Sara opens what is due
+2. A check-in without a narrative is refused
+3. Sara posts one
+4. Others cannot post or acknowledge
+5. Priya acknowledges from Review
+6. Inbox: read, snooze, mute
+7. A stale goal turns Outdated</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check-ins and confidence the weekly session starts from</t>
+        </is>
+      </c>
+      <c r="I18" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check-in frequency set to daily so a goal is due today</t>
+        </is>
+      </c>
+      <c r="J18" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="84" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15 Weekly session</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Run the cycle</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run the four-step weekly session the product facilitates</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sessions, Session / &lt;id&gt;</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin (facilitator), Priya, Sara, Mei</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Start the template's weekly session
+2. Confidence round: vote, reveal, confirm
+3. A low key result needs a blocker
+4. Resolve and reassign the blocker
+5. Set two or three commitments
+6. Digest and close</t>
+        </is>
+      </c>
+      <c r="G19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14</t>
+        </is>
+      </c>
+      <c r="H19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A finished session with blockers and commitments on record</t>
+        </is>
+      </c>
+      <c r="I19" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya and Sara are members of the session's space</t>
+        </is>
+      </c>
+      <c r="J19" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="84" customHeight="1">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16 Agents and nudges</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4. Run the cycle</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the two agents nudge, propose and stay quiet when they should</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin: Agents and runs, Nudge volume; Account, Where to reach you</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Sara</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Confirm both agents propose by default
+2. Run the Champion and the Coach now
+3. Apply and dismiss proposals
+4. Try sandbox and direct write
+5. A nudge reaches Sara once a day only
+6. Quiet hours and a switched-off rule hold nudges</t>
+        </is>
+      </c>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14</t>
+        </is>
+      </c>
+      <c r="H20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof the agents are safe with AI off</t>
+        </is>
+      </c>
+      <c r="I20" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J20" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" ht="84" customHeight="1">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M17 Work map, search and activity</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Close and check</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the overview screens, search and basic usability</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work map, Search, Activity, copilot panel</t>
+        </is>
+      </c>
+      <c r="E21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya, Jonas, Admin, Sara</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Read the work map strip and table
+2. Search finds only what you may open
+3. Page through Activity
+4. Open the copilot with AI off
+5. Check in with the keyboard only
+6. Use the app at phone width</t>
+        </is>
+      </c>
+      <c r="G21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15</t>
+        </is>
+      </c>
+      <c r="H21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A read of the whole workspace as a member sees it</t>
+        </is>
+      </c>
+      <c r="I21" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A phone, or a 375px browser window</t>
+        </is>
+      </c>
+      <c r="J21" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" ht="84" customHeight="1">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Close and check</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Close goals and the quarter, and record the result</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Goals / &lt;goal&gt;, Cycle phase 7, Scorecard, Cycles card</t>
+        </is>
+      </c>
+      <c r="E22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Admin</t>
+        </is>
+      </c>
+      <c r="F22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Closing a goal needs a retrospective
+2. Close and reopen a goal
+3. Score every key result in phase 7
+4. Record the result on the scorecard
+5. Archive the old cycle
+6. Look for the quarterly review</t>
+        </is>
+      </c>
+      <c r="G22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15</t>
+        </is>
+      </c>
+      <c r="H22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A closed cycle and a scorecard row</t>
+        </is>
+      </c>
+      <c r="I22" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J22" s="1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" ht="71" customHeight="1">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M19 Access and permissions</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5. Close and check</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check nobody sees or does more than their access allows</t>
+        </is>
+      </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin screens, any goal URL, People / &lt;person&gt;</t>
+        </is>
+      </c>
+      <c r="E23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jonas, Amara, Admin</t>
+        </is>
+      </c>
+      <c r="F23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. A member opening Admin gets Not Found
+2. Signed-out visitors go to sign-in
+3. A hidden goal reads as not found
+4. Convert a member to a guest
+5. Erase a spare member</t>
+        </is>
+      </c>
+      <c r="G23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Access control checked from the outside</t>
+        </is>
+      </c>
+      <c r="I23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One spare invited account for erasing</t>
+        </is>
+      </c>
+      <c r="J23" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" ht="84" customHeight="1">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20 AI provider and copilot</t>
+        </is>
+      </c>
+      <c r="B24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turn AI on and check it drafts while a person decides</t>
+        </is>
+      </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, AI; drafting surface; copilot</t>
+        </is>
+      </c>
+      <c r="E24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Sara, Jonas</t>
+        </is>
+      </c>
+      <c r="F24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Store a provider key
+2. A bad key is marked invalid
+3. AI buttons appear
+4. A draft is proposed, not saved
+5. The copilot answers with sources
+6. Remove the key and the rules still fire</t>
+        </is>
+      </c>
+      <c r="G24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI checked on and off</t>
+        </is>
+      </c>
+      <c r="I24" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A provider key with a spending limit</t>
+        </is>
+      </c>
+      <c r="J24" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" ht="84" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21 Chat channels and email</t>
+        </is>
+      </c>
+      <c r="B25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Deliver mail and chat messages to real inboxes and apps</t>
+        </is>
+      </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Channels; Account, Where to reach you</t>
+        </is>
+      </c>
+      <c r="E25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Sara, Jonas</t>
+        </is>
+      </c>
+      <c r="F25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Real mail arrives
+2. Connect Slack and link Sara
+3. A nudge arrives in Slack
+4. Chat commands work
+5. Repeat for Teams, WhatsApp, Telegram
+6. Disconnect a channel</t>
+        </is>
+      </c>
+      <c r="G25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16</t>
+        </is>
+      </c>
+      <c r="H25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof that reminders leave the product</t>
+        </is>
+      </c>
+      <c r="I25" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SMTP or Mailpit. A public URL and an app per chat provider</t>
+        </is>
+      </c>
+      <c r="J25" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" ht="84" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
+        </is>
+      </c>
+      <c r="B26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sign in through a company identity provider and sync the directory</t>
+        </is>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin: Single sign-on, Directory sync, General</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Jonas</t>
+        </is>
+      </c>
+      <c r="F26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Add an OIDC provider and restart
+2. Sign in with it
+3. Enforce SSO for a domain
+4. Try SAML
+5. Push a user through SCIM
+6. Require a second factor for everyone</t>
+        </is>
+      </c>
+      <c r="G26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M04</t>
+        </is>
+      </c>
+      <c r="H26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Company sign-in checked</t>
+        </is>
+      </c>
+      <c r="I26" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An identity provider account. Server access to restart</t>
+        </is>
+      </c>
+      <c r="J26" s="1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" ht="84" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M23 Import and export</t>
+        </is>
+      </c>
+      <c r="B27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bring data in from spreadsheets and FlowyTeam, and take it out</t>
+        </is>
+      </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Import</t>
+        </is>
+      </c>
+      <c r="E27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="F27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Import goals from CSV
+2. Import the same file again: nothing new
+3. A bad row is reported
+4. Import KPI records from xlsx
+5. Export the workspace
+6. FlowyTeam import from the command line</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M07</t>
+        </is>
+      </c>
+      <c r="H27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Import and export checked</t>
+        </is>
+      </c>
+      <c r="I27" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample CSV and xlsx files. A FlowyTeam MySQL copy for the last case</t>
+        </is>
+      </c>
+      <c r="J27" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" ht="71" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
+        </is>
+      </c>
+      <c r="B28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reach the product from scripts, the command line and outside AI agents</t>
+        </is>
+      </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Account: API tokens, Device, Connected agents; /oauth/authorize</t>
+        </is>
+      </c>
+      <c r="E28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="F28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Create and revoke a token
+2. Call the API with it
+3. Log the command line in by device approval
+4. Connect an MCP agent and ask it for goals
+5. Revoke the agent</t>
+        </is>
+      </c>
+      <c r="G28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The outside surfaces checked</t>
+        </is>
+      </c>
+      <c r="I28" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The okr command line. An MCP client. A public HTTPS URL</t>
+        </is>
+      </c>
+      <c r="J28" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" ht="58" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25 Audit trail and workspace state</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the audit trail recorded the sensitive actions from earlier modules</t>
+        </is>
+      </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Audit trail; Admin, General, State</t>
+        </is>
+      </c>
+      <c r="E29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, Sara</t>
+        </is>
+      </c>
+      <c r="F29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Find the suspend and the publish override
+2. Verify the chain
+3. Export a date range
+4. Set the workspace read only, then active again</t>
+        </is>
+      </c>
+      <c r="G29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11</t>
+        </is>
+      </c>
+      <c r="H29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A verified audit trail</t>
+        </is>
+      </c>
+      <c r="I29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nothing extra</t>
+        </is>
+      </c>
+      <c r="J29" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="71" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26 Cloud operator console</t>
+        </is>
+      </c>
+      <c r="B30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6. Integrations</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check the managed-cloud operator console</t>
+        </is>
+      </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">/operator, /operator/&lt;workspace&gt;, /operator/instance, Admin, Support access</t>
+        </is>
+      </c>
+      <c r="E30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator, Admin, Sara</t>
+        </is>
+      </c>
+      <c r="F30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Console is hidden on self-hosted
+2. Operator lists workspaces
+3. Suspend and restore a workspace
+4. Ask for and approve support access
+5. Show an instance banner</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M04</t>
+        </is>
+      </c>
+      <c r="H30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cloud operations checked</t>
+        </is>
+      </c>
+      <c r="I30" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator row added by SQL</t>
+        </is>
+      </c>
+      <c r="J30" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total time</t>
+        </is>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7">
+        <f>SUM(J5:J30)</f>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1591,7 +3223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -1951,7 +3583,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -2045,7 +3677,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M01 Install and first account</t>
+          <t xml:space="preserve">M01 Install and first account: Turn an empty server into an instance with one owner. About 10 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B2" s="3"/>
@@ -2283,7 +3915,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M02 Welcome wizard</t>
+          <t xml:space="preserve">M02 Welcome wizard: Give the new workspace its name, clock, rhythm and starting content. Needs M01 first. About 10 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B7" s="3"/>
@@ -2474,7 +4106,7 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M03 Workspace settings</t>
+          <t xml:space="preserve">M03 Workspace settings: Check that workspace settings save, reload and reset. Needs M02 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B11" s="3"/>
@@ -2825,7 +4457,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M04 Invitations and building the team</t>
+          <t xml:space="preserve">M04 Invitations and building the team: Bring the seven Northwind people into the workspace. Needs M02 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B18" s="3"/>
@@ -3229,7 +4861,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M05 Sign-in and account security</t>
+          <t xml:space="preserve">M05 Sign-in and account security: Prove sign-in, password reset and the second factor protect an account. Needs M04 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B26" s="3"/>
@@ -3802,7 +5434,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M06 People and org chart</t>
+          <t xml:space="preserve">M06 People and org chart: Give everyone a title and a manager so the org chart is real. Needs M04 first. About 20 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B37" s="3"/>
@@ -4251,7 +5883,7 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M07 Spaces</t>
+          <t xml:space="preserve">M07 Spaces: Create the team homes that own goals, boards and sessions. Needs M06 first. About 20 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B46" s="3"/>
@@ -4593,7 +6225,7 @@
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M08 Cycle: prepare, diagnose, direction</t>
+          <t xml:space="preserve">M08 Cycle: prepare, diagnose, direction: Walk the first three phases so drafting has something to stand on. Needs M07 first. About 25 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B53" s="3"/>
@@ -4939,7 +6571,7 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M09 Drafting OKRs and quality checks</t>
+          <t xml:space="preserve">M09 Drafting OKRs and quality checks: Draft objectives and key results while the quality checks fire live. Needs M08 first. About 40 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B60" s="3"/>
@@ -5700,7 +7332,7 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M10 Goal page and documents</t>
+          <t xml:space="preserve">M10 Goal page and documents: Work on one goal: values, confidence, comments, documents and files. Needs M09 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B75" s="3"/>
@@ -6261,7 +7893,7 @@
     <row r="86">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M11 Alignment and publishing</t>
+          <t xml:space="preserve">M11 Alignment and publishing: Align the set and publish it through the six gates. Needs M10 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B86" s="3"/>
@@ -6713,7 +8345,7 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12 KPIs and recovery</t>
+          <t xml:space="preserve">M12 KPIs and recovery: Track KPIs continuously and recover one that falls out of its corridor. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B95" s="3"/>
@@ -7323,7 +8955,7 @@
     <row r="107">
       <c r="A107" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+          <t xml:space="preserve">M13 Initiatives, board and tasks: Plan the work behind key results and move it on the board. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B107" s="3"/>
@@ -7826,7 +9458,7 @@
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+          <t xml:space="preserve">M14 Check-in, review and inbox: Report progress every week and have the reviewer acknowledge it. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B117" s="3"/>
@@ -8435,7 +10067,7 @@
     <row r="129">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15 Weekly session</t>
+          <t xml:space="preserve">M15 Weekly session: Run the four-step weekly session the product facilitates. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B129" s="3"/>
@@ -8832,7 +10464,7 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16 Agents and nudges</t>
+          <t xml:space="preserve">M16 Agents and nudges: Check the two agents nudge, propose and stay quiet when they should. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B137" s="3"/>
@@ -9439,7 +11071,7 @@
     <row r="149">
       <c r="A149" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17 Work map, search and activity</t>
+          <t xml:space="preserve">M17 Work map, search and activity: Check the overview screens, search and basic usability. Needs M15 first. About 20 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B149" s="3"/>
@@ -9777,7 +11409,7 @@
     <row r="156">
       <c r="A156" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard: Close goals and the quarter, and record the result. Needs M15 first. About 25 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B156" s="3"/>
@@ -10120,7 +11752,7 @@
     <row r="163">
       <c r="A163" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19 Access and permissions</t>
+          <t xml:space="preserve">M19 Access and permissions: Check nobody sees or does more than their access allows. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B163" s="3"/>
@@ -10412,7 +12044,7 @@
     <row r="169">
       <c r="A169" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20 AI provider and copilot</t>
+          <t xml:space="preserve">M20 AI provider and copilot: Turn AI on and check it drafts while a person decides. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B169" s="3"/>
@@ -10858,7 +12490,7 @@
     <row r="178">
       <c r="A178" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21 Chat channels and email</t>
+          <t xml:space="preserve">M21 Chat channels and email: Deliver mail and chat messages to real inboxes and apps. Needs M16 first. About 60 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B178" s="3"/>
@@ -11372,7 +13004,7 @@
     <row r="188">
       <c r="A188" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
+          <t xml:space="preserve">M22 Single sign-on and directory sync: Sign in through a company identity provider and sync the directory. Needs M04 first. About 45 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B188" s="3"/>
@@ -11670,7 +13302,7 @@
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23 Import and export</t>
+          <t xml:space="preserve">M23 Import and export: Bring data in from spreadsheets and FlowyTeam, and take it out. Needs M07 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B194" s="3"/>
@@ -12012,7 +13644,7 @@
     <row r="201">
       <c r="A201" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
+          <t xml:space="preserve">M24 API tokens, CLI and external agents: Reach the product from scripts, the command line and outside AI agents. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B201" s="3"/>
@@ -12250,7 +13882,7 @@
     <row r="206">
       <c r="A206" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M25 Audit trail and workspace state</t>
+          <t xml:space="preserve">M25 Audit trail and workspace state: Check the audit trail recorded the sensitive actions from earlier modules. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B206" s="3"/>
@@ -12481,7 +14113,7 @@
     <row r="211">
       <c r="A211" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26 Cloud operator console</t>
+          <t xml:space="preserve">M26 Cloud operator console: Check the managed-cloud operator console. Needs M04 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
       <c r="B211" s="3"/>
@@ -12799,7 +14431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -335,7 +335,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start a fresh instance with an empty database and the staging overlay (docs/testing/staging.md). Note the URL.</t>
+          <t xml:space="preserve">Start a fresh instance with an empty database and the staging overlay (docs/install/staging.md). Note the URL.</t>
         </is>
       </c>
     </row>

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Bug Log" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$220</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bug Log'!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -662,7 +662,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 191 test cases across 26 modules.</t>
+          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 193 test cases across 26 modules.</t>
         </is>
       </c>
       <c r="B86" s="10"/>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator row added by SQL</t>
+          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator</t>
         </is>
       </c>
       <c r="J30" s="1">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPENOKR_CLOUD=true and the operator row added by SQL (docs/design/p8-t01b-operator-console.md)</t>
+          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator (docs/install/cloud.md)</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
@@ -14589,9 +14589,116 @@
       <c r="M218" s="5"/>
       <c r="N218" s="5"/>
     </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-06</t>
+        </is>
+      </c>
+      <c r="B219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26 Cloud operator console</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator sets a plan, and a downgrade below the headcount is refused</t>
+        </is>
+      </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator</t>
+        </is>
+      </c>
+      <c r="E219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-02 done, and cloud.plans holds a plan with fewer seats than Northwind Labs has people</t>
+        </is>
+      </c>
+      <c r="F219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the workspace, under "Plan and seats" pick the small plan, write a reason, click "Set the plan for Northwind Labs"
+2. Pick a larger plan, or type a seat count above the headcount, and apply again</t>
+        </is>
+      </c>
+      <c r="G219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The first is refused naming the seats the plan has and the seats in use. The second is applied and the Tenant facts show the new plan and seats</t>
+        </is>
+      </c>
+      <c r="H219" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="I219" s="1"/>
+      <c r="J219" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K219" s="5"/>
+      <c r="L219" s="5"/>
+      <c r="M219" s="5"/>
+      <c r="N219" s="5"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07</t>
+        </is>
+      </c>
+      <c r="B220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26 Cloud operator console</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrator sees who holds a seat and changes plan</t>
+        </is>
+      </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07 done</t>
+        </is>
+      </c>
+      <c r="F220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Admin, Plan and seats
+2. Read the list under "Who holds a seat"
+3. Under "Move to" pick another plan and click "Change plan"</t>
+        </is>
+      </c>
+      <c r="G220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The list names every person and invitation the seat count counts, and no guest or agent. The plan changes, or is refused naming both numbers when it has too few seats</t>
+        </is>
+      </c>
+      <c r="H220" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="I220" s="1"/>
+      <c r="J220" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K220" s="5"/>
+      <c r="L220" s="5"/>
+      <c r="M220" s="5"/>
+      <c r="N220" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N218"/>
-  <conditionalFormatting sqref="J2:J218">
+  <autoFilter ref="A1:N220"/>
+  <conditionalFormatting sqref="J2:J220">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",J2)))</formula>
     </cfRule>
@@ -14609,10 +14716,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J218">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J220">
       <formula1>"Not Run,Pass,Fail,Error,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H218">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H220">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -1702,7 +1702,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" ht="84" customHeight="1">
+    <row r="22" ht="110" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
@@ -1732,8 +1732,8 @@
         <is>
           <t xml:space="preserve">1. Closing a goal needs a retrospective
 2. Close and reopen a goal
-3. Score every key result in phase 7
-4. Record the result on the scorecard
+3. Score every key result and close the cycle in phase 7
+4. See the result on the scorecard and the inheritance in the next quarter
 5. Archive the old cycle
 6. Look for the quarterly review</t>
         </is>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 7 Review and learn</t>
+          <t xml:space="preserve">Phase 7 Review and learn, and close the cycle</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
@@ -11745,19 +11745,19 @@
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every key result has a score</t>
+          <t xml:space="preserve">A quarterly review of the current cycle is running</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 7
-2. Score every key result and write the retrospective
-3. Use "Carry into the next cycle"</t>
+          <t xml:space="preserve">1. Open Cycle, phase 7, before any key result is scored
+2. Score every key result and write the team retro in the quarterly review, then close the review
+3. Back on phase 7, click "Close &lt;cycle name&gt;"</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portfolio average and bands shown. Phase 7 shows done. Carried items appear in the next cycle</t>
+          <t xml:space="preserve">Before scoring, "Close the cycle" is disabled and lists what phase 7 still needs. After scoring, the portfolio average and bands show and phase 7 shows done. After closing, the chip reads "closed" and "How this cycle closed" shows the result and verdict, and says the next cycle receives the inheritance when it is created</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Record the result on the scorecard</t>
+          <t xml:space="preserve">The closed cycle on the scorecard and in the next quarter</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
@@ -11799,20 +11799,21 @@
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Current cycle scored</t>
+          <t xml:space="preserve">M18-03 done</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Scorecard
-2. In "Close a cycle out" pick the cycle and click "Record"
-3. Use "Hand over from" into the next cycle
-4. Click "Export as CSV"</t>
+2. Check "Close a cycle out" no longer offers the closed cycle
+3. On the Cycles card create the cycle containing a date in the next quarter
+4. Open the new quarter's phase 2 and phase 3
+5. Click "Export as CSV" on the scorecard</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The cycle row shows result and verdict. The CSV downloads and opens</t>
+          <t xml:space="preserve">The closed cycle's row shows result and verdict. Phase 2 lists every prior score and each carried item at impact 4. Phase 3 lists the lowest process-health statement as a priority, not as an issue. The CSV downloads and opens</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G61" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warning "This phase is blocked by earlier work" with "Go and gather what is missing". The forms can still be used</t>
+          <t xml:space="preserve">Notice "Earlier phases still have gaps" with "Go and gather what is missing". The forms can still be used</t>
         </is>
       </c>
       <c r="H61" s="1" t="inlineStr">

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G66" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBJ-1 FAIL and "OBJ-2 · Inspiring and directional" WARN. The meter shows the pass, warn and fail counts</t>
+          <t xml:space="preserve">OBJ-1 WARN and "OBJ-2 · Qualitative and memorable" WARN. The meter shows the pass, warn and fail counts</t>
         </is>
       </c>
       <c r="H66" s="1" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A one-word objective warns</t>
+          <t xml:space="preserve">A long objective warns</t>
         </is>
       </c>
       <c r="D67" s="1" t="inlineStr">
@@ -7018,13 +7018,13 @@
       </c>
       <c r="F67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type: Grow
+          <t xml:space="preserve">1. Type an objective of more than eighteen words
 2. Click the OBJ-2 chip</t>
         </is>
       </c>
       <c r="G67" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The rule card shows WARN and the prompt "Very short. Would someone outside your team understand where you are headed and why it matters?"</t>
+          <t xml:space="preserve">The rule card shows WARN and the prompt "Trim it. If your team cannot recite it from memory, it will not steer their daily decisions."</t>
         </is>
       </c>
       <c r="H67" s="1" t="inlineStr">

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Bug Log" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$221</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bug Log'!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -662,7 +662,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 193 test cases across 26 modules.</t>
+          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 194 test cases across 26 modules.</t>
         </is>
       </c>
       <c r="B86" s="10"/>
@@ -8295,7 +8295,7 @@
       </c>
       <c r="G92" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chip "&lt;n&gt; of 6 green". Each red gate lists its reasons. Each fix link opens the place that fixes it</t>
+          <t xml:space="preserve">Chip "&lt;n&gt; of 5 green" (gate 6 is off by default). Each gate shows Blocks, Warns or Off. Each unmet gate lists its reasons, and each fix link opens the place that fixes it</t>
         </is>
       </c>
       <c r="H92" s="1" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="C93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn all six gates green</t>
+          <t xml:space="preserve">Turn the blocking gates green</t>
         </is>
       </c>
       <c r="D93" s="1" t="inlineStr">
@@ -8346,12 +8346,12 @@
       </c>
       <c r="F93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Follow every gate's fix until each one is green</t>
+          <t xml:space="preserve">1. Follow the fix for gates 1 and 2 until both are green</t>
         </is>
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"6 of 6 green" and "Publish the set" becomes clickable</t>
+          <t xml:space="preserve">"Publish the set" becomes clickable, even with a gate that warns still amber</t>
         </is>
       </c>
       <c r="H93" s="1" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Button disabled. Text: "All six gates have to be green. A gate nobody can judge counts against publication."</t>
+          <t xml:space="preserve">Button disabled. Text: "Every gate that blocks has to be green. A gate nobody can judge counts against publication; a gate that warns does not."</t>
         </is>
       </c>
       <c r="H94" s="1" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="C95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Override needs a real reason</t>
+          <t xml:space="preserve">Publish the company set first</t>
         </is>
       </c>
       <c r="D95" s="1" t="inlineStr">
@@ -8449,19 +8449,17 @@
       </c>
       <c r="E95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least one gate red</t>
+          <t xml:space="preserve">Company objectives drafted, team objectives still in progress</t>
         </is>
       </c>
       <c r="F95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Expand "Publish anyway, past the red gates"
-2. Type a reason under 20 characters
-3. Type a reason of 20+ characters and click "Override and publish"</t>
+          <t xml:space="preserve">1. Click "Publish the company set first"</t>
         </is>
       </c>
       <c r="G95" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Short reason is blocked. Long reason publishes: "Published &lt;date&gt;." and the cycle moves to phase 6</t>
+          <t xml:space="preserve">"Company set published &lt;date&gt;." The main button now reads "Publish the department and team sets"</t>
         </is>
       </c>
       <c r="H95" s="1" t="inlineStr">
@@ -8493,27 +8491,29 @@
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Only the admin can publish</t>
+          <t xml:space="preserve">Override needs a real reason</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before publishing</t>
+          <t xml:space="preserve">At least one gate red</t>
         </is>
       </c>
       <c r="F96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 5</t>
+          <t xml:space="preserve">1. Expand "Publish anyway, past the red gates"
+2. Type a reason under 20 characters
+3. Type a reason of 20+ characters and click "Override and publish"</t>
         </is>
       </c>
       <c r="G96" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Publishing is a workspace administrator's call." No publish button</t>
+          <t xml:space="preserve">Short reason is blocked. Long reason publishes: "Published &lt;date&gt;." and the cycle moves to phase 6</t>
         </is>
       </c>
       <c r="H96" s="1" t="inlineStr">
@@ -8533,115 +8533,113 @@
       <c r="N96" s="5"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11-09</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M11 Alignment and publishing</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the admin can publish</t>
+        </is>
+      </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya</t>
+        </is>
+      </c>
+      <c r="E97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before publishing</t>
+        </is>
+      </c>
+      <c r="F97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Cycle, phase 5</t>
+        </is>
+      </c>
+      <c r="G97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Publishing is a workspace administrator's call." No publish button</t>
+        </is>
+      </c>
+      <c r="H97" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I97" s="1"/>
+      <c r="J97" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K97" s="5"/>
+      <c r="L97" s="5"/>
+      <c r="M97" s="5"/>
+      <c r="N97" s="5"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M12 KPIs and recovery: Track KPIs continuously and recover one that falls out of its corridor. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="3"/>
-      <c r="D97" s="3"/>
-      <c r="E97" s="3"/>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="H97" s="3"/>
-      <c r="I97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
-      <c r="L97" s="3"/>
-      <c r="M97" s="3"/>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="inlineStr">
+      <c r="B98" s="3"/>
+      <c r="C98" s="3"/>
+      <c r="D98" s="3"/>
+      <c r="E98" s="3"/>
+      <c r="F98" s="3"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="3"/>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3"/>
+      <c r="K98" s="3"/>
+      <c r="L98" s="3"/>
+      <c r="M98" s="3"/>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M12-01</t>
         </is>
       </c>
-      <c r="B98" s="1" t="inlineStr">
+      <c r="B99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M12 KPIs and recovery</t>
         </is>
       </c>
-      <c r="C98" s="1" t="inlineStr">
+      <c r="C99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Add a KPI</t>
         </is>
       </c>
-      <c r="D98" s="1" t="inlineStr">
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Priya</t>
         </is>
       </c>
-      <c r="E98" s="1" t="inlineStr">
+      <c r="E99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F98" s="1" t="inlineStr">
+      <c r="F99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open KPIs, card "Add a KPI"
 2. Click "Add" with an empty title
 3. Title Test NPS, Frequency monthly, Better when higher, Standing target 100, click "Add"</t>
         </is>
       </c>
-      <c r="G98" s="1" t="inlineStr">
+      <c r="G99" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Empty: "A KPI needs a title. What is being measured?" Then Test NPS appears in the grid</t>
-        </is>
-      </c>
-      <c r="H98" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I98" s="1"/>
-      <c r="J98" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M12-02</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M12 KPIs and recovery</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Values colour by the health corridor</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M12-01 done</t>
-        </is>
-      </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. In the current period cell of Test NPS type 95 and press Enter
-2. Change it to 80
-3. Change it to 60</t>
-        </is>
-      </c>
-      <c r="G99" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95 green and healthy. 80 amber and watch. 60 red and unhealthy. "Now" shows the percentage</t>
         </is>
       </c>
       <c r="H99" s="1" t="inlineStr">
@@ -8663,7 +8661,7 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-03</t>
+          <t xml:space="preserve">M12-02</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
@@ -8673,7 +8671,7 @@
       </c>
       <c r="C100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lower-is-better KPI reverses the maths</t>
+          <t xml:space="preserve">Values colour by the health corridor</t>
         </is>
       </c>
       <c r="D100" s="1" t="inlineStr">
@@ -8683,23 +8681,24 @@
       </c>
       <c r="E100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">M12-01 done</t>
         </is>
       </c>
       <c r="F100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Add KPI Support backlog, Better when lower, target 100
-2. Enter 125</t>
+          <t xml:space="preserve">1. In the current period cell of Test NPS type 95 and press Enter
+2. Change it to 80
+3. Change it to 60</t>
         </is>
       </c>
       <c r="G100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amber, 80%, watch</t>
+          <t xml:space="preserve">95 green and healthy. 80 amber and watch. 60 red and unhealthy. "Now" shows the percentage</t>
         </is>
       </c>
       <c r="H100" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I100" s="1"/>
@@ -8716,7 +8715,7 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-04</t>
+          <t xml:space="preserve">M12-03</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
@@ -8726,7 +8725,7 @@
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grid refuses text and handles clearing</t>
+          <t xml:space="preserve">Lower-is-better KPI reverses the maths</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -8736,19 +8735,18 @@
       </c>
       <c r="E101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-01 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Type abc in a cell and press Enter
-2. Clear a cell and press Enter
-3. Type a value and press Esc</t>
+          <t xml:space="preserve">1. Add KPI Support backlog, Better when lower, target 100
+2. Enter 125</t>
         </is>
       </c>
       <c r="G101" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">abc: "A value has to be a number, or empty to clear it." Clearing shows no data. Esc restores the old value</t>
+          <t xml:space="preserve">Amber, 80%, watch</t>
         </is>
       </c>
       <c r="H101" s="1" t="inlineStr">
@@ -8770,7 +8768,7 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-05</t>
+          <t xml:space="preserve">M12-04</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
@@ -8780,7 +8778,7 @@
       </c>
       <c r="C102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add a category and filter</t>
+          <t xml:space="preserve">Grid refuses text and handles clearing</t>
         </is>
       </c>
       <c r="D102" s="1" t="inlineStr">
@@ -8790,23 +8788,24 @@
       </c>
       <c r="E102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">M12-01 done</t>
         </is>
       </c>
       <c r="F102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In "Add a category" add Revenue
-2. Filter the grid by "Category" and "State"</t>
+          <t xml:space="preserve">1. Type abc in a cell and press Enter
+2. Clear a cell and press Enter
+3. Type a value and press Esc</t>
         </is>
       </c>
       <c r="G102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The grid shows only matching KPIs. The filter stays in the URL after reload</t>
+          <t xml:space="preserve">abc: "A value has to be a number, or empty to clear it." Clearing shows no data. Esc restores the old value</t>
         </is>
       </c>
       <c r="H102" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I102" s="1"/>
@@ -8823,7 +8822,7 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-06</t>
+          <t xml:space="preserve">M12-05</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
@@ -8833,7 +8832,7 @@
       </c>
       <c r="C103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">KPI detail page</t>
+          <t xml:space="preserve">Add a category and filter</t>
         </is>
       </c>
       <c r="D103" s="1" t="inlineStr">
@@ -8843,22 +8842,23 @@
       </c>
       <c r="E103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-02 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click Test NPS</t>
+          <t xml:space="preserve">1. In "Add a category" add Revenue
+2. Filter the grid by "Category" and "State"</t>
         </is>
       </c>
       <c r="G103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chart "The periods, against the corridor", the "Records" table and "healthy at 90%, watch at 70%"</t>
+          <t xml:space="preserve">The grid shows only matching KPIs. The filter stays in the URL after reload</t>
         </is>
       </c>
       <c r="H103" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I103" s="1"/>
@@ -8875,7 +8875,7 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-07</t>
+          <t xml:space="preserve">M12-06</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
@@ -8885,7 +8885,7 @@
       </c>
       <c r="C104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A calculated KPI from a formula</t>
+          <t xml:space="preserve">KPI detail page</t>
         </is>
       </c>
       <c r="D104" s="1" t="inlineStr">
@@ -8895,19 +8895,17 @@
       </c>
       <c r="E104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two KPIs with values</t>
+          <t xml:space="preserve">M12-02 done</t>
         </is>
       </c>
       <c r="F104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open a third KPI, section Formula
-2. Pick one source only and click "Save the formula"
-3. Pick sum with two sources and save</t>
+          <t xml:space="preserve">1. Click Test NPS</t>
         </is>
       </c>
       <c r="G104" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One source: "One source is a copy, not a calculation." Two sources: "Saved and evaluated for this period." The grid cell becomes read-only</t>
+          <t xml:space="preserve">Chart "The periods, against the corridor", the "Records" table and "healthy at 90%, watch at 70%"</t>
         </is>
       </c>
       <c r="H104" s="1" t="inlineStr">
@@ -8929,30 +8927,84 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M12-07</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12 KPIs and recovery</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A calculated KPI from a formula</t>
+        </is>
+      </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya</t>
+        </is>
+      </c>
+      <c r="E105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Two KPIs with values</t>
+        </is>
+      </c>
+      <c r="F105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open a third KPI, section Formula
+2. Pick one source only and click "Save the formula"
+3. Pick sum with two sources and save</t>
+        </is>
+      </c>
+      <c r="G105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">One source: "One source is a copy, not a calculation." Two sources: "Saved and evaluated for this period." The grid cell becomes read-only</t>
+        </is>
+      </c>
+      <c r="H105" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I105" s="1"/>
+      <c r="J105" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M12-08</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
+      <c r="B106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M12 KPIs and recovery</t>
         </is>
       </c>
-      <c r="C105" s="1" t="inlineStr">
+      <c r="C106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Build a KPI tree with a driver</t>
         </is>
       </c>
-      <c r="D105" s="1" t="inlineStr">
+      <c r="D106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Priya</t>
         </is>
       </c>
-      <c r="E105" s="1" t="inlineStr">
+      <c r="E106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F105" s="1" t="inlineStr">
+      <c r="F106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open KPIs, Trees
 2. In "Name a tree" type Operating margin and click "Name it"
@@ -8960,66 +9012,14 @@
 4. Click "add driver" and add Qualified leads, leading</t>
         </is>
       </c>
-      <c r="G105" s="1" t="inlineStr">
+      <c r="G106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The tree lists Test NPS with Qualified leads under it</t>
         </is>
       </c>
-      <c r="H105" s="1" t="inlineStr">
+      <c r="H106" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I105" s="1"/>
-      <c r="J105" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M12-09</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M12 KPIs and recovery</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An unhealthy KPI appears on the recovery board</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test NPS at 60</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open KPIs, "Recovery board"</t>
-        </is>
-      </c>
-      <c r="G106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Test NPS card with chip "unhealthy", 60% and "Launch recovery"</t>
-        </is>
-      </c>
-      <c r="H106" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I106" s="1"/>
@@ -9036,7 +9036,7 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-10</t>
+          <t xml:space="preserve">M12-09</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="C107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Launch a recovery objective</t>
+          <t xml:space="preserve">An unhealthy KPI appears on the recovery board</t>
         </is>
       </c>
       <c r="D107" s="1" t="inlineStr">
@@ -9056,19 +9056,17 @@
       </c>
       <c r="E107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12-09 done. A current quarterly cycle exists</t>
+          <t xml:space="preserve">Test NPS at 60</t>
         </is>
       </c>
       <c r="F107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Launch recovery"
-2. Click it again if still visible
-3. Open the new objective</t>
+          <t xml:space="preserve">1. Open KPIs, "Recovery board"</t>
         </is>
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objective "Bring Test NPS back to 100" with one key result per leading driver. KPI chip becomes "recovering". A second launch is refused</t>
+          <t xml:space="preserve">Test NPS card with chip "unhealthy", 60% and "Launch recovery"</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
@@ -9090,30 +9088,84 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M12-10</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12 KPIs and recovery</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Launch a recovery objective</t>
+        </is>
+      </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12-09 done. A current quarterly cycle exists</t>
+        </is>
+      </c>
+      <c r="F108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click "Launch recovery"
+2. Click it again if still visible
+3. Open the new objective</t>
+        </is>
+      </c>
+      <c r="G108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Objective "Bring Test NPS back to 100" with one key result per leading driver. KPI chip becomes "recovering". A second launch is refused</t>
+        </is>
+      </c>
+      <c r="H108" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I108" s="1"/>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M12-11</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M12 KPIs and recovery</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Changing a threshold changes the colours</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="D109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
+      <c r="E109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M12-02 done</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
+      <c r="F109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Rhythm, "KPIs and recovery"
 2. Raise the healthy line to 96 and save
@@ -9121,136 +9173,82 @@
 4. Reset to defaults afterwards</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr">
+      <c r="G109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The 95 value turns amber. After reset it is green again</t>
         </is>
       </c>
-      <c r="H108" s="1" t="inlineStr">
+      <c r="H109" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I108" s="1"/>
-      <c r="J108" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K108" s="5"/>
-      <c r="L108" s="5"/>
-      <c r="M108" s="5"/>
-      <c r="N108" s="5"/>
-    </row>
-    <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="I109" s="1"/>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K109" s="5"/>
+      <c r="L109" s="5"/>
+      <c r="M109" s="5"/>
+      <c r="N109" s="5"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks: Plan the work behind key results and move it on the board. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B109" s="3"/>
-      <c r="C109" s="3"/>
-      <c r="D109" s="3"/>
-      <c r="E109" s="3"/>
-      <c r="F109" s="3"/>
-      <c r="G109" s="3"/>
-      <c r="H109" s="3"/>
-      <c r="I109" s="3"/>
-      <c r="J109" s="3"/>
-      <c r="K109" s="3"/>
-      <c r="L109" s="3"/>
-      <c r="M109" s="3"/>
-      <c r="N109" s="3"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="inlineStr">
+      <c r="B110" s="3"/>
+      <c r="C110" s="3"/>
+      <c r="D110" s="3"/>
+      <c r="E110" s="3"/>
+      <c r="F110" s="3"/>
+      <c r="G110" s="3"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="J110" s="3"/>
+      <c r="K110" s="3"/>
+      <c r="L110" s="3"/>
+      <c r="M110" s="3"/>
+      <c r="N110" s="3"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13-01</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
+      <c r="B111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks</t>
         </is>
       </c>
-      <c r="C110" s="1" t="inlineStr">
+      <c r="C111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Add an initiative</t>
         </is>
       </c>
-      <c r="D110" s="1" t="inlineStr">
+      <c r="D111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mei</t>
         </is>
       </c>
-      <c r="E110" s="1" t="inlineStr">
+      <c r="E111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M07 done</t>
         </is>
       </c>
-      <c r="F110" s="1" t="inlineStr">
+      <c r="F111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Initiatives, click "Add" with empty fields
 2. Title Rebuild the activation flow, Space Product, Owner Mei, start and end dates, click "Add"</t>
         </is>
       </c>
-      <c r="G110" s="1" t="inlineStr">
+      <c r="G111" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Empty: "An initiative needs a title. What work is this?" Then the initiative is listed with "not yet behind a key result"</t>
-        </is>
-      </c>
-      <c r="H110" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I110" s="1"/>
-      <c r="J110" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K110" s="5"/>
-      <c r="L110" s="5"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-02</t>
-        </is>
-      </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link an initiative to a key result</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mei</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-01 done</t>
-        </is>
-      </c>
-      <c r="F111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open the initiative
-2. In "Record this work against a key result" pick one and click "Link"
-3. Click "Unlink" then link again</t>
-        </is>
-      </c>
-      <c r="G111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The key result is listed and can be removed and added back</t>
         </is>
       </c>
       <c r="H111" s="1" t="inlineStr">
@@ -9272,7 +9270,7 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-03</t>
+          <t xml:space="preserve">M13-02</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
@@ -9282,7 +9280,7 @@
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Over-capacity warning</t>
+          <t xml:space="preserve">Link an initiative to a key result</t>
         </is>
       </c>
       <c r="D112" s="1" t="inlineStr">
@@ -9297,17 +9295,19 @@
       </c>
       <c r="F112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set Capacity to Exceeds</t>
+          <t xml:space="preserve">1. Open the initiative
+2. In "Record this work against a key result" pick one and click "Link"
+3. Click "Unlink" then link again</t>
         </is>
       </c>
       <c r="G112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"This is over capacity, so publish gate five refuses the cycle..."</t>
+          <t xml:space="preserve">The key result is listed and can be removed and added back</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I112" s="1"/>
@@ -9324,7 +9324,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-04</t>
+          <t xml:space="preserve">M13-03</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
@@ -9334,34 +9334,32 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add a task on the board</t>
+          <t xml:space="preserve">Over-capacity warning</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Mei</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M07 done</t>
+          <t xml:space="preserve">M13-01 done</t>
         </is>
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Board, pick Product
-2. Click "Add" with an empty title
-3. Add Rewrite the first-run screen, column To do, a key result, a due date</t>
+          <t xml:space="preserve">1. Set Capacity to Exceeds</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty: "A task needs a title. What has to happen?" Then the card is in "To do" with the key result and due date</t>
+          <t xml:space="preserve">"This is over capacity, so publish gate five refuses the cycle..."</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I113" s="1"/>
@@ -9378,7 +9376,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-05</t>
+          <t xml:space="preserve">M13-04</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
@@ -9388,7 +9386,7 @@
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Move a card by drag and by arrows</t>
+          <t xml:space="preserve">Add a task on the board</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
@@ -9398,18 +9396,19 @@
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-04 done</t>
+          <t xml:space="preserve">M07 done</t>
         </is>
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Drag the card to "In progress"
-2. Use the arrow button to move it to "Done"</t>
+          <t xml:space="preserve">1. Open Board, pick Product
+2. Click "Add" with an empty title
+3. Add Rewrite the first-run screen, column To do, a key result, a due date</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The card moves and the column counts change. Moving never changes key result progress</t>
+          <t xml:space="preserve">Empty: "A task needs a title. What has to happen?" Then the card is in "To do" with the key result and due date</t>
         </is>
       </c>
       <c r="H114" s="1" t="inlineStr">
@@ -9431,7 +9430,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-06</t>
+          <t xml:space="preserve">M13-05</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
@@ -9441,32 +9440,33 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The board updates live for others</t>
+          <t xml:space="preserve">Move a card by drag and by arrows</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya and Sara both on the Product board</t>
+          <t xml:space="preserve">M13-04 done</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sara moves a card</t>
+          <t xml:space="preserve">1. Drag the card to "In progress"
+2. Use the arrow button to move it to "Done"</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya's board shows the move without reloading</t>
+          <t xml:space="preserve">The card moves and the column counts change. Moving never changes key result progress</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I115" s="1"/>
@@ -9483,7 +9483,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-07</t>
+          <t xml:space="preserve">M13-06</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
@@ -9493,28 +9493,27 @@
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done work with no movement raises a warning</t>
+          <t xml:space="preserve">The board updates live for others</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A key result with linked tasks and no value change</t>
+          <t xml:space="preserve">Priya and Sara both on the Product board</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Move every linked task to Done
-2. Read the rail "What this work is meant to move"</t>
+          <t xml:space="preserve">1. Sara moves a card</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warning that all linked tasks are complete and the measure is still at its baseline</t>
+          <t xml:space="preserve">Priya's board shows the move without reloading</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr">
@@ -9536,30 +9535,83 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M13-07</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done work with no movement raises a warning</t>
+        </is>
+      </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A key result with linked tasks and no value change</t>
+        </is>
+      </c>
+      <c r="F117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Move every linked task to Done
+2. Read the rail "What this work is meant to move"</t>
+        </is>
+      </c>
+      <c r="G117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warning that all linked tasks are complete and the measure is still at its baseline</t>
+        </is>
+      </c>
+      <c r="H117" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I117" s="1"/>
+      <c r="J117" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K117" s="5"/>
+      <c r="L117" s="5"/>
+      <c r="M117" s="5"/>
+      <c r="N117" s="5"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M13-08</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
+      <c r="B118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks</t>
         </is>
       </c>
-      <c r="C117" s="1" t="inlineStr">
+      <c r="C118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Task checklist, assignees and due date</t>
         </is>
       </c>
-      <c r="D117" s="1" t="inlineStr">
+      <c r="D118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E117" s="1" t="inlineStr">
+      <c r="E118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13-04 done</t>
         </is>
       </c>
-      <c r="F117" s="1" t="inlineStr">
+      <c r="F118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the task
 2. Click "Add" on an empty checklist line
@@ -9567,74 +9619,21 @@
 4. Assign Mei. Change the due date</t>
         </is>
       </c>
-      <c r="G117" s="1" t="inlineStr">
+      <c r="G118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Empty: "A checklist line needs some words." Count shows "1 of 2 done". Mei is under "Assignees"</t>
         </is>
       </c>
-      <c r="H117" s="1" t="inlineStr">
+      <c r="H118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I117" s="1" t="inlineStr">
+      <c r="I118" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tasks have no comments or files by design today</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K117" s="5"/>
-      <c r="L117" s="5"/>
-      <c r="M117" s="5"/>
-      <c r="N117" s="5"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-09</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only the admin can delete a task</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara, then Admin</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-04 done</t>
-        </is>
-      </c>
-      <c r="F118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. As Sara open the task and look for "Delete"
-2. As Admin delete it</t>
-        </is>
-      </c>
-      <c r="G118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara sees no Delete. Admin's delete returns to the board and the card is gone</t>
-        </is>
-      </c>
-      <c r="H118" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I118" s="1"/>
       <c r="J118" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -9646,85 +9645,82 @@
       <c r="N118" s="5"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13-09</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the admin can delete a task</t>
+        </is>
+      </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, then Admin</t>
+        </is>
+      </c>
+      <c r="E119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13-04 done</t>
+        </is>
+      </c>
+      <c r="F119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. As Sara open the task and look for "Delete"
+2. As Admin delete it</t>
+        </is>
+      </c>
+      <c r="G119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara sees no Delete. Admin's delete returns to the board and the card is gone</t>
+        </is>
+      </c>
+      <c r="H119" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I119" s="1"/>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K119" s="5"/>
+      <c r="L119" s="5"/>
+      <c r="M119" s="5"/>
+      <c r="N119" s="5"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M14 Check-in, review and inbox: Report progress every week and have the reviewer acknowledge it. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B119" s="3"/>
-      <c r="C119" s="3"/>
-      <c r="D119" s="3"/>
-      <c r="E119" s="3"/>
-      <c r="F119" s="3"/>
-      <c r="G119" s="3"/>
-      <c r="H119" s="3"/>
-      <c r="I119" s="3"/>
-      <c r="J119" s="3"/>
-      <c r="K119" s="3"/>
-      <c r="L119" s="3"/>
-      <c r="M119" s="3"/>
-      <c r="N119" s="3"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14-01</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14 Check-in, review and inbox</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only what is due is listed</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara champions a goal that is due</t>
-        </is>
-      </c>
-      <c r="F120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Check in</t>
-        </is>
-      </c>
-      <c r="G120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara's goal is listed. If nothing is due: "Nothing of yours is due."</t>
-        </is>
-      </c>
-      <c r="H120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I120" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A goal is due only near its next check-in date. Set Admin, Rhythm check-in frequency to daily to make it due today</t>
-        </is>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K120" s="5"/>
-      <c r="L120" s="5"/>
-      <c r="M120" s="5"/>
-      <c r="N120" s="5"/>
+      <c r="B120" s="3"/>
+      <c r="C120" s="3"/>
+      <c r="D120" s="3"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="3"/>
+      <c r="G120" s="3"/>
+      <c r="H120" s="3"/>
+      <c r="I120" s="3"/>
+      <c r="J120" s="3"/>
+      <c r="K120" s="3"/>
+      <c r="L120" s="3"/>
+      <c r="M120" s="3"/>
+      <c r="N120" s="3"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-02</t>
+          <t xml:space="preserve">M14-01</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
@@ -9734,7 +9730,7 @@
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A check-in needs a narrative</t>
+          <t xml:space="preserve">Only what is due is listed</t>
         </is>
       </c>
       <c r="D121" s="1" t="inlineStr">
@@ -9744,19 +9740,17 @@
       </c>
       <c r="E121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-01 done</t>
+          <t xml:space="preserve">Sara champions a goal that is due</t>
         </is>
       </c>
       <c r="F121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Pick the goal
-2. Set "Status" to "Caution", set confidence and new key result values
-3. Leave the narrative empty and click "Publish"</t>
+          <t xml:space="preserve">1. Open Check in</t>
         </is>
       </c>
       <c r="G121" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"A check-in needs a narrative. What moved, what is in the way, and what happens next?"</t>
+          <t xml:space="preserve">Sara's goal is listed. If nothing is due: "Nothing of yours is due."</t>
         </is>
       </c>
       <c r="H121" s="1" t="inlineStr">
@@ -9764,7 +9758,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I121" s="1"/>
+      <c r="I121" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal is due only near its next check-in date. Set Admin, Rhythm check-in frequency to daily to make it due today</t>
+        </is>
+      </c>
       <c r="J121" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -9778,7 +9776,7 @@
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-03</t>
+          <t xml:space="preserve">M14-02</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
@@ -9788,7 +9786,7 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post a check-in</t>
+          <t xml:space="preserve">A check-in needs a narrative</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -9798,17 +9796,19 @@
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-02 done</t>
+          <t xml:space="preserve">M14-01 done</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Write the narrative and click "Publish"</t>
+          <t xml:space="preserve">1. Pick the goal
+2. Set "Status" to "Caution", set confidence and new key result values
+3. Leave the narrative empty and click "Publish"</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Check-in history" shows it as "awaiting the reviewer". The goal page shows the new values</t>
+          <t xml:space="preserve">"A check-in needs a narrative. What moved, what is in the way, and what happens next?"</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
@@ -9830,7 +9830,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-04</t>
+          <t xml:space="preserve">M14-03</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
@@ -9840,27 +9840,27 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Someone who is not the champion cannot post</t>
+          <t xml:space="preserve">Post a check-in</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-03 done</t>
+          <t xml:space="preserve">M14-02 done</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Sara's goal check-ins</t>
+          <t xml:space="preserve">1. Write the narrative and click "Publish"</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"You can read this goal's check-ins but not post one. The champion posts them."</t>
+          <t xml:space="preserve">"Check-in history" shows it as "awaiting the reviewer". The goal page shows the new values</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr">
@@ -9882,7 +9882,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-05</t>
+          <t xml:space="preserve">M14-04</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
@@ -9892,12 +9892,12 @@
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The wrong reviewer cannot acknowledge</t>
+          <t xml:space="preserve">Someone who is not the champion cannot post</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mei</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
@@ -9907,17 +9907,17 @@
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the check-in and try "Acknowledge"</t>
+          <t xml:space="preserve">1. Open Sara's goal check-ins</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Only this goal's reviewer can acknowledge its check-ins."</t>
+          <t xml:space="preserve">"You can read this goal's check-ins but not post one. The champion posts them."</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I124" s="1"/>
@@ -9934,7 +9934,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-06</t>
+          <t xml:space="preserve">M14-05</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
@@ -9944,12 +9944,12 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The reviewer acknowledges from What you owe</t>
+          <t xml:space="preserve">The wrong reviewer cannot acknowledge</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya</t>
+          <t xml:space="preserve">Mei</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -9959,18 +9959,17 @@
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Review
-2. Find the check-in row and click its action</t>
+          <t xml:space="preserve">1. Open the check-in and try "Acknowledge"</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The check-in shows "acknowledged". The row leaves the list. An empty list says "You are all caught up."</t>
+          <t xml:space="preserve">"Only this goal's reviewer can acknowledge its check-ins."</t>
         </is>
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I125" s="1"/>
@@ -9987,7 +9986,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-07</t>
+          <t xml:space="preserve">M14-06</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
@@ -9997,12 +9996,12 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correct a check-in inside the window</t>
+          <t xml:space="preserve">The reviewer acknowledges from What you owe</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -10012,17 +10011,18 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Correct it" and change the narrative</t>
+          <t xml:space="preserve">1. Open Review
+2. Find the check-in row and click its action</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The change saves. After the window: "The window has closed; post a new one instead"</t>
+          <t xml:space="preserve">The check-in shows "acknowledged". The row leaves the list. An empty list says "You are all caught up."</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I126" s="1"/>
@@ -10039,7 +10039,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-08</t>
+          <t xml:space="preserve">M14-07</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
@@ -10049,33 +10049,32 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team confidence votes reveal together</t>
+          <t xml:space="preserve">Correct a check-in inside the window</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara, Priya, Mei</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-01 done</t>
+          <t xml:space="preserve">M14-03 done</t>
         </is>
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each person clicks "Vote" on a key result
-2. Click "Reveal together"</t>
+          <t xml:space="preserve">1. Click "Correct it" and change the narrative</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before reveal each sees only "Your vote: X". After reveal all votes show</t>
+          <t xml:space="preserve">The change saves. After the window: "The window has closed; post a new one instead"</t>
         </is>
       </c>
       <c r="H127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I127" s="1"/>
@@ -10092,30 +10091,83 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M14-08</t>
+        </is>
+      </c>
+      <c r="B128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team confidence votes reveal together</t>
+        </is>
+      </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Priya, Mei</t>
+        </is>
+      </c>
+      <c r="E128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14-01 done</t>
+        </is>
+      </c>
+      <c r="F128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Each person clicks "Vote" on a key result
+2. Click "Reveal together"</t>
+        </is>
+      </c>
+      <c r="G128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before reveal each sees only "Your vote: X". After reveal all votes show</t>
+        </is>
+      </c>
+      <c r="H128" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I128" s="1"/>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K128" s="5"/>
+      <c r="L128" s="5"/>
+      <c r="M128" s="5"/>
+      <c r="N128" s="5"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M14-09</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
+      <c r="B129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M14 Check-in, review and inbox</t>
         </is>
       </c>
-      <c r="C128" s="1" t="inlineStr">
+      <c r="C129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Inbox: read, filter, snooze, mute</t>
         </is>
       </c>
-      <c r="D128" s="1" t="inlineStr">
+      <c r="D129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E128" s="1" t="inlineStr">
+      <c r="E129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara has notifications (comment from M10-04)</t>
         </is>
       </c>
-      <c r="F128" s="1" t="inlineStr">
+      <c r="F129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Inbox, switch to "Unread"
 2. Click "Mark read"
@@ -10123,67 +10175,14 @@
 4. Click "Mute" on a group</t>
         </is>
       </c>
-      <c r="G128" s="1" t="inlineStr">
+      <c r="G129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Unread count drops. Snoozed item is quiet. Muted group stops notifying</t>
         </is>
       </c>
-      <c r="H128" s="1" t="inlineStr">
+      <c r="H129" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I128" s="1"/>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K128" s="5"/>
-      <c r="L128" s="5"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="5"/>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14-10</t>
-        </is>
-      </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14 Check-in, review and inbox</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A snooze never hides an obligation</t>
-        </is>
-      </c>
-      <c r="D129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya</t>
-        </is>
-      </c>
-      <c r="E129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya owes an acknowledgement</t>
-        </is>
-      </c>
-      <c r="F129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Snooze the related nudge in Inbox
-2. Open Review</t>
-        </is>
-      </c>
-      <c r="G129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The item is still on Review</t>
-        </is>
-      </c>
-      <c r="H129" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I129" s="1"/>
@@ -10200,7 +10199,7 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-11</t>
+          <t xml:space="preserve">M14-10</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
@@ -10210,40 +10209,36 @@
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal with no check-in turns Outdated</t>
+          <t xml:space="preserve">A snooze never hides an obligation</t>
         </is>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal past its check-in grace</t>
+          <t xml:space="preserve">Priya owes an acknowledgement</t>
         </is>
       </c>
       <c r="F130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Wait for the scheduler, or ask the operator to run pnpm cadence:sweep
-2. Open the work map</t>
+          <t xml:space="preserve">1. Snooze the related nudge in Inbox
+2. Open Review</t>
         </is>
       </c>
       <c r="G130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The goal shows "Outdated", overriding its last reported health</t>
+          <t xml:space="preserve">The item is still on Review</t>
         </is>
       </c>
       <c r="H130" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Needs time or server access</t>
-        </is>
-      </c>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I130" s="1"/>
       <c r="J130" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10255,81 +10250,86 @@
       <c r="N130" s="5"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14-11</t>
+        </is>
+      </c>
+      <c r="B131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal with no check-in turns Outdated</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal past its check-in grace</t>
+        </is>
+      </c>
+      <c r="F131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Wait for the scheduler, or ask the operator to run pnpm cadence:sweep
+2. Open the work map</t>
+        </is>
+      </c>
+      <c r="G131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The goal shows "Outdated", overriding its last reported health</t>
+        </is>
+      </c>
+      <c r="H131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I131" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs time or server access</t>
+        </is>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K131" s="5"/>
+      <c r="L131" s="5"/>
+      <c r="M131" s="5"/>
+      <c r="N131" s="5"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M15 Weekly session: Run the four-step weekly session the product facilitates. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="3"/>
-      <c r="I131" s="3"/>
-      <c r="J131" s="3"/>
-      <c r="K131" s="3"/>
-      <c r="L131" s="3"/>
-      <c r="M131" s="3"/>
-      <c r="N131" s="3"/>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M15-01</t>
-        </is>
-      </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M15 Weekly session</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The template session is listed</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M02-02 done</t>
-        </is>
-      </c>
-      <c r="F132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Sessions</t>
-        </is>
-      </c>
-      <c r="G132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Weekly session" under "Ahead" with chip "You facilitate" and action "Open"</t>
-        </is>
-      </c>
-      <c r="H132" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I132" s="1"/>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K132" s="5"/>
-      <c r="L132" s="5"/>
-      <c r="M132" s="5"/>
-      <c r="N132" s="5"/>
+      <c r="B132" s="3"/>
+      <c r="C132" s="3"/>
+      <c r="D132" s="3"/>
+      <c r="E132" s="3"/>
+      <c r="F132" s="3"/>
+      <c r="G132" s="3"/>
+      <c r="H132" s="3"/>
+      <c r="I132" s="3"/>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3"/>
+      <c r="N132" s="3"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-02</t>
+          <t xml:space="preserve">M15-01</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start the session</t>
+          <t xml:space="preserve">The template session is listed</t>
         </is>
       </c>
       <c r="D133" s="1" t="inlineStr">
@@ -10349,17 +10349,17 @@
       </c>
       <c r="E133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-01 done</t>
+          <t xml:space="preserve">M02-02 done</t>
         </is>
       </c>
       <c r="F133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open it and click "Start session"</t>
+          <t xml:space="preserve">1. Open Sessions</t>
         </is>
       </c>
       <c r="G133" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The steps rail shows "Confidence round", "Diagnose what is low", "Commitments", "Digest"</t>
+          <t xml:space="preserve">"Weekly session" under "Ahead" with chip "You facilitate" and action "Open"</t>
         </is>
       </c>
       <c r="H133" s="1" t="inlineStr">
@@ -10381,7 +10381,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-03</t>
+          <t xml:space="preserve">M15-02</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
@@ -10391,29 +10391,27 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confidence round: vote, reveal, confirm</t>
+          <t xml:space="preserve">Start the session</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, Priya, Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Session running</t>
+          <t xml:space="preserve">M15-01 done</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Priya and Sara open the session and click "Cast vote"
-2. Admin clicks "Continue to next step" before confirming
-3. Admin clicks "Reveal votes", writes "What changed this week", clicks "Confirm confidence"</t>
+          <t xml:space="preserve">1. Open it and click "Start session"</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voters see "Vote cast. Waiting for reveal." Early continue: "Cannot advance: &lt;KR&gt; has no confirmed confidence." After confirming, continue works</t>
+          <t xml:space="preserve">The steps rail shows "Confidence round", "Diagnose what is low", "Commitments", "Digest"</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
@@ -10421,11 +10419,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I134" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Space members join the session. Add Priya and Sara to the session's space first</t>
-        </is>
-      </c>
+      <c r="I134" s="1"/>
       <c r="J134" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10439,7 +10433,7 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-04</t>
+          <t xml:space="preserve">M15-03</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
@@ -10449,29 +10443,29 @@
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A low key result needs a blocker</t>
+          <t xml:space="preserve">Confidence round: vote, reveal, confirm</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, Priya, Sara</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One key result confirmed below 0.4</t>
+          <t xml:space="preserve">Session running</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On "Diagnose what is low" click "Continue to next step"
-2. Click "Raise a blocker" with empty fields
-3. Fill key result, kind Dependency, owner Mei, next action, and raise it</t>
+          <t xml:space="preserve">1. Priya and Sara open the session and click "Cast vote"
+2. Admin clicks "Continue to next step" before confirming
+3. Admin clicks "Reveal votes", writes "What changed this week", clicks "Confirm confidence"</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue: "Cannot advance: &lt;KR&gt; scored below 0.4 and has no blocker." Empty form shows field errors. The blocker shows "&lt;h&gt;h open"</t>
+          <t xml:space="preserve">Voters see "Vote cast. Waiting for reveal." Early continue: "Cannot advance: &lt;KR&gt; has no confirmed confidence." After confirming, continue works</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
@@ -10479,7 +10473,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I135" s="1"/>
+      <c r="I135" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Space members join the session. Add Priya and Sara to the session's space first</t>
+        </is>
+      </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10493,7 +10491,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-05</t>
+          <t xml:space="preserve">M15-04</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
@@ -10503,7 +10501,7 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve and reassign a blocker</t>
+          <t xml:space="preserve">A low key result needs a blocker</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
@@ -10513,24 +10511,24 @@
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-04 done</t>
+          <t xml:space="preserve">One key result confirmed below 0.4</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Use "Move it to" and "Reassign" to Sara
-2. Click "Resolve"
-3. Open the space page</t>
+          <t xml:space="preserve">1. On "Diagnose what is low" click "Continue to next step"
+2. Click "Raise a blocker" with empty fields
+3. Fill key result, kind Dependency, owner Mei, next action, and raise it</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner changes, then the chip says "resolved". Open blockers also appear on the space page while open</t>
+          <t xml:space="preserve">Continue: "Cannot advance: &lt;KR&gt; scored below 0.4 and has no blocker." Empty form shows field errors. The blocker shows "&lt;h&gt;h open"</t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I136" s="1"/>
@@ -10547,7 +10545,7 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-06</t>
+          <t xml:space="preserve">M15-05</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
@@ -10557,7 +10555,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least two commitments</t>
+          <t xml:space="preserve">Resolve and reassign a blocker</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
@@ -10567,23 +10565,24 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">On step Commitments</t>
+          <t xml:space="preserve">M15-04 done</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set one commitment and continue
-2. Add a second with "Add one more" and click "Set this week's commitments"</t>
+          <t xml:space="preserve">1. Use "Move it to" and "Reassign" to Sara
+2. Click "Resolve"
+3. Open the space page</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One: "Cannot advance: at least 2 commitments are required, but only 1 were set." Two: accepted</t>
+          <t xml:space="preserve">Owner changes, then the chip says "resolved". Open blockers also appear on the space page while open</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I137" s="1"/>
@@ -10600,7 +10599,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-07</t>
+          <t xml:space="preserve">M15-06</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
@@ -10610,7 +10609,7 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digest and close</t>
+          <t xml:space="preserve">At least two commitments</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -10620,19 +10619,18 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-06 done</t>
+          <t xml:space="preserve">On step Commitments</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Continue to "Digest"
-2. Click "Close session"
-3. Open Sessions, "Show finished"</t>
+          <t xml:space="preserve">1. Set one commitment and continue
+2. Add a second with "Add one more" and click "Set this week's commitments"</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The session is under "Finished"</t>
+          <t xml:space="preserve">One: "Cannot advance: at least 2 commitments are required, but only 1 were set." Two: accepted</t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
@@ -10652,81 +10650,83 @@
       <c r="N138" s="5"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15-07</t>
+        </is>
+      </c>
+      <c r="B139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15 Weekly session</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digest and close</t>
+        </is>
+      </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15-06 done</t>
+        </is>
+      </c>
+      <c r="F139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Continue to "Digest"
+2. Click "Close session"
+3. Open Sessions, "Show finished"</t>
+        </is>
+      </c>
+      <c r="G139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The session is under "Finished"</t>
+        </is>
+      </c>
+      <c r="H139" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I139" s="1"/>
+      <c r="J139" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K139" s="5"/>
+      <c r="L139" s="5"/>
+      <c r="M139" s="5"/>
+      <c r="N139" s="5"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M16 Agents and nudges: Check the two agents nudge, propose and stay quiet when they should. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B139" s="3"/>
-      <c r="C139" s="3"/>
-      <c r="D139" s="3"/>
-      <c r="E139" s="3"/>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
-      <c r="J139" s="3"/>
-      <c r="K139" s="3"/>
-      <c r="L139" s="3"/>
-      <c r="M139" s="3"/>
-      <c r="N139" s="3"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M16-01</t>
-        </is>
-      </c>
-      <c r="B140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M16 Agents and nudges</t>
-        </is>
-      </c>
-      <c r="C140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both agents are present with safe defaults</t>
-        </is>
-      </c>
-      <c r="D140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
-        </is>
-      </c>
-      <c r="G140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OKR Champion "On the hour", propose. OKR Coach "On every write", propose. Both "On". Chip "Deterministic only" with AI off</t>
-        </is>
-      </c>
-      <c r="H140" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I140" s="1"/>
-      <c r="J140" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K140" s="5"/>
-      <c r="L140" s="5"/>
-      <c r="M140" s="5"/>
-      <c r="N140" s="5"/>
+      <c r="B140" s="3"/>
+      <c r="C140" s="3"/>
+      <c r="D140" s="3"/>
+      <c r="E140" s="3"/>
+      <c r="F140" s="3"/>
+      <c r="G140" s="3"/>
+      <c r="H140" s="3"/>
+      <c r="I140" s="3"/>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3"/>
+      <c r="N140" s="3"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-02</t>
+          <t xml:space="preserve">M16-01</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run an agent now</t>
+          <t xml:space="preserve">Both agents are present with safe defaults</t>
         </is>
       </c>
       <c r="D141" s="1" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="F141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In "Run one now" click "Nudge queue", then "Daily sweep", then "Quality pass"</t>
+          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
         </is>
       </c>
       <c r="G141" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Each run appears under "Recent runs" as completed, with a log. A run with nothing to do says "Nothing was due."</t>
+          <t xml:space="preserve">OKR Champion "On the hour", propose. OKR Coach "On every write", propose. Both "On". Chip "Deterministic only" with AI off</t>
         </is>
       </c>
       <c r="H141" s="1" t="inlineStr">
@@ -10778,7 +10778,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-03</t>
+          <t xml:space="preserve">M16-02</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approve and dismiss proposals</t>
+          <t xml:space="preserve">Run an agent now</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -10798,18 +10798,17 @@
       </c>
       <c r="E142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Proposals waiting" has items (run the Coach after M09)</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tick one proposal, click "Apply 1"
-2. Tick another, click "Dismiss"</t>
+          <t xml:space="preserve">1. In "Run one now" click "Nudge queue", then "Daily sweep", then "Quality pass"</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Applied 1 of 1." and "Dismissed 1." The applied change is visible on the goal</t>
+          <t xml:space="preserve">Each run appears under "Recent runs" as completed, with a log. A run with nothing to do says "Nothing was due."</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
@@ -10817,11 +10816,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I142" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Members see proposals on Review with a link to Admin, Agents, which they cannot open. Record what a member sees</t>
-        </is>
-      </c>
+      <c r="I142" s="1"/>
       <c r="J142" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10835,7 +10830,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-04</t>
+          <t xml:space="preserve">M16-03</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
@@ -10845,7 +10840,7 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbox commits nothing</t>
+          <t xml:space="preserve">Approve and dismiss proposals</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -10855,27 +10850,30 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">"Proposals waiting" has items (run the Coach after M09)</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set the Coach "Write policy" to "Sandbox"
-2. Run "Quality pass"
-3. Set it back to "Propose"</t>
+          <t xml:space="preserve">1. Tick one proposal, click "Apply 1"
+2. Tick another, click "Dismiss"</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The run is logged. No proposal and no change is written</t>
+          <t xml:space="preserve">"Applied 1 of 1." and "Dismissed 1." The applied change is visible on the goal</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I143" s="1"/>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I143" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Members see proposals on Review with a link to Admin, Agents, which they cannot open. Record what a member sees</t>
+        </is>
+      </c>
       <c r="J143" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10889,7 +10887,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-05</t>
+          <t xml:space="preserve">M16-04</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
@@ -10899,7 +10897,7 @@
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct writes ask for confirmation</t>
+          <t xml:space="preserve">Sandbox commits nothing</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -10914,13 +10912,14 @@
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Scoped direct" on the Champion
-2. Cancel the dialog</t>
+          <t xml:space="preserve">1. Set the Coach "Write policy" to "Sandbox"
+2. Run "Quality pass"
+3. Set it back to "Propose"</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dialog "Let OKR Champion write directly?". After cancel the policy is still propose</t>
+          <t xml:space="preserve">The run is logged. No proposal and no change is written</t>
         </is>
       </c>
       <c r="H144" s="1" t="inlineStr">
@@ -10942,7 +10941,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-06</t>
+          <t xml:space="preserve">M16-05</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
@@ -10952,7 +10951,7 @@
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn an agent off and on</t>
+          <t xml:space="preserve">Direct writes ask for confirmation</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -10967,13 +10966,13 @@
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Turn off" on the Coach and confirm
-2. Click "Turn on"</t>
+          <t xml:space="preserve">1. Click "Scoped direct" on the Champion
+2. Cancel the dialog</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chip switches to "Off" and back to "On"</t>
+          <t xml:space="preserve">Dialog "Let OKR Champion write directly?". After cancel the policy is still propose</t>
         </is>
       </c>
       <c r="H145" s="1" t="inlineStr">
@@ -10995,7 +10994,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-07</t>
+          <t xml:space="preserve">M16-06</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
@@ -11005,33 +11004,33 @@
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A nudge reaches the member</t>
+          <t xml:space="preserve">Turn an agent off and on</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara owes a check-in</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Admin runs "Nudge queue"
-2. Sara opens Inbox</t>
+          <t xml:space="preserve">1. Click "Turn off" on the Coach and confirm
+2. Click "Turn on"</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A reminder line "Reminder: &lt;rule&gt;" is in Sara's Inbox</t>
+          <t xml:space="preserve">The chip switches to "Off" and back to "On"</t>
         </is>
       </c>
       <c r="H146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I146" s="1"/>
@@ -11048,7 +11047,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-08</t>
+          <t xml:space="preserve">M16-07</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
@@ -11058,28 +11057,28 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One nudge per subject per day</t>
+          <t xml:space="preserve">A nudge reaches the member</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-07 done</t>
+          <t xml:space="preserve">Sara owes a check-in</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Run "Nudge queue" again
-2. Open Admin, Nudge volume</t>
+          <t xml:space="preserve">1. Admin runs "Nudge queue"
+2. Sara opens Inbox</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara gets no second copy. "Why it stayed quiet" counts "Already said today"</t>
+          <t xml:space="preserve">A reminder line "Reminder: &lt;rule&gt;" is in Sara's Inbox</t>
         </is>
       </c>
       <c r="H147" s="1" t="inlineStr">
@@ -11101,7 +11100,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-09</t>
+          <t xml:space="preserve">M16-08</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
@@ -11111,29 +11110,28 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quiet hours hold nudges</t>
+          <t xml:space="preserve">One nudge per subject per day</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara, then Admin</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">M16-07 done</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sara sets "Quiet hours" to cover the current time on Account, Where to reach you, and saves
-2. Admin runs "Nudge queue"
-3. Admin opens Nudge volume</t>
+          <t xml:space="preserve">1. Run "Nudge queue" again
+2. Open Admin, Nudge volume</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No new nudge for Sara. The reason "Quiet hours" is counted</t>
+          <t xml:space="preserve">Sara gets no second copy. "Why it stayed quiet" counts "Already said today"</t>
         </is>
       </c>
       <c r="H148" s="1" t="inlineStr">
@@ -11155,7 +11153,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-10</t>
+          <t xml:space="preserve">M16-09</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
@@ -11165,12 +11163,12 @@
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn a nudge rule off</t>
+          <t xml:space="preserve">Quiet hours hold nudges</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara, then Admin</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -11180,19 +11178,19 @@
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Nudge volume, "Rules (n)"
-2. Click "Turn off" on a rule
-3. Run "Nudge queue"</t>
+          <t xml:space="preserve">1. Sara sets "Quiet hours" to cover the current time on Account, Where to reach you, and saves
+2. Admin runs "Nudge queue"
+3. Admin opens Nudge volume</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The rule shows as changed. Its nudges are held with "Rule switched off"</t>
+          <t xml:space="preserve">No new nudge for Sara. The reason "Quiet hours" is counted</t>
         </is>
       </c>
       <c r="H149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I149" s="1"/>
@@ -11209,7 +11207,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-11</t>
+          <t xml:space="preserve">M16-10</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
@@ -11219,27 +11217,29 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Coach strip on a goal</t>
+          <t xml:space="preserve">Turn a nudge rule off</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M09 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Sara's goal</t>
+          <t xml:space="preserve">1. Open Admin, Nudge volume, "Rules (n)"
+2. Click "Turn off" on a rule
+3. Run "Nudge queue"</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"What the Coach sees" lists the rules the goal still breaks</t>
+          <t xml:space="preserve">The rule shows as changed. Its nudges are held with "Rule switched off"</t>
         </is>
       </c>
       <c r="H150" s="1" t="inlineStr">
@@ -11259,115 +11259,113 @@
       <c r="N150" s="5"/>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16-11</t>
+        </is>
+      </c>
+      <c r="B151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16 Agents and nudges</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Coach strip on a goal</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M09 done</t>
+        </is>
+      </c>
+      <c r="F151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Sara's goal</t>
+        </is>
+      </c>
+      <c r="G151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"What the Coach sees" lists the rules the goal still breaks</t>
+        </is>
+      </c>
+      <c r="H151" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I151" s="1"/>
+      <c r="J151" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K151" s="5"/>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5"/>
+      <c r="N151" s="5"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M17 Work map, search and activity: Check the overview screens, search and basic usability. Needs M15 first. About 20 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B151" s="3"/>
-      <c r="C151" s="3"/>
-      <c r="D151" s="3"/>
-      <c r="E151" s="3"/>
-      <c r="F151" s="3"/>
-      <c r="G151" s="3"/>
-      <c r="H151" s="3"/>
-      <c r="I151" s="3"/>
-      <c r="J151" s="3"/>
-      <c r="K151" s="3"/>
-      <c r="L151" s="3"/>
-      <c r="M151" s="3"/>
-      <c r="N151" s="3"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="1" t="inlineStr">
+      <c r="B152" s="3"/>
+      <c r="C152" s="3"/>
+      <c r="D152" s="3"/>
+      <c r="E152" s="3"/>
+      <c r="F152" s="3"/>
+      <c r="G152" s="3"/>
+      <c r="H152" s="3"/>
+      <c r="I152" s="3"/>
+      <c r="J152" s="3"/>
+      <c r="K152" s="3"/>
+      <c r="L152" s="3"/>
+      <c r="M152" s="3"/>
+      <c r="N152" s="3"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M17-01</t>
         </is>
       </c>
-      <c r="B152" s="1" t="inlineStr">
+      <c r="B153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M17 Work map, search and activity</t>
         </is>
       </c>
-      <c r="C152" s="1" t="inlineStr">
+      <c r="C153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Work map context strip and table</t>
         </is>
       </c>
-      <c r="D152" s="1" t="inlineStr">
+      <c r="D153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Priya</t>
         </is>
       </c>
-      <c r="E152" s="1" t="inlineStr">
+      <c r="E153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M11 done</t>
         </is>
       </c>
-      <c r="F152" s="1" t="inlineStr">
+      <c r="F153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the work map
 2. Switch the scope tabs Company and each space
 3. Click a row, then "Open the goal"</t>
         </is>
       </c>
-      <c r="G152" s="1" t="inlineStr">
+      <c r="G153" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Strip shows "Phase n" and the gate status. Columns Goal, Health, Confidence, Progress, Next step, Champion. The row panel opens the goal</t>
-        </is>
-      </c>
-      <c r="H152" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I152" s="1"/>
-      <c r="J152" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K152" s="5"/>
-      <c r="L152" s="5"/>
-      <c r="M152" s="5"/>
-      <c r="N152" s="5"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M17-02</t>
-        </is>
-      </c>
-      <c r="B153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M17 Work map, search and activity</t>
-        </is>
-      </c>
-      <c r="C153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Search finds only what you may open</t>
-        </is>
-      </c>
-      <c r="D153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jonas</t>
-        </is>
-      </c>
-      <c r="E153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M10 done</t>
-        </is>
-      </c>
-      <c r="F153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Search, type onboarding
-2. Switch the type tabs
-3. Type zzzz</t>
-        </is>
-      </c>
-      <c r="G153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Results group by type. zzzz shows "Nothing matches". Sara's draft document never appears</t>
         </is>
       </c>
       <c r="H153" s="1" t="inlineStr">
@@ -11389,7 +11387,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-03</t>
+          <t xml:space="preserve">M17-02</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
@@ -11399,33 +11397,34 @@
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Activity feed</t>
+          <t xml:space="preserve">Search finds only what you may open</t>
         </is>
       </c>
       <c r="D154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work done in earlier modules</t>
+          <t xml:space="preserve">M10 done</t>
         </is>
       </c>
       <c r="F154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Activity
-2. Click "Older" then "Back to the newest"</t>
+          <t xml:space="preserve">1. Open Search, type onboarding
+2. Switch the type tabs
+3. Type zzzz</t>
         </is>
       </c>
       <c r="G154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check-ins, goals, sessions and setting changes are listed newest first</t>
+          <t xml:space="preserve">Results group by type. zzzz shows "Nothing matches". Sara's draft document never appears</t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I154" s="1"/>
@@ -11442,7 +11441,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-04</t>
+          <t xml:space="preserve">M17-03</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
@@ -11452,28 +11451,28 @@
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot with AI off</t>
+          <t xml:space="preserve">Activity feed</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No AI provider</t>
+          <t xml:space="preserve">Work done in earlier modules</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Ask the copilot" (or Ctrl+J)
-2. Ask: which key results are at risk</t>
+          <t xml:space="preserve">1. Open Activity
+2. Click "Older" then "Back to the newest"</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chip "AI off". Only "Passages that match" is shown. No error</t>
+          <t xml:space="preserve">Check-ins, goals, sessions and setting changes are listed newest first</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
@@ -11495,7 +11494,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-05</t>
+          <t xml:space="preserve">M17-04</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
@@ -11505,7 +11504,7 @@
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyboard-only check-in</t>
+          <t xml:space="preserve">Copilot with AI off</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
@@ -11515,17 +11514,18 @@
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal is due</t>
+          <t xml:space="preserve">No AI provider</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Using only Tab, Shift+Tab, Enter and arrows, post a check-in</t>
+          <t xml:space="preserve">1. Click "Ask the copilot" (or Ctrl+J)
+2. Ask: which key results are at risk</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every control is reachable and the focus is visible</t>
+          <t xml:space="preserve">Chip "AI off". Only "Passages that match" is shown. No error</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
@@ -11547,7 +11547,7 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-06</t>
+          <t xml:space="preserve">M17-05</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone-width layout</t>
+          <t xml:space="preserve">Keyboard-only check-in</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
@@ -11567,17 +11567,17 @@
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">A goal is due</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the work map, Check in and Board on a phone or a 375px-wide window</t>
+          <t xml:space="preserve">1. Using only Tab, Shift+Tab, Enter and arrows, post a check-in</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No sideways page scroll. Every button can be tapped</t>
+          <t xml:space="preserve">Every control is reachable and the focus is visible</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
@@ -11597,113 +11597,112 @@
       <c r="N157" s="5"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M17-06</t>
+        </is>
+      </c>
+      <c r="B158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M17 Work map, search and activity</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone-width layout</t>
+        </is>
+      </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the work map, Check in and Board on a phone or a 375px-wide window</t>
+        </is>
+      </c>
+      <c r="G158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No sideways page scroll. Every button can be tapped</t>
+        </is>
+      </c>
+      <c r="H158" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I158" s="1"/>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K158" s="5"/>
+      <c r="L158" s="5"/>
+      <c r="M158" s="5"/>
+      <c r="N158" s="5"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard: Close goals and the quarter, and record the result. Needs M15 first. About 25 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B158" s="3"/>
-      <c r="C158" s="3"/>
-      <c r="D158" s="3"/>
-      <c r="E158" s="3"/>
-      <c r="F158" s="3"/>
-      <c r="G158" s="3"/>
-      <c r="H158" s="3"/>
-      <c r="I158" s="3"/>
-      <c r="J158" s="3"/>
-      <c r="K158" s="3"/>
-      <c r="L158" s="3"/>
-      <c r="M158" s="3"/>
-      <c r="N158" s="3"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="1" t="inlineStr">
+      <c r="B159" s="3"/>
+      <c r="C159" s="3"/>
+      <c r="D159" s="3"/>
+      <c r="E159" s="3"/>
+      <c r="F159" s="3"/>
+      <c r="G159" s="3"/>
+      <c r="H159" s="3"/>
+      <c r="I159" s="3"/>
+      <c r="J159" s="3"/>
+      <c r="K159" s="3"/>
+      <c r="L159" s="3"/>
+      <c r="M159" s="3"/>
+      <c r="N159" s="3"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18-01</t>
         </is>
       </c>
-      <c r="B159" s="1" t="inlineStr">
+      <c r="B160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
         </is>
       </c>
-      <c r="C159" s="1" t="inlineStr">
+      <c r="C160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Closing a goal needs a retrospective</t>
         </is>
       </c>
-      <c r="D159" s="1" t="inlineStr">
+      <c r="D160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E159" s="1" t="inlineStr">
+      <c r="E160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A published goal</t>
         </is>
       </c>
-      <c r="F159" s="1" t="inlineStr">
+      <c r="F160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the goal, pick "Achieved" and "Keep"
 2. Leave the retrospective empty and click "Close this goal"</t>
         </is>
       </c>
-      <c r="G159" s="1" t="inlineStr">
+      <c r="G160" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Closing a goal needs a retrospective. What happened, and what would you do differently?"</t>
-        </is>
-      </c>
-      <c r="H159" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I159" s="1"/>
-      <c r="J159" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K159" s="5"/>
-      <c r="L159" s="5"/>
-      <c r="M159" s="5"/>
-      <c r="N159" s="5"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-02</t>
-        </is>
-      </c>
-      <c r="B160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
-        </is>
-      </c>
-      <c r="C160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Close and reopen a goal</t>
-        </is>
-      </c>
-      <c r="D160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara</t>
-        </is>
-      </c>
-      <c r="E160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-01 done</t>
-        </is>
-      </c>
-      <c r="F160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Write the retrospective and close
-2. Click "Reopen this goal"</t>
-        </is>
-      </c>
-      <c r="G160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Header shows "closed · achieved" and "No check-in is due. A closed goal never is." Reopen returns it to open</t>
         </is>
       </c>
       <c r="H160" s="1" t="inlineStr">
@@ -11725,7 +11724,7 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M18-03</t>
+          <t xml:space="preserve">M18-02</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
@@ -11735,29 +11734,28 @@
       </c>
       <c r="C161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 7 Review and learn, and close the cycle</t>
+          <t xml:space="preserve">Close and reopen a goal</t>
         </is>
       </c>
       <c r="D161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A quarterly review of the current cycle is running</t>
+          <t xml:space="preserve">M18-01 done</t>
         </is>
       </c>
       <c r="F161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 7, before any key result is scored
-2. Score every key result and write the team retro in the quarterly review, then close the review
-3. Back on phase 7, click "Close &lt;cycle name&gt;"</t>
+          <t xml:space="preserve">1. Write the retrospective and close
+2. Click "Reopen this goal"</t>
         </is>
       </c>
       <c r="G161" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before scoring, "Close the cycle" is disabled and lists what phase 7 still needs. After scoring, the portfolio average and bands show and phase 7 shows done. After closing, the chip reads "closed" and "How this cycle closed" shows the result and verdict, and says the next cycle receives the inheritance when it is created</t>
+          <t xml:space="preserve">Header shows "closed · achieved" and "No check-in is due. A closed goal never is." Reopen returns it to open</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
@@ -11779,30 +11777,84 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M18-03</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase 7 Review and learn, and close the cycle</t>
+        </is>
+      </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A quarterly review of the current cycle is running</t>
+        </is>
+      </c>
+      <c r="F162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Cycle, phase 7, before any key result is scored
+2. Score every key result and write the team retro in the quarterly review, then close the review
+3. Back on phase 7, click "Close &lt;cycle name&gt;"</t>
+        </is>
+      </c>
+      <c r="G162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before scoring, "Close the cycle" is disabled and lists what phase 7 still needs. After scoring, the portfolio average and bands show and phase 7 shows done. After closing, the chip reads "closed" and "How this cycle closed" shows the result and verdict, and says the next cycle receives the inheritance when it is created</t>
+        </is>
+      </c>
+      <c r="H162" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I162" s="1"/>
+      <c r="J162" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K162" s="5"/>
+      <c r="L162" s="5"/>
+      <c r="M162" s="5"/>
+      <c r="N162" s="5"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M18-04</t>
         </is>
       </c>
-      <c r="B162" s="1" t="inlineStr">
+      <c r="B163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
         </is>
       </c>
-      <c r="C162" s="1" t="inlineStr">
+      <c r="C163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The closed cycle on the scorecard and in the next quarter</t>
         </is>
       </c>
-      <c r="D162" s="1" t="inlineStr">
+      <c r="D163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E162" s="1" t="inlineStr">
+      <c r="E163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18-03 done</t>
         </is>
       </c>
-      <c r="F162" s="1" t="inlineStr">
+      <c r="F163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Scorecard
 2. Check "Close a cycle out" no longer offers the closed cycle
@@ -11811,61 +11863,9 @@
 5. Click "Export as CSV" on the scorecard</t>
         </is>
       </c>
-      <c r="G162" s="1" t="inlineStr">
+      <c r="G163" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The closed cycle's row shows result and verdict. Phase 2 lists every prior score and each carried item at impact 4. Phase 3 lists the lowest process-health statement as a priority, not as an issue. The CSV downloads and opens</t>
-        </is>
-      </c>
-      <c r="H162" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I162" s="1"/>
-      <c r="J162" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K162" s="5"/>
-      <c r="L162" s="5"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="5"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-05</t>
-        </is>
-      </c>
-      <c r="B163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
-        </is>
-      </c>
-      <c r="C163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Archive the old cycle</t>
-        </is>
-      </c>
-      <c r="D163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-04 done</t>
-        </is>
-      </c>
-      <c r="F163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On the Cycles card click "Archive &lt;name&gt;"</t>
-        </is>
-      </c>
-      <c r="G163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The cycle is archived and the next one becomes current</t>
         </is>
       </c>
       <c r="H163" s="1" t="inlineStr">
@@ -11887,7 +11887,7 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M18-06</t>
+          <t xml:space="preserve">M18-05</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="C164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run a quarterly review session</t>
+          <t xml:space="preserve">Archive the old cycle</t>
         </is>
       </c>
       <c r="D164" s="1" t="inlineStr">
@@ -11907,17 +11907,17 @@
       </c>
       <c r="E164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">End of cycle</t>
+          <t xml:space="preserve">M18-04 done</t>
         </is>
       </c>
       <c r="F164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Look on Sessions and on the space page for a way to schedule a quarterly review</t>
+          <t xml:space="preserve">1. On the Cycles card click "Archive &lt;name&gt;"</t>
         </is>
       </c>
       <c r="G164" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A quarterly review with 11 stages can be scheduled and run, then "The minutes" can be downloaded as Markdown and PDF</t>
+          <t xml:space="preserve">The cycle is archived and the next one becomes current</t>
         </is>
       </c>
       <c r="H164" s="1" t="inlineStr">
@@ -11925,11 +11925,7 @@
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code review found no UI to create a session. If there is none, mark Blocked and log it</t>
-        </is>
-      </c>
+      <c r="I164" s="1"/>
       <c r="J164" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -11941,124 +11937,128 @@
       <c r="N164" s="5"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18-06</t>
+        </is>
+      </c>
+      <c r="B165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run a quarterly review session</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End of cycle</t>
+        </is>
+      </c>
+      <c r="F165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Look on Sessions and on the space page for a way to schedule a quarterly review</t>
+        </is>
+      </c>
+      <c r="G165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A quarterly review with 11 stages can be scheduled and run, then "The minutes" can be downloaded as Markdown and PDF</t>
+        </is>
+      </c>
+      <c r="H165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I165" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code review found no UI to create a session. If there is none, mark Blocked and log it</t>
+        </is>
+      </c>
+      <c r="J165" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K165" s="5"/>
+      <c r="L165" s="5"/>
+      <c r="M165" s="5"/>
+      <c r="N165" s="5"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M19 Access and permissions: Check nobody sees or does more than their access allows. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B165" s="3"/>
-      <c r="C165" s="3"/>
-      <c r="D165" s="3"/>
-      <c r="E165" s="3"/>
-      <c r="F165" s="3"/>
-      <c r="G165" s="3"/>
-      <c r="H165" s="3"/>
-      <c r="I165" s="3"/>
-      <c r="J165" s="3"/>
-      <c r="K165" s="3"/>
-      <c r="L165" s="3"/>
-      <c r="M165" s="3"/>
-      <c r="N165" s="3"/>
-    </row>
-    <row r="166">
-      <c r="A166" s="1" t="inlineStr">
+      <c r="B166" s="3"/>
+      <c r="C166" s="3"/>
+      <c r="D166" s="3"/>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3"/>
+      <c r="G166" s="3"/>
+      <c r="H166" s="3"/>
+      <c r="I166" s="3"/>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="3"/>
+      <c r="N166" s="3"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M19-01</t>
         </is>
       </c>
-      <c r="B166" s="1" t="inlineStr">
+      <c r="B167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M19 Access and permissions</t>
         </is>
       </c>
-      <c r="C166" s="1" t="inlineStr">
+      <c r="C167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A member cannot open admin screens</t>
         </is>
       </c>
-      <c r="D166" s="1" t="inlineStr">
+      <c r="D167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas</t>
         </is>
       </c>
-      <c r="E166" s="1" t="inlineStr">
+      <c r="E167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F166" s="1" t="inlineStr">
+      <c r="F167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open /admin/general
 2. Open /admin/agents</t>
         </is>
       </c>
-      <c r="G166" s="1" t="inlineStr">
+      <c r="G167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Both return a Not Found page. No admin data is shown</t>
         </is>
       </c>
-      <c r="H166" s="1" t="inlineStr">
+      <c r="H167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I166" s="1" t="inlineStr">
+      <c r="I167" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The product answers 404 on purpose, so the page's existence is not revealed</t>
         </is>
       </c>
-      <c r="J166" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K166" s="5"/>
-      <c r="L166" s="5"/>
-      <c r="M166" s="5"/>
-      <c r="N166" s="5"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M19-02</t>
-        </is>
-      </c>
-      <c r="B167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M19 Access and permissions</t>
-        </is>
-      </c>
-      <c r="C167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signed-out visitors are sent to sign-in</t>
-        </is>
-      </c>
-      <c r="D167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nobody (signed out)</t>
-        </is>
-      </c>
-      <c r="E167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open /goals and /kpis</t>
-        </is>
-      </c>
-      <c r="G167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Redirected to /sign-in</t>
-        </is>
-      </c>
-      <c r="H167" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I167" s="1"/>
       <c r="J167" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12072,7 +12072,7 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-03</t>
+          <t xml:space="preserve">M19-02</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
@@ -12082,27 +12082,27 @@
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal you cannot see reads as not found</t>
+          <t xml:space="preserve">Signed-out visitors are sent to sign-in</t>
         </is>
       </c>
       <c r="D168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Nobody (signed out)</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The URL of a goal Jonas has no access to, or a made-up id</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open /goals/&lt;id&gt;</t>
+          <t xml:space="preserve">1. Open /goals and /kpis</t>
         </is>
       </c>
       <c r="G168" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"We could not find that, or it is not yours to see."</t>
+          <t xml:space="preserve">Redirected to /sign-in</t>
         </is>
       </c>
       <c r="H168" s="1" t="inlineStr">
@@ -12124,7 +12124,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-04</t>
+          <t xml:space="preserve">M19-03</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
@@ -12134,33 +12134,32 @@
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert a member to a guest</t>
+          <t xml:space="preserve">A goal you cannot see reads as not found</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Amara</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">The URL of a goal Jonas has no access to, or a made-up id</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Amara's profile click "Convert to a guest"
-2. As Amara browse the work map, Goals and Spaces</t>
+          <t xml:space="preserve">1. Open /goals/&lt;id&gt;</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amara shows the badge "Guest" and sees less than before. Write down what Amara can still see</t>
+          <t xml:space="preserve">"We could not find that, or it is not yours to see."</t>
         </is>
       </c>
       <c r="H169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I169" s="1"/>
@@ -12177,7 +12176,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-05</t>
+          <t xml:space="preserve">M19-04</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
@@ -12187,29 +12186,28 @@
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erase a member</t>
+          <t xml:space="preserve">Convert a member to a guest</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, then Amara</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Leaver from M04-02</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On their profile click "Erase this member"
-2. Type their name to confirm
-3. Click "Download the erasure export"</t>
+          <t xml:space="preserve">1. On Amara's profile click "Convert to a guest"
+2. As Amara browse the work map, Goals and Spaces</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The member is erased and the export downloads</t>
+          <t xml:space="preserve">Amara shows the badge "Guest" and sees less than before. Write down what Amara can still see</t>
         </is>
       </c>
       <c r="H170" s="1" t="inlineStr">
@@ -12217,11 +12215,7 @@
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I170" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Irreversible. Never use one of the seven personas</t>
-        </is>
-      </c>
+      <c r="I170" s="1"/>
       <c r="J170" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12233,125 +12227,131 @@
       <c r="N170" s="5"/>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M19-05</t>
+        </is>
+      </c>
+      <c r="B171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M19 Access and permissions</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erase a member</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Leaver from M04-02</t>
+        </is>
+      </c>
+      <c r="F171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On their profile click "Erase this member"
+2. Type their name to confirm
+3. Click "Download the erasure export"</t>
+        </is>
+      </c>
+      <c r="G171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The member is erased and the export downloads</t>
+        </is>
+      </c>
+      <c r="H171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I171" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irreversible. Never use one of the seven personas</t>
+        </is>
+      </c>
+      <c r="J171" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K171" s="5"/>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M20 AI provider and copilot: Turn AI on and check it drafts while a person decides. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B171" s="3"/>
-      <c r="C171" s="3"/>
-      <c r="D171" s="3"/>
-      <c r="E171" s="3"/>
-      <c r="F171" s="3"/>
-      <c r="G171" s="3"/>
-      <c r="H171" s="3"/>
-      <c r="I171" s="3"/>
-      <c r="J171" s="3"/>
-      <c r="K171" s="3"/>
-      <c r="L171" s="3"/>
-      <c r="M171" s="3"/>
-      <c r="N171" s="3"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="1" t="inlineStr">
+      <c r="B172" s="3"/>
+      <c r="C172" s="3"/>
+      <c r="D172" s="3"/>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3"/>
+      <c r="G172" s="3"/>
+      <c r="H172" s="3"/>
+      <c r="I172" s="3"/>
+      <c r="J172" s="3"/>
+      <c r="K172" s="3"/>
+      <c r="L172" s="3"/>
+      <c r="M172" s="3"/>
+      <c r="N172" s="3"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M20-01</t>
         </is>
       </c>
-      <c r="B172" s="1" t="inlineStr">
+      <c r="B173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M20 AI provider and copilot</t>
         </is>
       </c>
-      <c r="C172" s="1" t="inlineStr">
+      <c r="C173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connect an AI provider</t>
         </is>
       </c>
-      <c r="D172" s="1" t="inlineStr">
+      <c r="D173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E172" s="1" t="inlineStr">
+      <c r="E173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An API key from Anthropic, OpenAI, Google, OpenRouter, or a local Ollama</t>
         </is>
       </c>
-      <c r="F172" s="1" t="inlineStr">
+      <c r="F173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, AI
 2. On the provider card tick "Use this provider" and click "Save"
 3. Paste the key and click "Store"</t>
         </is>
       </c>
-      <c r="G172" s="1" t="inlineStr">
+      <c r="G173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Key chip shows "verified". The header counts 1 configured</t>
         </is>
       </c>
-      <c r="H172" s="1" t="inlineStr">
+      <c r="H173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I172" s="1" t="inlineStr">
+      <c r="I173" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Use a key with a small spend limit. Never paste the key into the spreadsheet</t>
         </is>
       </c>
-      <c r="J172" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K172" s="5"/>
-      <c r="L172" s="5"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="5"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M20-02</t>
-        </is>
-      </c>
-      <c r="B173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M20 AI provider and copilot</t>
-        </is>
-      </c>
-      <c r="C173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A bad key is marked invalid</t>
-        </is>
-      </c>
-      <c r="D173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Click "Replace" and store a wrong key</t>
-        </is>
-      </c>
-      <c r="G173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Key chip shows "invalid"</t>
-        </is>
-      </c>
-      <c r="H173" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I173" s="1"/>
       <c r="J173" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12365,7 +12365,7 @@
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-03</t>
+          <t xml:space="preserve">M20-02</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
@@ -12375,33 +12375,32 @@
       </c>
       <c r="C174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI buttons appear when AI is on</t>
+          <t xml:space="preserve">A bad key is marked invalid</t>
         </is>
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 4
-2. Open a goal</t>
+          <t xml:space="preserve">1. Click "Replace" and store a wrong key</t>
         </is>
       </c>
       <c r="G174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Draft from an ambition", "Suggest a parent", "Suggest numbers" and "Suggest a fix" are visible</t>
+          <t xml:space="preserve">Key chip shows "invalid"</t>
         </is>
       </c>
       <c r="H174" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I174" s="1"/>
@@ -12418,7 +12417,7 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-04</t>
+          <t xml:space="preserve">M20-03</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
@@ -12428,7 +12427,7 @@
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI drafts, a person decides</t>
+          <t xml:space="preserve">AI buttons appear when AI is on</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
@@ -12438,19 +12437,18 @@
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-03 done</t>
+          <t xml:space="preserve">M20-01 done</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Draft from an ambition" and give one sentence
-2. Read the result without accepting it
-3. Reload</t>
+          <t xml:space="preserve">1. Open Cycle, phase 4
+2. Open a goal</t>
         </is>
       </c>
       <c r="G175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A draft is proposed. Nothing is saved until accepted</t>
+          <t xml:space="preserve">"Draft from an ambition", "Suggest a parent", "Suggest numbers" and "Suggest a fix" are visible</t>
         </is>
       </c>
       <c r="H175" s="1" t="inlineStr">
@@ -12472,7 +12470,7 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-05</t>
+          <t xml:space="preserve">M20-04</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
@@ -12482,7 +12480,7 @@
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot answers with sources</t>
+          <t xml:space="preserve">AI drafts, a person decides</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
@@ -12492,17 +12490,19 @@
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">M20-03 done</t>
         </is>
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the copilot and ask: which key results are at risk this cycle</t>
+          <t xml:space="preserve">1. Click "Draft from an ambition" and give one sentence
+2. Read the result without accepting it
+3. Reload</t>
         </is>
       </c>
       <c r="G176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A streamed answer with "Sources". Any change is shown as "Proposed change" with "Undo"</t>
+          <t xml:space="preserve">A draft is proposed. Nothing is saved until accepted</t>
         </is>
       </c>
       <c r="H176" s="1" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-06</t>
+          <t xml:space="preserve">M20-05</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
@@ -12534,27 +12534,27 @@
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot does not leak private items</t>
+          <t xml:space="preserve">Copilot answers with sources</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara has a draft document</t>
+          <t xml:space="preserve">M20-01 done</t>
         </is>
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Ask the copilot about Sara's draft document</t>
+          <t xml:space="preserve">1. Open the copilot and ask: which key results are at risk this cycle</t>
         </is>
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The answer does not show its content</t>
+          <t xml:space="preserve">A streamed answer with "Sources". Any change is shown as "Proposed change" with "Undo"</t>
         </is>
       </c>
       <c r="H177" s="1" t="inlineStr">
@@ -12576,7 +12576,7 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-07</t>
+          <t xml:space="preserve">M20-06</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agents draft with AI on</t>
+          <t xml:space="preserve">Copilot does not leak private items</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">Sara has a draft document</t>
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
+          <t xml:space="preserve">1. Ask the copilot about Sara's draft document</t>
         </is>
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chip shows "Drafting on"</t>
+          <t xml:space="preserve">The answer does not show its content</t>
         </is>
       </c>
       <c r="H178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I178" s="1"/>
@@ -12628,7 +12628,7 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-08</t>
+          <t xml:space="preserve">M20-07</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removing the key returns to deterministic mode</t>
+          <t xml:space="preserve">Agents draft with AI on</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
@@ -12653,18 +12653,17 @@
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Remove the key"
-2. Draft an objective with bad wording</t>
+          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
         </is>
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI buttons disappear. Quality checks still fire</t>
+          <t xml:space="preserve">Chip shows "Drafting on"</t>
         </is>
       </c>
       <c r="H179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I179" s="1"/>
@@ -12679,128 +12678,123 @@
       <c r="N179" s="5"/>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="A180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20-08</t>
+        </is>
+      </c>
+      <c r="B180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20 AI provider and copilot</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removing the key returns to deterministic mode</t>
+        </is>
+      </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20-01 done</t>
+        </is>
+      </c>
+      <c r="F180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click "Remove the key"
+2. Draft an objective with bad wording</t>
+        </is>
+      </c>
+      <c r="G180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI buttons disappear. Quality checks still fire</t>
+        </is>
+      </c>
+      <c r="H180" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I180" s="1"/>
+      <c r="J180" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K180" s="5"/>
+      <c r="L180" s="5"/>
+      <c r="M180" s="5"/>
+      <c r="N180" s="5"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email: Deliver mail and chat messages to real inboxes and apps. Needs M16 first. About 60 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B180" s="3"/>
-      <c r="C180" s="3"/>
-      <c r="D180" s="3"/>
-      <c r="E180" s="3"/>
-      <c r="F180" s="3"/>
-      <c r="G180" s="3"/>
-      <c r="H180" s="3"/>
-      <c r="I180" s="3"/>
-      <c r="J180" s="3"/>
-      <c r="K180" s="3"/>
-      <c r="L180" s="3"/>
-      <c r="M180" s="3"/>
-      <c r="N180" s="3"/>
-    </row>
-    <row r="181">
-      <c r="A181" s="1" t="inlineStr">
+      <c r="B181" s="3"/>
+      <c r="C181" s="3"/>
+      <c r="D181" s="3"/>
+      <c r="E181" s="3"/>
+      <c r="F181" s="3"/>
+      <c r="G181" s="3"/>
+      <c r="H181" s="3"/>
+      <c r="I181" s="3"/>
+      <c r="J181" s="3"/>
+      <c r="K181" s="3"/>
+      <c r="L181" s="3"/>
+      <c r="M181" s="3"/>
+      <c r="N181" s="3"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21-01</t>
         </is>
       </c>
-      <c r="B181" s="1" t="inlineStr">
+      <c r="B182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email</t>
         </is>
       </c>
-      <c r="C181" s="1" t="inlineStr">
+      <c r="C182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Real email delivery</t>
         </is>
       </c>
-      <c r="D181" s="1" t="inlineStr">
+      <c r="D182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin, then Jonas</t>
         </is>
       </c>
-      <c r="E181" s="1" t="inlineStr">
+      <c r="E182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Server started with SMTP settings (OPENOKR_MAIL_TRANSPORT and friends), or Mailpit on localhost port 1025</t>
         </is>
       </c>
-      <c r="F181" s="1" t="inlineStr">
+      <c r="F182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Create a personal invitation for a spare email
 2. Jonas uses "Forgot your password?"</t>
         </is>
       </c>
-      <c r="G181" s="1" t="inlineStr">
+      <c r="G182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Both mails arrive with working links. The console mail banner on Admin, General is gone</t>
         </is>
       </c>
-      <c r="H181" s="1" t="inlineStr">
+      <c r="H182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I181" s="1" t="inlineStr">
+      <c r="I182" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mailpit shows every mail at http://localhost:8025</t>
-        </is>
-      </c>
-      <c r="J181" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K181" s="5"/>
-      <c r="L181" s="5"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="5"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21-02</t>
-        </is>
-      </c>
-      <c r="B182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21 Chat channels and email</t>
-        </is>
-      </c>
-      <c r="C182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect Slack</t>
-        </is>
-      </c>
-      <c r="D182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Slack app with bot token, signing secret and workspace id. Events URL set to &lt;instance&gt;/api/channels/slack</t>
-        </is>
-      </c>
-      <c r="F182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Admin, Channels, Slack
-2. Fill "Bot token", "Signing or webhook secret", "Provider workspace id"
-3. Click "Connect"</t>
-        </is>
-      </c>
-      <c r="G182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status "connected"</t>
-        </is>
-      </c>
-      <c r="H182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I182" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The instance must be reachable from the internet (ngrok or a public host)</t>
         </is>
       </c>
       <c r="J182" s="5" t="inlineStr">
@@ -12816,7 +12810,7 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03</t>
+          <t xml:space="preserve">M21-02</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
@@ -12826,28 +12820,29 @@
       </c>
       <c r="C183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link a member's Slack account</t>
+          <t xml:space="preserve">Connect Slack</t>
         </is>
       </c>
       <c r="D183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-02 done</t>
+          <t xml:space="preserve">A Slack app with bot token, signing secret and workspace id. Events URL set to &lt;instance&gt;/api/channels/slack</t>
         </is>
       </c>
       <c r="F183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Account, Where to reach you, "Linked accounts", click "Get a code"
-2. Send the 6-digit code to the OpenOKR bot in Slack within ten minutes</t>
+          <t xml:space="preserve">1. Open Admin, Channels, Slack
+2. Fill "Bot token", "Signing or webhook secret", "Provider workspace id"
+3. Click "Connect"</t>
         </is>
       </c>
       <c r="G183" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chip turns from "not linked" to "linked" with "Unlink"</t>
+          <t xml:space="preserve">Status "connected"</t>
         </is>
       </c>
       <c r="H183" s="1" t="inlineStr">
@@ -12855,7 +12850,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I183" s="1"/>
+      <c r="I183" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The instance must be reachable from the internet (ngrok or a public host)</t>
+        </is>
+      </c>
       <c r="J183" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12869,7 +12868,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-04</t>
+          <t xml:space="preserve">M21-03</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
@@ -12879,7 +12878,7 @@
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A nudge arrives in Slack</t>
+          <t xml:space="preserve">Link a member's Slack account</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
@@ -12889,18 +12888,18 @@
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03 done. Sara owes a check-in</t>
+          <t xml:space="preserve">M21-02 done</t>
         </is>
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set "Primary channel" to Slack and save
-2. Admin runs "Nudge queue"</t>
+          <t xml:space="preserve">1. Open Account, Where to reach you, "Linked accounts", click "Get a code"
+2. Send the 6-digit code to the OpenOKR bot in Slack within ten minutes</t>
         </is>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The message arrives in Slack. Admin, Channels, "Recent messages" shows sent</t>
+          <t xml:space="preserve">The chip turns from "not linked" to "linked" with "Unlink"</t>
         </is>
       </c>
       <c r="H184" s="1" t="inlineStr">
@@ -12908,11 +12907,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I184" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Send me a test" sends an email, not a Slack message. Do not use it to prove chat delivery</t>
-        </is>
-      </c>
+      <c r="I184" s="1"/>
       <c r="J184" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12926,7 +12921,7 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-05</t>
+          <t xml:space="preserve">M21-04</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
@@ -12936,7 +12931,7 @@
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chat commands work</t>
+          <t xml:space="preserve">A nudge arrives in Slack</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -12946,26 +12941,30 @@
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03 done</t>
+          <t xml:space="preserve">M21-03 done. Sara owes a check-in</t>
         </is>
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In Slack type /okr help
-2. Type /okr checkin and follow the prompts</t>
+          <t xml:space="preserve">1. Set "Primary channel" to Slack and save
+2. Admin runs "Nudge queue"</t>
         </is>
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help lists the commands. The check-in appears on the goal like one made in the browser</t>
+          <t xml:space="preserve">The message arrives in Slack. Admin, Channels, "Recent messages" shows sent</t>
         </is>
       </c>
       <c r="H185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I185" s="1"/>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I185" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Send me a test" sends an email, not a Slack message. Do not use it to prove chat delivery</t>
+        </is>
+      </c>
       <c r="J185" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12979,7 +12978,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-06</t>
+          <t xml:space="preserve">M21-05</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
@@ -12989,29 +12988,28 @@
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft Teams end to end</t>
+          <t xml:space="preserve">Chat commands work</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Sara</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Teams app (deploy/teams manifest), client id and secret, tenant id</t>
+          <t xml:space="preserve">M21-03 done</t>
         </is>
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Connect Teams on Admin, Channels
-2. Sara links her account with a code
-3. Run "Nudge queue"</t>
+          <t xml:space="preserve">1. In Slack type /okr help
+2. Type /okr checkin and follow the prompts</t>
         </is>
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connected, linked, and the nudge arrives in Teams</t>
+          <t xml:space="preserve">Help lists the commands. The check-in appears on the goal like one made in the browser</t>
         </is>
       </c>
       <c r="H186" s="1" t="inlineStr">
@@ -13033,30 +13031,84 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M21-06</t>
+        </is>
+      </c>
+      <c r="B187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21 Chat channels and email</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft Teams end to end</t>
+        </is>
+      </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Sara</t>
+        </is>
+      </c>
+      <c r="E187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Teams app (deploy/teams manifest), client id and secret, tenant id</t>
+        </is>
+      </c>
+      <c r="F187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Connect Teams on Admin, Channels
+2. Sara links her account with a code
+3. Run "Nudge queue"</t>
+        </is>
+      </c>
+      <c r="G187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connected, linked, and the nudge arrives in Teams</t>
+        </is>
+      </c>
+      <c r="H187" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I187" s="1"/>
+      <c r="J187" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K187" s="5"/>
+      <c r="L187" s="5"/>
+      <c r="M187" s="5"/>
+      <c r="N187" s="5"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M21-07</t>
         </is>
       </c>
-      <c r="B187" s="1" t="inlineStr">
+      <c r="B188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email</t>
         </is>
       </c>
-      <c r="C187" s="1" t="inlineStr">
+      <c r="C188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">WhatsApp end to end</t>
         </is>
       </c>
-      <c r="D187" s="1" t="inlineStr">
+      <c r="D188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin, then Sara</t>
         </is>
       </c>
-      <c r="E187" s="1" t="inlineStr">
+      <c r="E188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Meta WhatsApp Business app, permanent token, app secret and verify token, phone number id</t>
         </is>
       </c>
-      <c r="F187" s="1" t="inlineStr">
+      <c r="F188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Connect WhatsApp on Admin, Channels
 2. Click "Sync from Meta" and map a template to a reminder
@@ -13064,63 +13116,9 @@
 4. Run "Nudge queue"</t>
         </is>
       </c>
-      <c r="G187" s="1" t="inlineStr">
+      <c r="G188" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connected, linked, and the reminder arrives on WhatsApp</t>
-        </is>
-      </c>
-      <c r="H187" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I187" s="1"/>
-      <c r="J187" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K187" s="5"/>
-      <c r="L187" s="5"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="5"/>
-    </row>
-    <row r="188">
-      <c r="A188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21-08</t>
-        </is>
-      </c>
-      <c r="B188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21 Chat channels and email</t>
-        </is>
-      </c>
-      <c r="C188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telegram end to end</t>
-        </is>
-      </c>
-      <c r="D188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin, then Sara</t>
-        </is>
-      </c>
-      <c r="E188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A BotFather token and a webhook secret</t>
-        </is>
-      </c>
-      <c r="F188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Connect Telegram on Admin, Channels
-2. Sara links her account with a code
-3. Run "Nudge queue"</t>
-        </is>
-      </c>
-      <c r="G188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connected, linked, and the nudge arrives in Telegram</t>
         </is>
       </c>
       <c r="H188" s="1" t="inlineStr">
@@ -13142,7 +13140,7 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-09</t>
+          <t xml:space="preserve">M21-08</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
@@ -13152,28 +13150,29 @@
       </c>
       <c r="C189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disconnect a channel</t>
+          <t xml:space="preserve">Telegram end to end</t>
         </is>
       </c>
       <c r="D189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, then Sara</t>
         </is>
       </c>
       <c r="E189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A connected channel</t>
+          <t xml:space="preserve">A BotFather token and a webhook secret</t>
         </is>
       </c>
       <c r="F189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Disconnect"
-2. As Sara open Account, Where to reach you</t>
+          <t xml:space="preserve">1. Connect Telegram on Admin, Channels
+2. Sara links her account with a code
+3. Run "Nudge queue"</t>
         </is>
       </c>
       <c r="G189" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status "not connected". Sara's option for that channel is disabled</t>
+          <t xml:space="preserve">Connected, linked, and the nudge arrives in Telegram</t>
         </is>
       </c>
       <c r="H189" s="1" t="inlineStr">
@@ -13193,52 +13192,105 @@
       <c r="N189" s="5"/>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
+      <c r="A190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21-09</t>
+        </is>
+      </c>
+      <c r="B190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21 Chat channels and email</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disconnect a channel</t>
+        </is>
+      </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A connected channel</t>
+        </is>
+      </c>
+      <c r="F190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click "Disconnect"
+2. As Sara open Account, Where to reach you</t>
+        </is>
+      </c>
+      <c r="G190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status "not connected". Sara's option for that channel is disabled</t>
+        </is>
+      </c>
+      <c r="H190" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I190" s="1"/>
+      <c r="J190" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K190" s="5"/>
+      <c r="L190" s="5"/>
+      <c r="M190" s="5"/>
+      <c r="N190" s="5"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M22 Single sign-on and directory sync: Sign in through a company identity provider and sync the directory. Needs M04 first. About 45 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B190" s="3"/>
-      <c r="C190" s="3"/>
-      <c r="D190" s="3"/>
-      <c r="E190" s="3"/>
-      <c r="F190" s="3"/>
-      <c r="G190" s="3"/>
-      <c r="H190" s="3"/>
-      <c r="I190" s="3"/>
-      <c r="J190" s="3"/>
-      <c r="K190" s="3"/>
-      <c r="L190" s="3"/>
-      <c r="M190" s="3"/>
-      <c r="N190" s="3"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="1" t="inlineStr">
+      <c r="B191" s="3"/>
+      <c r="C191" s="3"/>
+      <c r="D191" s="3"/>
+      <c r="E191" s="3"/>
+      <c r="F191" s="3"/>
+      <c r="G191" s="3"/>
+      <c r="H191" s="3"/>
+      <c r="I191" s="3"/>
+      <c r="J191" s="3"/>
+      <c r="K191" s="3"/>
+      <c r="L191" s="3"/>
+      <c r="M191" s="3"/>
+      <c r="N191" s="3"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M22-01</t>
         </is>
       </c>
-      <c r="B191" s="1" t="inlineStr">
+      <c r="B192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M22 Single sign-on and directory sync</t>
         </is>
       </c>
-      <c r="C191" s="1" t="inlineStr">
+      <c r="C192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Add an OIDC provider and sign in with it</t>
         </is>
       </c>
-      <c r="D191" s="1" t="inlineStr">
+      <c r="D192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E191" s="1" t="inlineStr">
+      <c r="E192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An OIDC app at Google, Okta, Entra or Keycloak with the redirect URL registered</t>
         </is>
       </c>
-      <c r="F191" s="1" t="inlineStr">
+      <c r="F192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Single sign-on, "Add provider"
 2. Protocol OIDC, fill Provider ID, Display name, Discovery URL, Client ID, Client secret, email domain
@@ -13247,76 +13299,19 @@
 5. Sign out, use the new button on the sign-in page</t>
         </is>
       </c>
-      <c r="G191" s="1" t="inlineStr">
+      <c r="G192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Provider saved. It will take effect on the next instance restart." The sign-in page shows the provider button and sign-in works</t>
         </is>
       </c>
-      <c r="H191" s="1" t="inlineStr">
+      <c r="H192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I191" s="1" t="inlineStr">
+      <c r="I192" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Needs a restart, which needs server access</t>
-        </is>
-      </c>
-      <c r="J191" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K191" s="5"/>
-      <c r="L191" s="5"/>
-      <c r="M191" s="5"/>
-      <c r="N191" s="5"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22-02</t>
-        </is>
-      </c>
-      <c r="B192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
-        </is>
-      </c>
-      <c r="C192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enforce SSO for a domain</t>
-        </is>
-      </c>
-      <c r="D192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22-01 done</t>
-        </is>
-      </c>
-      <c r="F192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Tick "Enforce SSO for the email domains listed above" and save, restart
-2. Try password sign-in with an address on that domain</t>
-        </is>
-      </c>
-      <c r="G192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Password sign-in is refused for that domain</t>
-        </is>
-      </c>
-      <c r="H192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I192" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Do not enforce on the Admin's own domain, or you lock yourself out</t>
         </is>
       </c>
       <c r="J192" s="5" t="inlineStr">
@@ -13332,7 +13327,7 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-03</t>
+          <t xml:space="preserve">M22-02</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
@@ -13342,7 +13337,7 @@
       </c>
       <c r="C193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAML provider</t>
+          <t xml:space="preserve">Enforce SSO for a domain</t>
         </is>
       </c>
       <c r="D193" s="1" t="inlineStr">
@@ -13352,27 +13347,30 @@
       </c>
       <c r="E193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A SAML IdP</t>
+          <t xml:space="preserve">M22-01 done</t>
         </is>
       </c>
       <c r="F193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Add a SAML 2.0 provider with Sign-on URL, Issuer and Signing certificate
-2. Copy the "Assertion consumer service" URL into the IdP
-3. Restart and sign in</t>
+          <t xml:space="preserve">1. Tick "Enforce SSO for the email domains listed above" and save, restart
+2. Try password sign-in with an address on that domain</t>
         </is>
       </c>
       <c r="G193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign-in through SAML works</t>
+          <t xml:space="preserve">Password sign-in is refused for that domain</t>
         </is>
       </c>
       <c r="H193" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
-        </is>
-      </c>
-      <c r="I193" s="1"/>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I193" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Do not enforce on the Admin's own domain, or you lock yourself out</t>
+        </is>
+      </c>
       <c r="J193" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -13386,7 +13384,7 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-04</t>
+          <t xml:space="preserve">M22-03</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
@@ -13396,7 +13394,7 @@
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCIM token and user push</t>
+          <t xml:space="preserve">SAML provider</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -13406,19 +13404,19 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An IdP that supports SCIM 2.0</t>
+          <t xml:space="preserve">A SAML IdP</t>
         </is>
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Directory sync, click "Generate SCIM token"
-2. Configure the IdP with the "SCIM endpoint" and token
-3. Assign a user in the IdP, then unassign</t>
+          <t xml:space="preserve">1. Add a SAML 2.0 provider with Sign-on URL, Issuer and Signing certificate
+2. Copy the "Assertion consumer service" URL into the IdP
+3. Restart and sign in</t>
         </is>
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Copy this token now. It will not be shown again." The user appears in People, then shows as suspended after unassign</t>
+          <t xml:space="preserve">Sign-in through SAML works</t>
         </is>
       </c>
       <c r="H194" s="1" t="inlineStr">
@@ -13440,7 +13438,7 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-05</t>
+          <t xml:space="preserve">M22-04</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
@@ -13450,33 +13448,34 @@
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Require a second factor for everyone</t>
+          <t xml:space="preserve">SCIM token and user push</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Jonas</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">An IdP that supports SCIM 2.0</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tick "Require a second factor for everybody in this workspace" on Admin, General and save
-2. Jonas signs in</t>
+          <t xml:space="preserve">1. Open Admin, Directory sync, click "Generate SCIM token"
+2. Configure the IdP with the "SCIM endpoint" and token
+3. Assign a user in the IdP, then unassign</t>
         </is>
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas is asked to set up a second factor before continuing. Untick afterwards</t>
+          <t xml:space="preserve">"Copy this token now. It will not be shown again." The user appears in People, then shows as suspended after unassign</t>
         </is>
       </c>
       <c r="H195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I195" s="1"/>
@@ -13491,52 +13490,105 @@
       <c r="N195" s="5"/>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="inlineStr">
+      <c r="A196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22-05</t>
+        </is>
+      </c>
+      <c r="B196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Require a second factor for everyone</t>
+        </is>
+      </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Jonas</t>
+        </is>
+      </c>
+      <c r="E196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Tick "Require a second factor for everybody in this workspace" on Admin, General and save
+2. Jonas signs in</t>
+        </is>
+      </c>
+      <c r="G196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jonas is asked to set up a second factor before continuing. Untick afterwards</t>
+        </is>
+      </c>
+      <c r="H196" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I196" s="1"/>
+      <c r="J196" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K196" s="5"/>
+      <c r="L196" s="5"/>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export: Bring data in from spreadsheets and FlowyTeam, and take it out. Needs M07 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B196" s="3"/>
-      <c r="C196" s="3"/>
-      <c r="D196" s="3"/>
-      <c r="E196" s="3"/>
-      <c r="F196" s="3"/>
-      <c r="G196" s="3"/>
-      <c r="H196" s="3"/>
-      <c r="I196" s="3"/>
-      <c r="J196" s="3"/>
-      <c r="K196" s="3"/>
-      <c r="L196" s="3"/>
-      <c r="M196" s="3"/>
-      <c r="N196" s="3"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="1" t="inlineStr">
+      <c r="B197" s="3"/>
+      <c r="C197" s="3"/>
+      <c r="D197" s="3"/>
+      <c r="E197" s="3"/>
+      <c r="F197" s="3"/>
+      <c r="G197" s="3"/>
+      <c r="H197" s="3"/>
+      <c r="I197" s="3"/>
+      <c r="J197" s="3"/>
+      <c r="K197" s="3"/>
+      <c r="L197" s="3"/>
+      <c r="M197" s="3"/>
+      <c r="N197" s="3"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23-01</t>
         </is>
       </c>
-      <c r="B197" s="1" t="inlineStr">
+      <c r="B198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export</t>
         </is>
       </c>
-      <c r="C197" s="1" t="inlineStr">
+      <c r="C198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Import goals from a CSV</t>
         </is>
       </c>
-      <c r="D197" s="1" t="inlineStr">
+      <c r="D198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E197" s="1" t="inlineStr">
+      <c r="E198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A CSV with 3 goals (title, level, champion email)</t>
         </is>
       </c>
-      <c r="F197" s="1" t="inlineStr">
+      <c r="F198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Import
 2. Pick goals in "What is in the file", choose the file, click "Read the file"
@@ -13544,61 +13596,9 @@
 4. Click "Import &lt;n&gt; rows"</t>
         </is>
       </c>
-      <c r="G197" s="1" t="inlineStr">
+      <c r="G198" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Preview counts Read, To create, To update, Skipped. After import: "Imported. Run the same file again and it writes nothing new." The goals are on the work map</t>
-        </is>
-      </c>
-      <c r="H197" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I197" s="1"/>
-      <c r="J197" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K197" s="5"/>
-      <c r="L197" s="5"/>
-      <c r="M197" s="5"/>
-      <c r="N197" s="5"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23-02</t>
-        </is>
-      </c>
-      <c r="B198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23 Import and export</t>
-        </is>
-      </c>
-      <c r="C198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Importing the same file twice writes nothing</t>
-        </is>
-      </c>
-      <c r="D198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23-01 done</t>
-        </is>
-      </c>
-      <c r="F198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Import the same file again</t>
-        </is>
-      </c>
-      <c r="G198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preview shows 0 to create</t>
         </is>
       </c>
       <c r="H198" s="1" t="inlineStr">
@@ -13620,7 +13620,7 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-03</t>
+          <t xml:space="preserve">M23-02</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
@@ -13630,7 +13630,7 @@
       </c>
       <c r="C199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A bad row is reported, not dropped silently</t>
+          <t xml:space="preserve">Importing the same file twice writes nothing</t>
         </is>
       </c>
       <c r="D199" s="1" t="inlineStr">
@@ -13640,22 +13640,22 @@
       </c>
       <c r="E199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV with one row missing its title</t>
+          <t xml:space="preserve">M23-01 done</t>
         </is>
       </c>
       <c r="F199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Import it</t>
+          <t xml:space="preserve">1. Import the same file again</t>
         </is>
       </c>
       <c r="G199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">That row is counted as Skipped with its reason</t>
+          <t xml:space="preserve">Preview shows 0 to create</t>
         </is>
       </c>
       <c r="H199" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I199" s="1"/>
@@ -13672,7 +13672,7 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-04</t>
+          <t xml:space="preserve">M23-03</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
@@ -13682,7 +13682,7 @@
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Import KPI records from an xlsx file</t>
+          <t xml:space="preserve">A bad row is reported, not dropped silently</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
@@ -13692,22 +13692,22 @@
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An xlsx of KPI records</t>
+          <t xml:space="preserve">A CSV with one row missing its title</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Import with kpi-records</t>
+          <t xml:space="preserve">1. Import it</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values appear in the KPI grid</t>
+          <t xml:space="preserve">That row is counted as Skipped with its reason</t>
         </is>
       </c>
       <c r="H200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I200" s="1"/>
@@ -13724,7 +13724,7 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-05</t>
+          <t xml:space="preserve">M23-04</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export the workspace</t>
+          <t xml:space="preserve">Import KPI records from an xlsx file</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
@@ -13744,22 +13744,22 @@
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">An xlsx of KPI records</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Admin, Import use "Export workspace" with "Include files"</t>
+          <t xml:space="preserve">1. Import with kpi-records</t>
         </is>
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An archive file downloads</t>
+          <t xml:space="preserve">Values appear in the KPI grid</t>
         </is>
       </c>
       <c r="H201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I201" s="1"/>
@@ -13776,30 +13776,82 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M23-05</t>
+        </is>
+      </c>
+      <c r="B202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M23 Import and export</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export the workspace</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On Admin, Import use "Export workspace" with "Include files"</t>
+        </is>
+      </c>
+      <c r="G202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An archive file downloads</t>
+        </is>
+      </c>
+      <c r="H202" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I202" s="1"/>
+      <c r="J202" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K202" s="5"/>
+      <c r="L202" s="5"/>
+      <c r="M202" s="5"/>
+      <c r="N202" s="5"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M23-06</t>
         </is>
       </c>
-      <c r="B202" s="1" t="inlineStr">
+      <c r="B203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export</t>
         </is>
       </c>
-      <c r="C202" s="1" t="inlineStr">
+      <c r="C203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">FlowyTeam import from the command line</t>
         </is>
       </c>
-      <c r="D202" s="1" t="inlineStr">
+      <c r="D203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin (server access)</t>
         </is>
       </c>
-      <c r="E202" s="1" t="inlineStr">
+      <c r="E203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A FlowyTeam MySQL copy and the company id</t>
         </is>
       </c>
-      <c r="F202" s="1" t="inlineStr">
+      <c r="F203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Run pnpm import:flowyteam with --source, --company, --workspace, --as, without --write
 2. Read the dry-run report
@@ -13807,78 +13859,78 @@
 4. Open the work map and People</t>
         </is>
       </c>
-      <c r="G202" s="1" t="inlineStr">
+      <c r="G203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The dry run writes nothing. The real run imports people, spaces, cycles, objectives and KPIs, visible in the UI</t>
         </is>
       </c>
-      <c r="H202" s="1" t="inlineStr">
+      <c r="H203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I202" s="1" t="inlineStr">
+      <c r="I203" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Technical step. Skip unless a FlowyTeam source is available</t>
         </is>
       </c>
-      <c r="J202" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K202" s="5"/>
-      <c r="L202" s="5"/>
-      <c r="M202" s="5"/>
-      <c r="N202" s="5"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="3" t="inlineStr">
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K203" s="5"/>
+      <c r="L203" s="5"/>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents: Reach the product from scripts, the command line and outside AI agents. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B203" s="3"/>
-      <c r="C203" s="3"/>
-      <c r="D203" s="3"/>
-      <c r="E203" s="3"/>
-      <c r="F203" s="3"/>
-      <c r="G203" s="3"/>
-      <c r="H203" s="3"/>
-      <c r="I203" s="3"/>
-      <c r="J203" s="3"/>
-      <c r="K203" s="3"/>
-      <c r="L203" s="3"/>
-      <c r="M203" s="3"/>
-      <c r="N203" s="3"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="1" t="inlineStr">
+      <c r="B204" s="3"/>
+      <c r="C204" s="3"/>
+      <c r="D204" s="3"/>
+      <c r="E204" s="3"/>
+      <c r="F204" s="3"/>
+      <c r="G204" s="3"/>
+      <c r="H204" s="3"/>
+      <c r="I204" s="3"/>
+      <c r="J204" s="3"/>
+      <c r="K204" s="3"/>
+      <c r="L204" s="3"/>
+      <c r="M204" s="3"/>
+      <c r="N204" s="3"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24-01</t>
         </is>
       </c>
-      <c r="B204" s="1" t="inlineStr">
+      <c r="B205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C204" s="1" t="inlineStr">
+      <c r="C205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Create and revoke an API token</t>
         </is>
       </c>
-      <c r="D204" s="1" t="inlineStr">
+      <c r="D205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E204" s="1" t="inlineStr">
+      <c r="E205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F204" s="1" t="inlineStr">
+      <c r="F205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Account, API tokens
 2. Click "Create token" with no name, then with no scope
@@ -13886,67 +13938,14 @@
 4. Click "Revoke"</t>
         </is>
       </c>
-      <c r="G204" s="1" t="inlineStr">
+      <c r="G205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Give the token a name." and "Choose at least one scope, or the token could reach nothing." The token shows once, is listed, then revoked</t>
         </is>
       </c>
-      <c r="H204" s="1" t="inlineStr">
+      <c r="H205" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I204" s="1"/>
-      <c r="J204" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K204" s="5"/>
-      <c r="L204" s="5"/>
-      <c r="M204" s="5"/>
-      <c r="N204" s="5"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M24-02</t>
-        </is>
-      </c>
-      <c r="B205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
-        </is>
-      </c>
-      <c r="C205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Use the token, then use it after revoking</t>
-        </is>
-      </c>
-      <c r="D205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara (technical)</t>
-        </is>
-      </c>
-      <c r="E205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A token from M24-01 before revoking</t>
-        </is>
-      </c>
-      <c r="F205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Call a GET endpoint from docs/api/reference.md with the token
-2. Revoke it and call again</t>
-        </is>
-      </c>
-      <c r="G205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">First call succeeds. After revoke it is refused</t>
-        </is>
-      </c>
-      <c r="H205" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I205" s="1"/>
@@ -13963,30 +13962,83 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M24-02</t>
+        </is>
+      </c>
+      <c r="B206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use the token, then use it after revoking</t>
+        </is>
+      </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara (technical)</t>
+        </is>
+      </c>
+      <c r="E206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A token from M24-01 before revoking</t>
+        </is>
+      </c>
+      <c r="F206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Call a GET endpoint from docs/api/reference.md with the token
+2. Revoke it and call again</t>
+        </is>
+      </c>
+      <c r="G206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First call succeeds. After revoke it is refused</t>
+        </is>
+      </c>
+      <c r="H206" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I206" s="1"/>
+      <c r="J206" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K206" s="5"/>
+      <c r="L206" s="5"/>
+      <c r="M206" s="5"/>
+      <c r="N206" s="5"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M24-03</t>
         </is>
       </c>
-      <c r="B206" s="1" t="inlineStr">
+      <c r="B207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C206" s="1" t="inlineStr">
+      <c r="C207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Command-line login by device approval</t>
         </is>
       </c>
-      <c r="D206" s="1" t="inlineStr">
+      <c r="D207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara (technical)</t>
         </is>
       </c>
-      <c r="E206" s="1" t="inlineStr">
+      <c r="E207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The okr command line</t>
         </is>
       </c>
-      <c r="F206" s="1" t="inlineStr">
+      <c r="F207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Run okr login --url &lt;instance&gt;
 2. Open the printed link, check "Scopes it asked for"
@@ -13994,54 +14046,54 @@
 4. Repeat and click "Refuse"</t>
         </is>
       </c>
-      <c r="G206" s="1" t="inlineStr">
+      <c r="G207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Authorise: the terminal prints Saved profile. Refuse: the login fails</t>
         </is>
       </c>
-      <c r="H206" s="1" t="inlineStr">
+      <c r="H207" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I206" s="1"/>
-      <c r="J206" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K206" s="5"/>
-      <c r="L206" s="5"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="5"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="1" t="inlineStr">
+      <c r="I207" s="1"/>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K207" s="5"/>
+      <c r="L207" s="5"/>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24-04</t>
         </is>
       </c>
-      <c r="B207" s="1" t="inlineStr">
+      <c r="B208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C207" s="1" t="inlineStr">
+      <c r="C208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connect an external AI agent (MCP)</t>
         </is>
       </c>
-      <c r="D207" s="1" t="inlineStr">
+      <c r="D208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E207" s="1" t="inlineStr">
+      <c r="E208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An MCP client such as Claude Desktop, and a public HTTPS URL for the instance</t>
         </is>
       </c>
-      <c r="F207" s="1" t="inlineStr">
+      <c r="F208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Add a remote MCP server &lt;instance&gt;/api/mcp
 2. On "Connect an agent" pick the workspace and click "Connect"
@@ -14049,134 +14101,82 @@
 4. Open Account, Connected agents and click "Revoke"</t>
         </is>
       </c>
-      <c r="G207" s="1" t="inlineStr">
+      <c r="G208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The agent lists only goals Sara may see. After revoke it loses access</t>
         </is>
       </c>
-      <c r="H207" s="1" t="inlineStr">
+      <c r="H208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I207" s="1"/>
-      <c r="J207" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K207" s="5"/>
-      <c r="L207" s="5"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="5"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="3" t="inlineStr">
+      <c r="I208" s="1"/>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K208" s="5"/>
+      <c r="L208" s="5"/>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M25 Audit trail and workspace state: Check the audit trail recorded the sensitive actions from earlier modules. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B208" s="3"/>
-      <c r="C208" s="3"/>
-      <c r="D208" s="3"/>
-      <c r="E208" s="3"/>
-      <c r="F208" s="3"/>
-      <c r="G208" s="3"/>
-      <c r="H208" s="3"/>
-      <c r="I208" s="3"/>
-      <c r="J208" s="3"/>
-      <c r="K208" s="3"/>
-      <c r="L208" s="3"/>
-      <c r="M208" s="3"/>
-      <c r="N208" s="3"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="1" t="inlineStr">
+      <c r="B209" s="3"/>
+      <c r="C209" s="3"/>
+      <c r="D209" s="3"/>
+      <c r="E209" s="3"/>
+      <c r="F209" s="3"/>
+      <c r="G209" s="3"/>
+      <c r="H209" s="3"/>
+      <c r="I209" s="3"/>
+      <c r="J209" s="3"/>
+      <c r="K209" s="3"/>
+      <c r="L209" s="3"/>
+      <c r="M209" s="3"/>
+      <c r="N209" s="3"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M25-01</t>
         </is>
       </c>
-      <c r="B209" s="1" t="inlineStr">
+      <c r="B210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M25 Audit trail and workspace state</t>
         </is>
       </c>
-      <c r="C209" s="1" t="inlineStr">
+      <c r="C210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The audit trail records sensitive actions</t>
         </is>
       </c>
-      <c r="D209" s="1" t="inlineStr">
+      <c r="D210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E209" s="1" t="inlineStr">
+      <c r="E210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Earlier modules done (suspend, override publish)</t>
         </is>
       </c>
-      <c r="F209" s="1" t="inlineStr">
+      <c r="F210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Audit trail
 2. Filter "Action" by people.suspend</t>
         </is>
       </c>
-      <c r="G209" s="1" t="inlineStr">
+      <c r="G210" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The suspend of Tomas and the publish override are listed with who did them</t>
-        </is>
-      </c>
-      <c r="H209" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I209" s="1"/>
-      <c r="J209" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K209" s="5"/>
-      <c r="L209" s="5"/>
-      <c r="M209" s="5"/>
-      <c r="N209" s="5"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M25-02</t>
-        </is>
-      </c>
-      <c r="B210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M25 Audit trail and workspace state</t>
-        </is>
-      </c>
-      <c r="C210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify the audit chain</t>
-        </is>
-      </c>
-      <c r="D210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Click "Verify the audit chain"</t>
-        </is>
-      </c>
-      <c r="G210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The chain is intact. &lt;n&gt; rows checked"</t>
         </is>
       </c>
       <c r="H210" s="1" t="inlineStr">
@@ -14198,7 +14198,7 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M25-03</t>
+          <t xml:space="preserve">M25-02</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
@@ -14208,7 +14208,7 @@
       </c>
       <c r="C211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export the audit trail</t>
+          <t xml:space="preserve">Verify the audit chain</t>
         </is>
       </c>
       <c r="D211" s="1" t="inlineStr">
@@ -14223,17 +14223,17 @@
       </c>
       <c r="F211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set From and To, click "Export as CSV"</t>
+          <t xml:space="preserve">1. Click "Verify the audit chain"</t>
         </is>
       </c>
       <c r="G211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV downloads. An empty range says "The export came back empty."</t>
+          <t xml:space="preserve">"The chain is intact. &lt;n&gt; rows checked"</t>
         </is>
       </c>
       <c r="H211" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I211" s="1"/>
@@ -14250,7 +14250,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M25-04</t>
+          <t xml:space="preserve">M25-03</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
@@ -14260,12 +14260,12 @@
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read-only workspace</t>
+          <t xml:space="preserve">Export the audit trail</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E212" s="1" t="inlineStr">
@@ -14275,19 +14275,17 @@
       </c>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Admin, General, card "State", click "Set to read only"
-2. Sara tries to post a check-in
-3. Admin clicks "Return to active"</t>
+          <t xml:space="preserve">1. Set From and To, click "Export as CSV"</t>
         </is>
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara can read but every write is refused with a message. After return to active, writes work</t>
+          <t xml:space="preserve">A CSV downloads. An empty range says "The export came back empty."</t>
         </is>
       </c>
       <c r="H212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I212" s="1"/>
@@ -14302,81 +14300,83 @@
       <c r="N212" s="5"/>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="inlineStr">
+      <c r="A213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25-04</t>
+        </is>
+      </c>
+      <c r="B213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25 Audit trail and workspace state</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read-only workspace</t>
+        </is>
+      </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Sara</t>
+        </is>
+      </c>
+      <c r="E213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On Admin, General, card "State", click "Set to read only"
+2. Sara tries to post a check-in
+3. Admin clicks "Return to active"</t>
+        </is>
+      </c>
+      <c r="G213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara can read but every write is refused with a message. After return to active, writes work</t>
+        </is>
+      </c>
+      <c r="H213" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I213" s="1"/>
+      <c r="J213" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K213" s="5"/>
+      <c r="L213" s="5"/>
+      <c r="M213" s="5"/>
+      <c r="N213" s="5"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M26 Cloud operator console: Check the managed-cloud operator console. Needs M04 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B213" s="3"/>
-      <c r="C213" s="3"/>
-      <c r="D213" s="3"/>
-      <c r="E213" s="3"/>
-      <c r="F213" s="3"/>
-      <c r="G213" s="3"/>
-      <c r="H213" s="3"/>
-      <c r="I213" s="3"/>
-      <c r="J213" s="3"/>
-      <c r="K213" s="3"/>
-      <c r="L213" s="3"/>
-      <c r="M213" s="3"/>
-      <c r="N213" s="3"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M26-01</t>
-        </is>
-      </c>
-      <c r="B214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M26 Cloud operator console</t>
-        </is>
-      </c>
-      <c r="C214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator console is off on a self-hosted instance</t>
-        </is>
-      </c>
-      <c r="D214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPENOKR_CLOUD not set</t>
-        </is>
-      </c>
-      <c r="F214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open /operator and /admin/plan</t>
-        </is>
-      </c>
-      <c r="G214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both return Not Found</t>
-        </is>
-      </c>
-      <c r="H214" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low</t>
-        </is>
-      </c>
-      <c r="I214" s="1"/>
-      <c r="J214" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K214" s="5"/>
-      <c r="L214" s="5"/>
-      <c r="M214" s="5"/>
-      <c r="N214" s="5"/>
+      <c r="B214" s="3"/>
+      <c r="C214" s="3"/>
+      <c r="D214" s="3"/>
+      <c r="E214" s="3"/>
+      <c r="F214" s="3"/>
+      <c r="G214" s="3"/>
+      <c r="H214" s="3"/>
+      <c r="I214" s="3"/>
+      <c r="J214" s="3"/>
+      <c r="K214" s="3"/>
+      <c r="L214" s="3"/>
+      <c r="M214" s="3"/>
+      <c r="N214" s="3"/>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02</t>
+          <t xml:space="preserve">M26-01</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr">
@@ -14386,27 +14386,27 @@
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator sees every workspace</t>
+          <t xml:space="preserve">Operator console is off on a self-hosted instance</t>
         </is>
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator (docs/install/cloud.md)</t>
+          <t xml:space="preserve">OPENOKR_CLOUD not set</t>
         </is>
       </c>
       <c r="F215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open /operator</t>
+          <t xml:space="preserve">1. Open /operator and /admin/plan</t>
         </is>
       </c>
       <c r="G215" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table with Workspace, State, Plan, Region, Members, Goals, Storage</t>
+          <t xml:space="preserve">Both return Not Found</t>
         </is>
       </c>
       <c r="H215" s="1" t="inlineStr">
@@ -14414,11 +14414,7 @@
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Technical setup. Skip unless testing the managed cloud</t>
-        </is>
-      </c>
+      <c r="I215" s="1"/>
       <c r="J215" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -14432,7 +14428,7 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-03</t>
+          <t xml:space="preserve">M26-02</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr">
@@ -14442,29 +14438,27 @@
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suspend a workspace from the console</t>
+          <t xml:space="preserve">Operator sees every workspace</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator, then Sara</t>
+          <t xml:space="preserve">Operator</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02 done</t>
+          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator (docs/install/cloud.md)</t>
         </is>
       </c>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the workspace, choose "Suspended", write a reason, click "Apply to Northwind Labs"
-2. Sara tries to edit
-3. Return it to Active</t>
+          <t xml:space="preserve">1. Open /operator</t>
         </is>
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara can read only while suspended</t>
+          <t xml:space="preserve">Table with Workspace, State, Plan, Region, Members, Goals, Storage</t>
         </is>
       </c>
       <c r="H216" s="1" t="inlineStr">
@@ -14472,7 +14466,11 @@
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I216" s="1"/>
+      <c r="I216" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical setup. Skip unless testing the managed cloud</t>
+        </is>
+      </c>
       <c r="J216" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -14486,7 +14484,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-04</t>
+          <t xml:space="preserve">M26-03</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
@@ -14496,12 +14494,12 @@
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support access needs the admin's approval</t>
+          <t xml:space="preserve">Suspend a workspace from the console</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator, then Admin</t>
+          <t xml:space="preserve">Operator, then Sara</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
@@ -14511,13 +14509,14 @@
       </c>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Operator writes "Why you need to be in there" and clicks "Ask to come in"
-2. Admin opens Admin, Support access, picks Read only for 1 hour, clicks "Let them in"</t>
+          <t xml:space="preserve">1. Open the workspace, choose "Suspended", write a reason, click "Apply to Northwind Labs"
+2. Sara tries to edit
+3. Return it to Active</t>
         </is>
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The request waits under "Waiting for you". After approval the operator can read the workspace for one hour</t>
+          <t xml:space="preserve">Sara can read only while suspended</t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
@@ -14539,7 +14538,7 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-05</t>
+          <t xml:space="preserve">M26-04</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
@@ -14549,12 +14548,12 @@
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instance banner</t>
+          <t xml:space="preserve">Support access needs the admin's approval</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator</t>
+          <t xml:space="preserve">Operator, then Admin</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -14564,14 +14563,13 @@
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On /operator/instance, "Say something": message, Tone Warning, a stop time, "People can dismiss it"
-2. Click "Show this message"
-3. Sara opens the app and dismisses it</t>
+          <t xml:space="preserve">1. Operator writes "Why you need to be in there" and clicks "Ask to come in"
+2. Admin opens Admin, Support access, picks Read only for 1 hour, clicks "Let them in"</t>
         </is>
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every user sees the banner. Dismissing hides it for Sara</t>
+          <t xml:space="preserve">The request waits under "Waiting for you". After approval the operator can read the workspace for one hour</t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
@@ -14593,7 +14591,7 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-06</t>
+          <t xml:space="preserve">M26-05</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
@@ -14603,7 +14601,7 @@
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator sets a plan, and a downgrade below the headcount is refused</t>
+          <t xml:space="preserve">Instance banner</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
@@ -14613,18 +14611,19 @@
       </c>
       <c r="E219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02 done, and cloud.plans holds a plan with fewer seats than Northwind Labs has people</t>
+          <t xml:space="preserve">M26-02 done</t>
         </is>
       </c>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the workspace, under "Plan and seats" pick the small plan, write a reason, click "Set the plan for Northwind Labs"
-2. Pick a larger plan, or type a seat count above the headcount, and apply again</t>
+          <t xml:space="preserve">1. On /operator/instance, "Say something": message, Tone Warning, a stop time, "People can dismiss it"
+2. Click "Show this message"
+3. Sara opens the app and dismisses it</t>
         </is>
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The first is refused naming the seats the plan has and the seats in use. The second is applied and the Tenant facts show the new plan and seats</t>
+          <t xml:space="preserve">Every user sees the banner. Dismissing hides it for Sara</t>
         </is>
       </c>
       <c r="H219" s="1" t="inlineStr">
@@ -14646,7 +14645,7 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-07</t>
+          <t xml:space="preserve">M26-06</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
@@ -14656,29 +14655,28 @@
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrator sees who holds a seat and changes plan</t>
+          <t xml:space="preserve">Operator sets a plan, and a downgrade below the headcount is refused</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Operator</t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-07 done</t>
+          <t xml:space="preserve">M26-02 done, and cloud.plans holds a plan with fewer seats than Northwind Labs has people</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Plan and seats
-2. Read the list under "Who holds a seat"
-3. Under "Move to" pick another plan and click "Change plan"</t>
+          <t xml:space="preserve">1. Open the workspace, under "Plan and seats" pick the small plan, write a reason, click "Set the plan for Northwind Labs"
+2. Pick a larger plan, or type a seat count above the headcount, and apply again</t>
         </is>
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The list names every person and invitation the seat count counts, and no guest or agent. The plan changes, or is refused naming both numbers when it has too few seats</t>
+          <t xml:space="preserve">The first is refused naming the seats the plan has and the seats in use. The second is applied and the Tenant facts show the new plan and seats</t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
@@ -14697,9 +14695,63 @@
       <c r="M220" s="5"/>
       <c r="N220" s="5"/>
     </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07</t>
+        </is>
+      </c>
+      <c r="B221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26 Cloud operator console</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrator sees who holds a seat and changes plan</t>
+        </is>
+      </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07 done</t>
+        </is>
+      </c>
+      <c r="F221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Admin, Plan and seats
+2. Read the list under "Who holds a seat"
+3. Under "Move to" pick another plan and click "Change plan"</t>
+        </is>
+      </c>
+      <c r="G221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The list names every person and invitation the seat count counts, and no guest or agent. The plan changes, or is refused naming both numbers when it has too few seats</t>
+        </is>
+      </c>
+      <c r="H221" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="I221" s="1"/>
+      <c r="J221" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K221" s="5"/>
+      <c r="L221" s="5"/>
+      <c r="M221" s="5"/>
+      <c r="N221" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N220"/>
-  <conditionalFormatting sqref="J2:J220">
+  <autoFilter ref="A1:N221"/>
+  <conditionalFormatting sqref="J2:J221">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",J2)))</formula>
     </cfRule>
@@ -14717,10 +14769,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J220">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J221">
       <formula1>"Not Run,Pass,Fail,Error,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H220">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H221">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/testing/OpenOKR-UAT.xlsx
+++ b/docs/testing/OpenOKR-UAT.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Bug Log" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Cases'!$A$1:$N$222</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Bug Log'!$A$1:$M$62</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -662,7 +662,7 @@
     <row r="86">
       <c r="A86" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 194 test cases across 26 modules.</t>
+          <t xml:space="preserve">Generated from docs/testing/uat-cases.mjs and uat-guide.mjs. 195 test cases across 26 modules.</t>
         </is>
       </c>
       <c r="B86" s="10"/>
@@ -9066,7 +9066,7 @@
       </c>
       <c r="G107" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test NPS card with chip "unhealthy", 60% and "Launch recovery"</t>
+          <t xml:space="preserve">Test NPS card with chip "unhealthy", 60% and "Decide a response. Watching it is not one." over three: "Fix it now", "Add a key result", "Launch a recovery OKR"</t>
         </is>
       </c>
       <c r="H107" s="1" t="inlineStr">
@@ -9113,14 +9113,14 @@
       </c>
       <c r="F108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Launch recovery"
-2. Click it again if still visible
+          <t xml:space="preserve">1. Open "Launch a recovery OKR" and read what launching creates
+2. Click "Launch recovery"
 3. Open the new objective</t>
         </is>
       </c>
       <c r="G108" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Objective "Bring Test NPS back to 100" with one key result per leading driver. KPI chip becomes "recovering". A second launch is refused</t>
+          <t xml:space="preserve">Objective "Test NPS back where the business can rely on it", committed, with Test NPS itself as the first key result and then one per leading driver below its target. The card shows "recovering" beside "unhealthy", never in its place</t>
         </is>
       </c>
       <c r="H108" s="1" t="inlineStr">
@@ -9195,114 +9195,114 @@
       <c r="N109" s="5"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12-12</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M12 KPIs and recovery</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Answer an unhealthy KPI by fixing it now</t>
+        </is>
+      </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Priya</t>
+        </is>
+      </c>
+      <c r="E110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A second KPI at 60 of 100 on the recovery board</t>
+        </is>
+      </c>
+      <c r="F110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On its card open "Fix it now"
+2. Leave the task title, choose an owner, a due date and a space
+3. Click "Create the task"</t>
+        </is>
+      </c>
+      <c r="G110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The card shows "Being fixed now" with the task and its date, and offers the three no more. No objective was created. The task is on the board with its owner and date</t>
+        </is>
+      </c>
+      <c r="H110" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I110" s="1"/>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks: Plan the work behind key results and move it on the board. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
-      <c r="H110" s="3"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="3"/>
-      <c r="N110" s="3"/>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="inlineStr">
+      <c r="B111" s="3"/>
+      <c r="C111" s="3"/>
+      <c r="D111" s="3"/>
+      <c r="E111" s="3"/>
+      <c r="F111" s="3"/>
+      <c r="G111" s="3"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="J111" s="3"/>
+      <c r="K111" s="3"/>
+      <c r="L111" s="3"/>
+      <c r="M111" s="3"/>
+      <c r="N111" s="3"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13-01</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
+      <c r="B112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks</t>
         </is>
       </c>
-      <c r="C111" s="1" t="inlineStr">
+      <c r="C112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Add an initiative</t>
         </is>
       </c>
-      <c r="D111" s="1" t="inlineStr">
+      <c r="D112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mei</t>
         </is>
       </c>
-      <c r="E111" s="1" t="inlineStr">
+      <c r="E112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M07 done</t>
         </is>
       </c>
-      <c r="F111" s="1" t="inlineStr">
+      <c r="F112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Initiatives, click "Add" with empty fields
 2. Title Rebuild the activation flow, Space Product, Owner Mei, start and end dates, click "Add"</t>
         </is>
       </c>
-      <c r="G111" s="1" t="inlineStr">
+      <c r="G112" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Empty: "An initiative needs a title. What work is this?" Then the initiative is listed with "not yet behind a key result"</t>
-        </is>
-      </c>
-      <c r="H111" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I111" s="1"/>
-      <c r="J111" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-02</t>
-        </is>
-      </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Link an initiative to a key result</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mei</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-01 done</t>
-        </is>
-      </c>
-      <c r="F112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open the initiative
-2. In "Record this work against a key result" pick one and click "Link"
-3. Click "Unlink" then link again</t>
-        </is>
-      </c>
-      <c r="G112" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The key result is listed and can be removed and added back</t>
         </is>
       </c>
       <c r="H112" s="1" t="inlineStr">
@@ -9324,7 +9324,7 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-03</t>
+          <t xml:space="preserve">M13-02</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Over-capacity warning</t>
+          <t xml:space="preserve">Link an initiative to a key result</t>
         </is>
       </c>
       <c r="D113" s="1" t="inlineStr">
@@ -9349,17 +9349,19 @@
       </c>
       <c r="F113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set Capacity to Exceeds</t>
+          <t xml:space="preserve">1. Open the initiative
+2. In "Record this work against a key result" pick one and click "Link"
+3. Click "Unlink" then link again</t>
         </is>
       </c>
       <c r="G113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"This is over capacity, so publish gate five refuses the cycle..."</t>
+          <t xml:space="preserve">The key result is listed and can be removed and added back</t>
         </is>
       </c>
       <c r="H113" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I113" s="1"/>
@@ -9376,7 +9378,7 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-04</t>
+          <t xml:space="preserve">M13-03</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
@@ -9386,34 +9388,32 @@
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add a task on the board</t>
+          <t xml:space="preserve">Over-capacity warning</t>
         </is>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Mei</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M07 done</t>
+          <t xml:space="preserve">M13-01 done</t>
         </is>
       </c>
       <c r="F114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Board, pick Product
-2. Click "Add" with an empty title
-3. Add Rewrite the first-run screen, column To do, a key result, a due date</t>
+          <t xml:space="preserve">1. Set Capacity to Exceeds</t>
         </is>
       </c>
       <c r="G114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty: "A task needs a title. What has to happen?" Then the card is in "To do" with the key result and due date</t>
+          <t xml:space="preserve">"This is over capacity, so publish gate five refuses the cycle..."</t>
         </is>
       </c>
       <c r="H114" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I114" s="1"/>
@@ -9430,7 +9430,7 @@
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-05</t>
+          <t xml:space="preserve">M13-04</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="C115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Move a card by drag and by arrows</t>
+          <t xml:space="preserve">Add a task on the board</t>
         </is>
       </c>
       <c r="D115" s="1" t="inlineStr">
@@ -9450,18 +9450,19 @@
       </c>
       <c r="E115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-04 done</t>
+          <t xml:space="preserve">M07 done</t>
         </is>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Drag the card to "In progress"
-2. Use the arrow button to move it to "Done"</t>
+          <t xml:space="preserve">1. Open Board, pick Product
+2. Click "Add" with an empty title
+3. Add Rewrite the first-run screen, column To do, a key result, a due date</t>
         </is>
       </c>
       <c r="G115" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The card moves and the column counts change. Moving never changes key result progress</t>
+          <t xml:space="preserve">Empty: "A task needs a title. What has to happen?" Then the card is in "To do" with the key result and due date</t>
         </is>
       </c>
       <c r="H115" s="1" t="inlineStr">
@@ -9483,7 +9484,7 @@
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-06</t>
+          <t xml:space="preserve">M13-05</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
@@ -9493,32 +9494,33 @@
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The board updates live for others</t>
+          <t xml:space="preserve">Move a card by drag and by arrows</t>
         </is>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya and Sara both on the Product board</t>
+          <t xml:space="preserve">M13-04 done</t>
         </is>
       </c>
       <c r="F116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sara moves a card</t>
+          <t xml:space="preserve">1. Drag the card to "In progress"
+2. Use the arrow button to move it to "Done"</t>
         </is>
       </c>
       <c r="G116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya's board shows the move without reloading</t>
+          <t xml:space="preserve">The card moves and the column counts change. Moving never changes key result progress</t>
         </is>
       </c>
       <c r="H116" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I116" s="1"/>
@@ -9535,7 +9537,7 @@
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M13-07</t>
+          <t xml:space="preserve">M13-06</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
@@ -9545,28 +9547,27 @@
       </c>
       <c r="C117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Done work with no movement raises a warning</t>
+          <t xml:space="preserve">The board updates live for others</t>
         </is>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A key result with linked tasks and no value change</t>
+          <t xml:space="preserve">Priya and Sara both on the Product board</t>
         </is>
       </c>
       <c r="F117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Move every linked task to Done
-2. Read the rail "What this work is meant to move"</t>
+          <t xml:space="preserve">1. Sara moves a card</t>
         </is>
       </c>
       <c r="G117" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Warning that all linked tasks are complete and the measure is still at its baseline</t>
+          <t xml:space="preserve">Priya's board shows the move without reloading</t>
         </is>
       </c>
       <c r="H117" s="1" t="inlineStr">
@@ -9588,30 +9589,83 @@
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M13-07</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Done work with no movement raises a warning</t>
+        </is>
+      </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A key result with linked tasks and no value change</t>
+        </is>
+      </c>
+      <c r="F118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Move every linked task to Done
+2. Read the rail "What this work is meant to move"</t>
+        </is>
+      </c>
+      <c r="G118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warning that all linked tasks are complete and the measure is still at its baseline</t>
+        </is>
+      </c>
+      <c r="H118" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I118" s="1"/>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K118" s="5"/>
+      <c r="L118" s="5"/>
+      <c r="M118" s="5"/>
+      <c r="N118" s="5"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M13-08</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
+      <c r="B119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13 Initiatives, board and tasks</t>
         </is>
       </c>
-      <c r="C118" s="1" t="inlineStr">
+      <c r="C119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Task checklist, assignees and due date</t>
         </is>
       </c>
-      <c r="D118" s="1" t="inlineStr">
+      <c r="D119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E118" s="1" t="inlineStr">
+      <c r="E119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M13-04 done</t>
         </is>
       </c>
-      <c r="F118" s="1" t="inlineStr">
+      <c r="F119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the task
 2. Click "Add" on an empty checklist line
@@ -9619,74 +9673,21 @@
 4. Assign Mei. Change the due date</t>
         </is>
       </c>
-      <c r="G118" s="1" t="inlineStr">
+      <c r="G119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Empty: "A checklist line needs some words." Count shows "1 of 2 done". Mei is under "Assignees"</t>
         </is>
       </c>
-      <c r="H118" s="1" t="inlineStr">
+      <c r="H119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I118" s="1" t="inlineStr">
+      <c r="I119" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Tasks have no comments or files by design today</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K118" s="5"/>
-      <c r="L118" s="5"/>
-      <c r="M118" s="5"/>
-      <c r="N118" s="5"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-09</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only the admin can delete a task</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara, then Admin</t>
-        </is>
-      </c>
-      <c r="E119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M13-04 done</t>
-        </is>
-      </c>
-      <c r="F119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. As Sara open the task and look for "Delete"
-2. As Admin delete it</t>
-        </is>
-      </c>
-      <c r="G119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara sees no Delete. Admin's delete returns to the board and the card is gone</t>
-        </is>
-      </c>
-      <c r="H119" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I119" s="1"/>
       <c r="J119" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -9698,85 +9699,82 @@
       <c r="N119" s="5"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13-09</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13 Initiatives, board and tasks</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only the admin can delete a task</t>
+        </is>
+      </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, then Admin</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M13-04 done</t>
+        </is>
+      </c>
+      <c r="F120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. As Sara open the task and look for "Delete"
+2. As Admin delete it</t>
+        </is>
+      </c>
+      <c r="G120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara sees no Delete. Admin's delete returns to the board and the card is gone</t>
+        </is>
+      </c>
+      <c r="H120" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I120" s="1"/>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K120" s="5"/>
+      <c r="L120" s="5"/>
+      <c r="M120" s="5"/>
+      <c r="N120" s="5"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M14 Check-in, review and inbox: Report progress every week and have the reviewer acknowledge it. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B120" s="3"/>
-      <c r="C120" s="3"/>
-      <c r="D120" s="3"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="3"/>
-      <c r="G120" s="3"/>
-      <c r="H120" s="3"/>
-      <c r="I120" s="3"/>
-      <c r="J120" s="3"/>
-      <c r="K120" s="3"/>
-      <c r="L120" s="3"/>
-      <c r="M120" s="3"/>
-      <c r="N120" s="3"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14-01</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14 Check-in, review and inbox</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Only what is due is listed</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara champions a goal that is due</t>
-        </is>
-      </c>
-      <c r="F121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Check in</t>
-        </is>
-      </c>
-      <c r="G121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara's goal is listed. If nothing is due: "Nothing of yours is due."</t>
-        </is>
-      </c>
-      <c r="H121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I121" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A goal is due only near its next check-in date. Set Admin, Rhythm check-in frequency to daily to make it due today</t>
-        </is>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K121" s="5"/>
-      <c r="L121" s="5"/>
-      <c r="M121" s="5"/>
-      <c r="N121" s="5"/>
+      <c r="B121" s="3"/>
+      <c r="C121" s="3"/>
+      <c r="D121" s="3"/>
+      <c r="E121" s="3"/>
+      <c r="F121" s="3"/>
+      <c r="G121" s="3"/>
+      <c r="H121" s="3"/>
+      <c r="I121" s="3"/>
+      <c r="J121" s="3"/>
+      <c r="K121" s="3"/>
+      <c r="L121" s="3"/>
+      <c r="M121" s="3"/>
+      <c r="N121" s="3"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-02</t>
+          <t xml:space="preserve">M14-01</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
@@ -9786,7 +9784,7 @@
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A check-in needs a narrative</t>
+          <t xml:space="preserve">Only what is due is listed</t>
         </is>
       </c>
       <c r="D122" s="1" t="inlineStr">
@@ -9796,19 +9794,17 @@
       </c>
       <c r="E122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-01 done</t>
+          <t xml:space="preserve">Sara champions a goal that is due</t>
         </is>
       </c>
       <c r="F122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Pick the goal
-2. Set "Status" to "Caution", set confidence and new key result values
-3. Leave the narrative empty and click "Publish"</t>
+          <t xml:space="preserve">1. Open Check in</t>
         </is>
       </c>
       <c r="G122" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"A check-in needs a narrative. What moved, what is in the way, and what happens next?"</t>
+          <t xml:space="preserve">Sara's goal is listed. If nothing is due: "Nothing of yours is due."</t>
         </is>
       </c>
       <c r="H122" s="1" t="inlineStr">
@@ -9816,7 +9812,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I122" s="1"/>
+      <c r="I122" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal is due only near its next check-in date. Set Admin, Rhythm check-in frequency to daily to make it due today</t>
+        </is>
+      </c>
       <c r="J122" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -9830,7 +9830,7 @@
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-03</t>
+          <t xml:space="preserve">M14-02</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
@@ -9840,7 +9840,7 @@
       </c>
       <c r="C123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post a check-in</t>
+          <t xml:space="preserve">A check-in needs a narrative</t>
         </is>
       </c>
       <c r="D123" s="1" t="inlineStr">
@@ -9850,17 +9850,19 @@
       </c>
       <c r="E123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-02 done</t>
+          <t xml:space="preserve">M14-01 done</t>
         </is>
       </c>
       <c r="F123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Write the narrative and click "Publish"</t>
+          <t xml:space="preserve">1. Pick the goal
+2. Set "Status" to "Caution", set confidence and new key result values
+3. Leave the narrative empty and click "Publish"</t>
         </is>
       </c>
       <c r="G123" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Check-in history" shows it as "awaiting the reviewer". The goal page shows the new values</t>
+          <t xml:space="preserve">"A check-in needs a narrative. What moved, what is in the way, and what happens next?"</t>
         </is>
       </c>
       <c r="H123" s="1" t="inlineStr">
@@ -9882,7 +9884,7 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-04</t>
+          <t xml:space="preserve">M14-03</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
@@ -9892,27 +9894,27 @@
       </c>
       <c r="C124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Someone who is not the champion cannot post</t>
+          <t xml:space="preserve">Post a check-in</t>
         </is>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-03 done</t>
+          <t xml:space="preserve">M14-02 done</t>
         </is>
       </c>
       <c r="F124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Sara's goal check-ins</t>
+          <t xml:space="preserve">1. Write the narrative and click "Publish"</t>
         </is>
       </c>
       <c r="G124" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"You can read this goal's check-ins but not post one. The champion posts them."</t>
+          <t xml:space="preserve">"Check-in history" shows it as "awaiting the reviewer". The goal page shows the new values</t>
         </is>
       </c>
       <c r="H124" s="1" t="inlineStr">
@@ -9934,7 +9936,7 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-05</t>
+          <t xml:space="preserve">M14-04</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
@@ -9944,12 +9946,12 @@
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The wrong reviewer cannot acknowledge</t>
+          <t xml:space="preserve">Someone who is not the champion cannot post</t>
         </is>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mei</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E125" s="1" t="inlineStr">
@@ -9959,17 +9961,17 @@
       </c>
       <c r="F125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the check-in and try "Acknowledge"</t>
+          <t xml:space="preserve">1. Open Sara's goal check-ins</t>
         </is>
       </c>
       <c r="G125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Only this goal's reviewer can acknowledge its check-ins."</t>
+          <t xml:space="preserve">"You can read this goal's check-ins but not post one. The champion posts them."</t>
         </is>
       </c>
       <c r="H125" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I125" s="1"/>
@@ -9986,7 +9988,7 @@
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-06</t>
+          <t xml:space="preserve">M14-05</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
@@ -9996,12 +9998,12 @@
       </c>
       <c r="C126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The reviewer acknowledges from What you owe</t>
+          <t xml:space="preserve">The wrong reviewer cannot acknowledge</t>
         </is>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priya</t>
+          <t xml:space="preserve">Mei</t>
         </is>
       </c>
       <c r="E126" s="1" t="inlineStr">
@@ -10011,18 +10013,17 @@
       </c>
       <c r="F126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Review
-2. Find the check-in row and click its action</t>
+          <t xml:space="preserve">1. Open the check-in and try "Acknowledge"</t>
         </is>
       </c>
       <c r="G126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The check-in shows "acknowledged". The row leaves the list. An empty list says "You are all caught up."</t>
+          <t xml:space="preserve">"Only this goal's reviewer can acknowledge its check-ins."</t>
         </is>
       </c>
       <c r="H126" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I126" s="1"/>
@@ -10039,7 +10040,7 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-07</t>
+          <t xml:space="preserve">M14-06</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
@@ -10049,12 +10050,12 @@
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Correct a check-in inside the window</t>
+          <t xml:space="preserve">The reviewer acknowledges from What you owe</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -10064,17 +10065,18 @@
       </c>
       <c r="F127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Correct it" and change the narrative</t>
+          <t xml:space="preserve">1. Open Review
+2. Find the check-in row and click its action</t>
         </is>
       </c>
       <c r="G127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The change saves. After the window: "The window has closed; post a new one instead"</t>
+          <t xml:space="preserve">The check-in shows "acknowledged". The row leaves the list. An empty list says "You are all caught up."</t>
         </is>
       </c>
       <c r="H127" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I127" s="1"/>
@@ -10091,7 +10093,7 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-08</t>
+          <t xml:space="preserve">M14-07</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
@@ -10101,33 +10103,32 @@
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Team confidence votes reveal together</t>
+          <t xml:space="preserve">Correct a check-in inside the window</t>
         </is>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara, Priya, Mei</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-01 done</t>
+          <t xml:space="preserve">M14-03 done</t>
         </is>
       </c>
       <c r="F128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Each person clicks "Vote" on a key result
-2. Click "Reveal together"</t>
+          <t xml:space="preserve">1. Click "Correct it" and change the narrative</t>
         </is>
       </c>
       <c r="G128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before reveal each sees only "Your vote: X". After reveal all votes show</t>
+          <t xml:space="preserve">The change saves. After the window: "The window has closed; post a new one instead"</t>
         </is>
       </c>
       <c r="H128" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I128" s="1"/>
@@ -10144,30 +10145,83 @@
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M14-08</t>
+        </is>
+      </c>
+      <c r="B129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Team confidence votes reveal together</t>
+        </is>
+      </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara, Priya, Mei</t>
+        </is>
+      </c>
+      <c r="E129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14-01 done</t>
+        </is>
+      </c>
+      <c r="F129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Each person clicks "Vote" on a key result
+2. Click "Reveal together"</t>
+        </is>
+      </c>
+      <c r="G129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before reveal each sees only "Your vote: X". After reveal all votes show</t>
+        </is>
+      </c>
+      <c r="H129" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I129" s="1"/>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K129" s="5"/>
+      <c r="L129" s="5"/>
+      <c r="M129" s="5"/>
+      <c r="N129" s="5"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M14-09</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
+      <c r="B130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M14 Check-in, review and inbox</t>
         </is>
       </c>
-      <c r="C129" s="1" t="inlineStr">
+      <c r="C130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Inbox: read, filter, snooze, mute</t>
         </is>
       </c>
-      <c r="D129" s="1" t="inlineStr">
+      <c r="D130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E129" s="1" t="inlineStr">
+      <c r="E130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara has notifications (comment from M10-04)</t>
         </is>
       </c>
-      <c r="F129" s="1" t="inlineStr">
+      <c r="F130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Inbox, switch to "Unread"
 2. Click "Mark read"
@@ -10175,67 +10229,14 @@
 4. Click "Mute" on a group</t>
         </is>
       </c>
-      <c r="G129" s="1" t="inlineStr">
+      <c r="G130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Unread count drops. Snoozed item is quiet. Muted group stops notifying</t>
         </is>
       </c>
-      <c r="H129" s="1" t="inlineStr">
+      <c r="H130" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I129" s="1"/>
-      <c r="J129" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K129" s="5"/>
-      <c r="L129" s="5"/>
-      <c r="M129" s="5"/>
-      <c r="N129" s="5"/>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14-10</t>
-        </is>
-      </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M14 Check-in, review and inbox</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A snooze never hides an obligation</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya</t>
-        </is>
-      </c>
-      <c r="E130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Priya owes an acknowledgement</t>
-        </is>
-      </c>
-      <c r="F130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Snooze the related nudge in Inbox
-2. Open Review</t>
-        </is>
-      </c>
-      <c r="G130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The item is still on Review</t>
-        </is>
-      </c>
-      <c r="H130" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I130" s="1"/>
@@ -10252,7 +10253,7 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M14-11</t>
+          <t xml:space="preserve">M14-10</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
@@ -10262,40 +10263,36 @@
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal with no check-in turns Outdated</t>
+          <t xml:space="preserve">A snooze never hides an obligation</t>
         </is>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Priya</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal past its check-in grace</t>
+          <t xml:space="preserve">Priya owes an acknowledgement</t>
         </is>
       </c>
       <c r="F131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Wait for the scheduler, or ask the operator to run pnpm cadence:sweep
-2. Open the work map</t>
+          <t xml:space="preserve">1. Snooze the related nudge in Inbox
+2. Open Review</t>
         </is>
       </c>
       <c r="G131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The goal shows "Outdated", overriding its last reported health</t>
+          <t xml:space="preserve">The item is still on Review</t>
         </is>
       </c>
       <c r="H131" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I131" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Needs time or server access</t>
-        </is>
-      </c>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I131" s="1"/>
       <c r="J131" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10307,81 +10304,86 @@
       <c r="N131" s="5"/>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14-11</t>
+        </is>
+      </c>
+      <c r="B132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M14 Check-in, review and inbox</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal with no check-in turns Outdated</t>
+        </is>
+      </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A goal past its check-in grace</t>
+        </is>
+      </c>
+      <c r="F132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Wait for the scheduler, or ask the operator to run pnpm cadence:sweep
+2. Open the work map</t>
+        </is>
+      </c>
+      <c r="G132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The goal shows "Outdated", overriding its last reported health</t>
+        </is>
+      </c>
+      <c r="H132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I132" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Needs time or server access</t>
+        </is>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K132" s="5"/>
+      <c r="L132" s="5"/>
+      <c r="M132" s="5"/>
+      <c r="N132" s="5"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M15 Weekly session: Run the four-step weekly session the product facilitates. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B132" s="3"/>
-      <c r="C132" s="3"/>
-      <c r="D132" s="3"/>
-      <c r="E132" s="3"/>
-      <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="3"/>
-      <c r="J132" s="3"/>
-      <c r="K132" s="3"/>
-      <c r="L132" s="3"/>
-      <c r="M132" s="3"/>
-      <c r="N132" s="3"/>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M15-01</t>
-        </is>
-      </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M15 Weekly session</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The template session is listed</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M02-02 done</t>
-        </is>
-      </c>
-      <c r="F133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Sessions</t>
-        </is>
-      </c>
-      <c r="G133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Weekly session" under "Ahead" with chip "You facilitate" and action "Open"</t>
-        </is>
-      </c>
-      <c r="H133" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I133" s="1"/>
-      <c r="J133" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K133" s="5"/>
-      <c r="L133" s="5"/>
-      <c r="M133" s="5"/>
-      <c r="N133" s="5"/>
+      <c r="B133" s="3"/>
+      <c r="C133" s="3"/>
+      <c r="D133" s="3"/>
+      <c r="E133" s="3"/>
+      <c r="F133" s="3"/>
+      <c r="G133" s="3"/>
+      <c r="H133" s="3"/>
+      <c r="I133" s="3"/>
+      <c r="J133" s="3"/>
+      <c r="K133" s="3"/>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-02</t>
+          <t xml:space="preserve">M15-01</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
@@ -10391,7 +10393,7 @@
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Start the session</t>
+          <t xml:space="preserve">The template session is listed</t>
         </is>
       </c>
       <c r="D134" s="1" t="inlineStr">
@@ -10401,17 +10403,17 @@
       </c>
       <c r="E134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-01 done</t>
+          <t xml:space="preserve">M02-02 done</t>
         </is>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open it and click "Start session"</t>
+          <t xml:space="preserve">1. Open Sessions</t>
         </is>
       </c>
       <c r="G134" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The steps rail shows "Confidence round", "Diagnose what is low", "Commitments", "Digest"</t>
+          <t xml:space="preserve">"Weekly session" under "Ahead" with chip "You facilitate" and action "Open"</t>
         </is>
       </c>
       <c r="H134" s="1" t="inlineStr">
@@ -10433,7 +10435,7 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-03</t>
+          <t xml:space="preserve">M15-02</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
@@ -10443,29 +10445,27 @@
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Confidence round: vote, reveal, confirm</t>
+          <t xml:space="preserve">Start the session</t>
         </is>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, Priya, Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Session running</t>
+          <t xml:space="preserve">M15-01 done</t>
         </is>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Priya and Sara open the session and click "Cast vote"
-2. Admin clicks "Continue to next step" before confirming
-3. Admin clicks "Reveal votes", writes "What changed this week", clicks "Confirm confidence"</t>
+          <t xml:space="preserve">1. Open it and click "Start session"</t>
         </is>
       </c>
       <c r="G135" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Voters see "Vote cast. Waiting for reveal." Early continue: "Cannot advance: &lt;KR&gt; has no confirmed confidence." After confirming, continue works</t>
+          <t xml:space="preserve">The steps rail shows "Confidence round", "Diagnose what is low", "Commitments", "Digest"</t>
         </is>
       </c>
       <c r="H135" s="1" t="inlineStr">
@@ -10473,11 +10473,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I135" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Space members join the session. Add Priya and Sara to the session's space first</t>
-        </is>
-      </c>
+      <c r="I135" s="1"/>
       <c r="J135" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10491,7 +10487,7 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-04</t>
+          <t xml:space="preserve">M15-03</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
@@ -10501,29 +10497,29 @@
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A low key result needs a blocker</t>
+          <t xml:space="preserve">Confidence round: vote, reveal, confirm</t>
         </is>
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, Priya, Sara</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One key result confirmed below 0.4</t>
+          <t xml:space="preserve">Session running</t>
         </is>
       </c>
       <c r="F136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On "Diagnose what is low" click "Continue to next step"
-2. Click "Raise a blocker" with empty fields
-3. Fill key result, kind Dependency, owner Mei, next action, and raise it</t>
+          <t xml:space="preserve">1. Priya and Sara open the session and click "Cast vote"
+2. Admin clicks "Continue to next step" before confirming
+3. Admin clicks "Reveal votes", writes "What changed this week", clicks "Confirm confidence"</t>
         </is>
       </c>
       <c r="G136" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continue: "Cannot advance: &lt;KR&gt; scored below 0.4 and has no blocker." Empty form shows field errors. The blocker shows "&lt;h&gt;h open"</t>
+          <t xml:space="preserve">Voters see "Vote cast. Waiting for reveal." Early continue: "Cannot advance: &lt;KR&gt; has no confirmed confidence." After confirming, continue works</t>
         </is>
       </c>
       <c r="H136" s="1" t="inlineStr">
@@ -10531,7 +10527,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I136" s="1"/>
+      <c r="I136" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Space members join the session. Add Priya and Sara to the session's space first</t>
+        </is>
+      </c>
       <c r="J136" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10545,7 +10545,7 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-05</t>
+          <t xml:space="preserve">M15-04</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Resolve and reassign a blocker</t>
+          <t xml:space="preserve">A low key result needs a blocker</t>
         </is>
       </c>
       <c r="D137" s="1" t="inlineStr">
@@ -10565,24 +10565,24 @@
       </c>
       <c r="E137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-04 done</t>
+          <t xml:space="preserve">One key result confirmed below 0.4</t>
         </is>
       </c>
       <c r="F137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Use "Move it to" and "Reassign" to Sara
-2. Click "Resolve"
-3. Open the space page</t>
+          <t xml:space="preserve">1. On "Diagnose what is low" click "Continue to next step"
+2. Click "Raise a blocker" with empty fields
+3. Fill key result, kind Dependency, owner Mei, next action, and raise it</t>
         </is>
       </c>
       <c r="G137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Owner changes, then the chip says "resolved". Open blockers also appear on the space page while open</t>
+          <t xml:space="preserve">Continue: "Cannot advance: &lt;KR&gt; scored below 0.4 and has no blocker." Empty form shows field errors. The blocker shows "&lt;h&gt;h open"</t>
         </is>
       </c>
       <c r="H137" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I137" s="1"/>
@@ -10599,7 +10599,7 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-06</t>
+          <t xml:space="preserve">M15-05</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="C138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">At least two commitments</t>
+          <t xml:space="preserve">Resolve and reassign a blocker</t>
         </is>
       </c>
       <c r="D138" s="1" t="inlineStr">
@@ -10619,23 +10619,24 @@
       </c>
       <c r="E138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">On step Commitments</t>
+          <t xml:space="preserve">M15-04 done</t>
         </is>
       </c>
       <c r="F138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set one commitment and continue
-2. Add a second with "Add one more" and click "Set this week's commitments"</t>
+          <t xml:space="preserve">1. Use "Move it to" and "Reassign" to Sara
+2. Click "Resolve"
+3. Open the space page</t>
         </is>
       </c>
       <c r="G138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One: "Cannot advance: at least 2 commitments are required, but only 1 were set." Two: accepted</t>
+          <t xml:space="preserve">Owner changes, then the chip says "resolved". Open blockers also appear on the space page while open</t>
         </is>
       </c>
       <c r="H138" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I138" s="1"/>
@@ -10652,7 +10653,7 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-07</t>
+          <t xml:space="preserve">M15-06</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
@@ -10662,7 +10663,7 @@
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Digest and close</t>
+          <t xml:space="preserve">At least two commitments</t>
         </is>
       </c>
       <c r="D139" s="1" t="inlineStr">
@@ -10672,19 +10673,18 @@
       </c>
       <c r="E139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M15-06 done</t>
+          <t xml:space="preserve">On step Commitments</t>
         </is>
       </c>
       <c r="F139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Continue to "Digest"
-2. Click "Close session"
-3. Open Sessions, "Show finished"</t>
+          <t xml:space="preserve">1. Set one commitment and continue
+2. Add a second with "Add one more" and click "Set this week's commitments"</t>
         </is>
       </c>
       <c r="G139" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The session is under "Finished"</t>
+          <t xml:space="preserve">One: "Cannot advance: at least 2 commitments are required, but only 1 were set." Two: accepted</t>
         </is>
       </c>
       <c r="H139" s="1" t="inlineStr">
@@ -10704,81 +10704,83 @@
       <c r="N139" s="5"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15-07</t>
+        </is>
+      </c>
+      <c r="B140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15 Weekly session</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digest and close</t>
+        </is>
+      </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M15-06 done</t>
+        </is>
+      </c>
+      <c r="F140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Continue to "Digest"
+2. Click "Close session"
+3. Open Sessions, "Show finished"</t>
+        </is>
+      </c>
+      <c r="G140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The session is under "Finished"</t>
+        </is>
+      </c>
+      <c r="H140" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I140" s="1"/>
+      <c r="J140" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K140" s="5"/>
+      <c r="L140" s="5"/>
+      <c r="M140" s="5"/>
+      <c r="N140" s="5"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M16 Agents and nudges: Check the two agents nudge, propose and stay quiet when they should. Needs M14 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B140" s="3"/>
-      <c r="C140" s="3"/>
-      <c r="D140" s="3"/>
-      <c r="E140" s="3"/>
-      <c r="F140" s="3"/>
-      <c r="G140" s="3"/>
-      <c r="H140" s="3"/>
-      <c r="I140" s="3"/>
-      <c r="J140" s="3"/>
-      <c r="K140" s="3"/>
-      <c r="L140" s="3"/>
-      <c r="M140" s="3"/>
-      <c r="N140" s="3"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M16-01</t>
-        </is>
-      </c>
-      <c r="B141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M16 Agents and nudges</t>
-        </is>
-      </c>
-      <c r="C141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both agents are present with safe defaults</t>
-        </is>
-      </c>
-      <c r="D141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
-        </is>
-      </c>
-      <c r="G141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OKR Champion "On the hour", propose. OKR Coach "On every write", propose. Both "On". Chip "Deterministic only" with AI off</t>
-        </is>
-      </c>
-      <c r="H141" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I141" s="1"/>
-      <c r="J141" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K141" s="5"/>
-      <c r="L141" s="5"/>
-      <c r="M141" s="5"/>
-      <c r="N141" s="5"/>
+      <c r="B141" s="3"/>
+      <c r="C141" s="3"/>
+      <c r="D141" s="3"/>
+      <c r="E141" s="3"/>
+      <c r="F141" s="3"/>
+      <c r="G141" s="3"/>
+      <c r="H141" s="3"/>
+      <c r="I141" s="3"/>
+      <c r="J141" s="3"/>
+      <c r="K141" s="3"/>
+      <c r="L141" s="3"/>
+      <c r="M141" s="3"/>
+      <c r="N141" s="3"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-02</t>
+          <t xml:space="preserve">M16-01</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
@@ -10788,7 +10790,7 @@
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run an agent now</t>
+          <t xml:space="preserve">Both agents are present with safe defaults</t>
         </is>
       </c>
       <c r="D142" s="1" t="inlineStr">
@@ -10803,12 +10805,12 @@
       </c>
       <c r="F142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In "Run one now" click "Nudge queue", then "Daily sweep", then "Quality pass"</t>
+          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
         </is>
       </c>
       <c r="G142" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Each run appears under "Recent runs" as completed, with a log. A run with nothing to do says "Nothing was due."</t>
+          <t xml:space="preserve">OKR Champion "On the hour", propose. OKR Coach "On every write", propose. Both "On". Chip "Deterministic only" with AI off</t>
         </is>
       </c>
       <c r="H142" s="1" t="inlineStr">
@@ -10830,7 +10832,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-03</t>
+          <t xml:space="preserve">M16-02</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
@@ -10840,7 +10842,7 @@
       </c>
       <c r="C143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Approve and dismiss proposals</t>
+          <t xml:space="preserve">Run an agent now</t>
         </is>
       </c>
       <c r="D143" s="1" t="inlineStr">
@@ -10850,18 +10852,17 @@
       </c>
       <c r="E143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Proposals waiting" has items (run the Coach after M09)</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tick one proposal, click "Apply 1"
-2. Tick another, click "Dismiss"</t>
+          <t xml:space="preserve">1. In "Run one now" click "Nudge queue", then "Daily sweep", then "Quality pass"</t>
         </is>
       </c>
       <c r="G143" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Applied 1 of 1." and "Dismissed 1." The applied change is visible on the goal</t>
+          <t xml:space="preserve">Each run appears under "Recent runs" as completed, with a log. A run with nothing to do says "Nothing was due."</t>
         </is>
       </c>
       <c r="H143" s="1" t="inlineStr">
@@ -10869,11 +10870,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I143" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Members see proposals on Review with a link to Admin, Agents, which they cannot open. Record what a member sees</t>
-        </is>
-      </c>
+      <c r="I143" s="1"/>
       <c r="J143" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10887,7 +10884,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-04</t>
+          <t xml:space="preserve">M16-03</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
@@ -10897,7 +10894,7 @@
       </c>
       <c r="C144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sandbox commits nothing</t>
+          <t xml:space="preserve">Approve and dismiss proposals</t>
         </is>
       </c>
       <c r="D144" s="1" t="inlineStr">
@@ -10907,27 +10904,30 @@
       </c>
       <c r="E144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">"Proposals waiting" has items (run the Coach after M09)</t>
         </is>
       </c>
       <c r="F144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set the Coach "Write policy" to "Sandbox"
-2. Run "Quality pass"
-3. Set it back to "Propose"</t>
+          <t xml:space="preserve">1. Tick one proposal, click "Apply 1"
+2. Tick another, click "Dismiss"</t>
         </is>
       </c>
       <c r="G144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The run is logged. No proposal and no change is written</t>
+          <t xml:space="preserve">"Applied 1 of 1." and "Dismissed 1." The applied change is visible on the goal</t>
         </is>
       </c>
       <c r="H144" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I144" s="1"/>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I144" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Members see proposals on Review with a link to Admin, Agents, which they cannot open. Record what a member sees</t>
+        </is>
+      </c>
       <c r="J144" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -10941,7 +10941,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-05</t>
+          <t xml:space="preserve">M16-04</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="C145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Direct writes ask for confirmation</t>
+          <t xml:space="preserve">Sandbox commits nothing</t>
         </is>
       </c>
       <c r="D145" s="1" t="inlineStr">
@@ -10966,13 +10966,14 @@
       </c>
       <c r="F145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Scoped direct" on the Champion
-2. Cancel the dialog</t>
+          <t xml:space="preserve">1. Set the Coach "Write policy" to "Sandbox"
+2. Run "Quality pass"
+3. Set it back to "Propose"</t>
         </is>
       </c>
       <c r="G145" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dialog "Let OKR Champion write directly?". After cancel the policy is still propose</t>
+          <t xml:space="preserve">The run is logged. No proposal and no change is written</t>
         </is>
       </c>
       <c r="H145" s="1" t="inlineStr">
@@ -10994,7 +10995,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-06</t>
+          <t xml:space="preserve">M16-05</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
@@ -11004,7 +11005,7 @@
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn an agent off and on</t>
+          <t xml:space="preserve">Direct writes ask for confirmation</t>
         </is>
       </c>
       <c r="D146" s="1" t="inlineStr">
@@ -11019,13 +11020,13 @@
       </c>
       <c r="F146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Turn off" on the Coach and confirm
-2. Click "Turn on"</t>
+          <t xml:space="preserve">1. Click "Scoped direct" on the Champion
+2. Cancel the dialog</t>
         </is>
       </c>
       <c r="G146" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chip switches to "Off" and back to "On"</t>
+          <t xml:space="preserve">Dialog "Let OKR Champion write directly?". After cancel the policy is still propose</t>
         </is>
       </c>
       <c r="H146" s="1" t="inlineStr">
@@ -11047,7 +11048,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-07</t>
+          <t xml:space="preserve">M16-06</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
@@ -11057,33 +11058,33 @@
       </c>
       <c r="C147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A nudge reaches the member</t>
+          <t xml:space="preserve">Turn an agent off and on</t>
         </is>
       </c>
       <c r="D147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara owes a check-in</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Admin runs "Nudge queue"
-2. Sara opens Inbox</t>
+          <t xml:space="preserve">1. Click "Turn off" on the Coach and confirm
+2. Click "Turn on"</t>
         </is>
       </c>
       <c r="G147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A reminder line "Reminder: &lt;rule&gt;" is in Sara's Inbox</t>
+          <t xml:space="preserve">The chip switches to "Off" and back to "On"</t>
         </is>
       </c>
       <c r="H147" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I147" s="1"/>
@@ -11100,7 +11101,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-08</t>
+          <t xml:space="preserve">M16-07</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
@@ -11110,28 +11111,28 @@
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">One nudge per subject per day</t>
+          <t xml:space="preserve">A nudge reaches the member</t>
         </is>
       </c>
       <c r="D148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-07 done</t>
+          <t xml:space="preserve">Sara owes a check-in</t>
         </is>
       </c>
       <c r="F148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Run "Nudge queue" again
-2. Open Admin, Nudge volume</t>
+          <t xml:space="preserve">1. Admin runs "Nudge queue"
+2. Sara opens Inbox</t>
         </is>
       </c>
       <c r="G148" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara gets no second copy. "Why it stayed quiet" counts "Already said today"</t>
+          <t xml:space="preserve">A reminder line "Reminder: &lt;rule&gt;" is in Sara's Inbox</t>
         </is>
       </c>
       <c r="H148" s="1" t="inlineStr">
@@ -11153,7 +11154,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-09</t>
+          <t xml:space="preserve">M16-08</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
@@ -11163,29 +11164,28 @@
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Quiet hours hold nudges</t>
+          <t xml:space="preserve">One nudge per subject per day</t>
         </is>
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara, then Admin</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">M16-07 done</t>
         </is>
       </c>
       <c r="F149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Sara sets "Quiet hours" to cover the current time on Account, Where to reach you, and saves
-2. Admin runs "Nudge queue"
-3. Admin opens Nudge volume</t>
+          <t xml:space="preserve">1. Run "Nudge queue" again
+2. Open Admin, Nudge volume</t>
         </is>
       </c>
       <c r="G149" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No new nudge for Sara. The reason "Quiet hours" is counted</t>
+          <t xml:space="preserve">Sara gets no second copy. "Why it stayed quiet" counts "Already said today"</t>
         </is>
       </c>
       <c r="H149" s="1" t="inlineStr">
@@ -11207,7 +11207,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-10</t>
+          <t xml:space="preserve">M16-09</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
@@ -11217,12 +11217,12 @@
       </c>
       <c r="C150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Turn a nudge rule off</t>
+          <t xml:space="preserve">Quiet hours hold nudges</t>
         </is>
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara, then Admin</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -11232,19 +11232,19 @@
       </c>
       <c r="F150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Nudge volume, "Rules (n)"
-2. Click "Turn off" on a rule
-3. Run "Nudge queue"</t>
+          <t xml:space="preserve">1. Sara sets "Quiet hours" to cover the current time on Account, Where to reach you, and saves
+2. Admin runs "Nudge queue"
+3. Admin opens Nudge volume</t>
         </is>
       </c>
       <c r="G150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The rule shows as changed. Its nudges are held with "Rule switched off"</t>
+          <t xml:space="preserve">No new nudge for Sara. The reason "Quiet hours" is counted</t>
         </is>
       </c>
       <c r="H150" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I150" s="1"/>
@@ -11261,7 +11261,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M16-11</t>
+          <t xml:space="preserve">M16-10</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
@@ -11271,27 +11271,29 @@
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The Coach strip on a goal</t>
+          <t xml:space="preserve">Turn a nudge rule off</t>
         </is>
       </c>
       <c r="D151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M09 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Sara's goal</t>
+          <t xml:space="preserve">1. Open Admin, Nudge volume, "Rules (n)"
+2. Click "Turn off" on a rule
+3. Run "Nudge queue"</t>
         </is>
       </c>
       <c r="G151" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"What the Coach sees" lists the rules the goal still breaks</t>
+          <t xml:space="preserve">The rule shows as changed. Its nudges are held with "Rule switched off"</t>
         </is>
       </c>
       <c r="H151" s="1" t="inlineStr">
@@ -11311,115 +11313,113 @@
       <c r="N151" s="5"/>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16-11</t>
+        </is>
+      </c>
+      <c r="B152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M16 Agents and nudges</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The Coach strip on a goal</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M09 done</t>
+        </is>
+      </c>
+      <c r="F152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Sara's goal</t>
+        </is>
+      </c>
+      <c r="G152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"What the Coach sees" lists the rules the goal still breaks</t>
+        </is>
+      </c>
+      <c r="H152" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I152" s="1"/>
+      <c r="J152" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K152" s="5"/>
+      <c r="L152" s="5"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M17 Work map, search and activity: Check the overview screens, search and basic usability. Needs M15 first. About 20 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B152" s="3"/>
-      <c r="C152" s="3"/>
-      <c r="D152" s="3"/>
-      <c r="E152" s="3"/>
-      <c r="F152" s="3"/>
-      <c r="G152" s="3"/>
-      <c r="H152" s="3"/>
-      <c r="I152" s="3"/>
-      <c r="J152" s="3"/>
-      <c r="K152" s="3"/>
-      <c r="L152" s="3"/>
-      <c r="M152" s="3"/>
-      <c r="N152" s="3"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="1" t="inlineStr">
+      <c r="B153" s="3"/>
+      <c r="C153" s="3"/>
+      <c r="D153" s="3"/>
+      <c r="E153" s="3"/>
+      <c r="F153" s="3"/>
+      <c r="G153" s="3"/>
+      <c r="H153" s="3"/>
+      <c r="I153" s="3"/>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="3"/>
+      <c r="M153" s="3"/>
+      <c r="N153" s="3"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M17-01</t>
         </is>
       </c>
-      <c r="B153" s="1" t="inlineStr">
+      <c r="B154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M17 Work map, search and activity</t>
         </is>
       </c>
-      <c r="C153" s="1" t="inlineStr">
+      <c r="C154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Work map context strip and table</t>
         </is>
       </c>
-      <c r="D153" s="1" t="inlineStr">
+      <c r="D154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Priya</t>
         </is>
       </c>
-      <c r="E153" s="1" t="inlineStr">
+      <c r="E154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M11 done</t>
         </is>
       </c>
-      <c r="F153" s="1" t="inlineStr">
+      <c r="F154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the work map
 2. Switch the scope tabs Company and each space
 3. Click a row, then "Open the goal"</t>
         </is>
       </c>
-      <c r="G153" s="1" t="inlineStr">
+      <c r="G154" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Strip shows "Phase n" and the gate status. Columns Goal, Health, Confidence, Progress, Next step, Champion. The row panel opens the goal</t>
-        </is>
-      </c>
-      <c r="H153" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I153" s="1"/>
-      <c r="J153" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K153" s="5"/>
-      <c r="L153" s="5"/>
-      <c r="M153" s="5"/>
-      <c r="N153" s="5"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M17-02</t>
-        </is>
-      </c>
-      <c r="B154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M17 Work map, search and activity</t>
-        </is>
-      </c>
-      <c r="C154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Search finds only what you may open</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Jonas</t>
-        </is>
-      </c>
-      <c r="E154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M10 done</t>
-        </is>
-      </c>
-      <c r="F154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Search, type onboarding
-2. Switch the type tabs
-3. Type zzzz</t>
-        </is>
-      </c>
-      <c r="G154" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Results group by type. zzzz shows "Nothing matches". Sara's draft document never appears</t>
         </is>
       </c>
       <c r="H154" s="1" t="inlineStr">
@@ -11441,7 +11441,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-03</t>
+          <t xml:space="preserve">M17-02</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
@@ -11451,33 +11451,34 @@
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Activity feed</t>
+          <t xml:space="preserve">Search finds only what you may open</t>
         </is>
       </c>
       <c r="D155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work done in earlier modules</t>
+          <t xml:space="preserve">M10 done</t>
         </is>
       </c>
       <c r="F155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Activity
-2. Click "Older" then "Back to the newest"</t>
+          <t xml:space="preserve">1. Open Search, type onboarding
+2. Switch the type tabs
+3. Type zzzz</t>
         </is>
       </c>
       <c r="G155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check-ins, goals, sessions and setting changes are listed newest first</t>
+          <t xml:space="preserve">Results group by type. zzzz shows "Nothing matches". Sara's draft document never appears</t>
         </is>
       </c>
       <c r="H155" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I155" s="1"/>
@@ -11494,7 +11495,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-04</t>
+          <t xml:space="preserve">M17-03</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
@@ -11504,28 +11505,28 @@
       </c>
       <c r="C156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot with AI off</t>
+          <t xml:space="preserve">Activity feed</t>
         </is>
       </c>
       <c r="D156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No AI provider</t>
+          <t xml:space="preserve">Work done in earlier modules</t>
         </is>
       </c>
       <c r="F156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Ask the copilot" (or Ctrl+J)
-2. Ask: which key results are at risk</t>
+          <t xml:space="preserve">1. Open Activity
+2. Click "Older" then "Back to the newest"</t>
         </is>
       </c>
       <c r="G156" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chip "AI off". Only "Passages that match" is shown. No error</t>
+          <t xml:space="preserve">Check-ins, goals, sessions and setting changes are listed newest first</t>
         </is>
       </c>
       <c r="H156" s="1" t="inlineStr">
@@ -11547,7 +11548,7 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-05</t>
+          <t xml:space="preserve">M17-04</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
@@ -11557,7 +11558,7 @@
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Keyboard-only check-in</t>
+          <t xml:space="preserve">Copilot with AI off</t>
         </is>
       </c>
       <c r="D157" s="1" t="inlineStr">
@@ -11567,17 +11568,18 @@
       </c>
       <c r="E157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal is due</t>
+          <t xml:space="preserve">No AI provider</t>
         </is>
       </c>
       <c r="F157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Using only Tab, Shift+Tab, Enter and arrows, post a check-in</t>
+          <t xml:space="preserve">1. Click "Ask the copilot" (or Ctrl+J)
+2. Ask: which key results are at risk</t>
         </is>
       </c>
       <c r="G157" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every control is reachable and the focus is visible</t>
+          <t xml:space="preserve">Chip "AI off". Only "Passages that match" is shown. No error</t>
         </is>
       </c>
       <c r="H157" s="1" t="inlineStr">
@@ -11599,7 +11601,7 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M17-06</t>
+          <t xml:space="preserve">M17-05</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
@@ -11609,7 +11611,7 @@
       </c>
       <c r="C158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phone-width layout</t>
+          <t xml:space="preserve">Keyboard-only check-in</t>
         </is>
       </c>
       <c r="D158" s="1" t="inlineStr">
@@ -11619,17 +11621,17 @@
       </c>
       <c r="E158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">A goal is due</t>
         </is>
       </c>
       <c r="F158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the work map, Check in and Board on a phone or a 375px-wide window</t>
+          <t xml:space="preserve">1. Using only Tab, Shift+Tab, Enter and arrows, post a check-in</t>
         </is>
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">No sideways page scroll. Every button can be tapped</t>
+          <t xml:space="preserve">Every control is reachable and the focus is visible</t>
         </is>
       </c>
       <c r="H158" s="1" t="inlineStr">
@@ -11649,113 +11651,112 @@
       <c r="N158" s="5"/>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M17-06</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M17 Work map, search and activity</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phone-width layout</t>
+        </is>
+      </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara</t>
+        </is>
+      </c>
+      <c r="E159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open the work map, Check in and Board on a phone or a 375px-wide window</t>
+        </is>
+      </c>
+      <c r="G159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No sideways page scroll. Every button can be tapped</t>
+        </is>
+      </c>
+      <c r="H159" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I159" s="1"/>
+      <c r="J159" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K159" s="5"/>
+      <c r="L159" s="5"/>
+      <c r="M159" s="5"/>
+      <c r="N159" s="5"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard: Close goals and the quarter, and record the result. Needs M15 first. About 25 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B159" s="3"/>
-      <c r="C159" s="3"/>
-      <c r="D159" s="3"/>
-      <c r="E159" s="3"/>
-      <c r="F159" s="3"/>
-      <c r="G159" s="3"/>
-      <c r="H159" s="3"/>
-      <c r="I159" s="3"/>
-      <c r="J159" s="3"/>
-      <c r="K159" s="3"/>
-      <c r="L159" s="3"/>
-      <c r="M159" s="3"/>
-      <c r="N159" s="3"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="1" t="inlineStr">
+      <c r="B160" s="3"/>
+      <c r="C160" s="3"/>
+      <c r="D160" s="3"/>
+      <c r="E160" s="3"/>
+      <c r="F160" s="3"/>
+      <c r="G160" s="3"/>
+      <c r="H160" s="3"/>
+      <c r="I160" s="3"/>
+      <c r="J160" s="3"/>
+      <c r="K160" s="3"/>
+      <c r="L160" s="3"/>
+      <c r="M160" s="3"/>
+      <c r="N160" s="3"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18-01</t>
         </is>
       </c>
-      <c r="B160" s="1" t="inlineStr">
+      <c r="B161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
         </is>
       </c>
-      <c r="C160" s="1" t="inlineStr">
+      <c r="C161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Closing a goal needs a retrospective</t>
         </is>
       </c>
-      <c r="D160" s="1" t="inlineStr">
+      <c r="D161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E160" s="1" t="inlineStr">
+      <c r="E161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A published goal</t>
         </is>
       </c>
-      <c r="F160" s="1" t="inlineStr">
+      <c r="F161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open the goal, pick "Achieved" and "Keep"
 2. Leave the retrospective empty and click "Close this goal"</t>
         </is>
       </c>
-      <c r="G160" s="1" t="inlineStr">
+      <c r="G161" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Closing a goal needs a retrospective. What happened, and what would you do differently?"</t>
-        </is>
-      </c>
-      <c r="H160" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I160" s="1"/>
-      <c r="J160" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K160" s="5"/>
-      <c r="L160" s="5"/>
-      <c r="M160" s="5"/>
-      <c r="N160" s="5"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-02</t>
-        </is>
-      </c>
-      <c r="B161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
-        </is>
-      </c>
-      <c r="C161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Close and reopen a goal</t>
-        </is>
-      </c>
-      <c r="D161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara</t>
-        </is>
-      </c>
-      <c r="E161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-01 done</t>
-        </is>
-      </c>
-      <c r="F161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Write the retrospective and close
-2. Click "Reopen this goal"</t>
-        </is>
-      </c>
-      <c r="G161" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Header shows "closed · achieved" and "No check-in is due. A closed goal never is." Reopen returns it to open</t>
         </is>
       </c>
       <c r="H161" s="1" t="inlineStr">
@@ -11777,7 +11778,7 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M18-03</t>
+          <t xml:space="preserve">M18-02</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
@@ -11787,29 +11788,28 @@
       </c>
       <c r="C162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Phase 7 Review and learn, and close the cycle</t>
+          <t xml:space="preserve">Close and reopen a goal</t>
         </is>
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A quarterly review of the current cycle is running</t>
+          <t xml:space="preserve">M18-01 done</t>
         </is>
       </c>
       <c r="F162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 7, before any key result is scored
-2. Score every key result and write the team retro in the quarterly review, then close the review
-3. Back on phase 7, click "Close &lt;cycle name&gt;"</t>
+          <t xml:space="preserve">1. Write the retrospective and close
+2. Click "Reopen this goal"</t>
         </is>
       </c>
       <c r="G162" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Before scoring, "Close the cycle" is disabled and lists what phase 7 still needs. After scoring, the portfolio average and bands show and phase 7 shows done. After closing, the chip reads "closed" and "How this cycle closed" shows the result and verdict, and says the next cycle receives the inheritance when it is created</t>
+          <t xml:space="preserve">Header shows "closed · achieved" and "No check-in is due. A closed goal never is." Reopen returns it to open</t>
         </is>
       </c>
       <c r="H162" s="1" t="inlineStr">
@@ -11831,30 +11831,84 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M18-03</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Phase 7 Review and learn, and close the cycle</t>
+        </is>
+      </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A quarterly review of the current cycle is running</t>
+        </is>
+      </c>
+      <c r="F163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Cycle, phase 7, before any key result is scored
+2. Score every key result and write the team retro in the quarterly review, then close the review
+3. Back on phase 7, click "Close &lt;cycle name&gt;"</t>
+        </is>
+      </c>
+      <c r="G163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Before scoring, "Close the cycle" is disabled and lists what phase 7 still needs. After scoring, the portfolio average and bands show and phase 7 shows done. After closing, the chip reads "closed" and "How this cycle closed" shows the result and verdict, and says the next cycle receives the inheritance when it is created</t>
+        </is>
+      </c>
+      <c r="H163" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I163" s="1"/>
+      <c r="J163" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K163" s="5"/>
+      <c r="L163" s="5"/>
+      <c r="M163" s="5"/>
+      <c r="N163" s="5"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M18-04</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
+      <c r="B164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The closed cycle on the scorecard and in the next quarter</t>
         </is>
       </c>
-      <c r="D163" s="1" t="inlineStr">
+      <c r="D164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E163" s="1" t="inlineStr">
+      <c r="E164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M18-03 done</t>
         </is>
       </c>
-      <c r="F163" s="1" t="inlineStr">
+      <c r="F164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Scorecard
 2. Check "Close a cycle out" no longer offers the closed cycle
@@ -11863,61 +11917,9 @@
 5. Click "Export as CSV" on the scorecard</t>
         </is>
       </c>
-      <c r="G163" s="1" t="inlineStr">
+      <c r="G164" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The closed cycle's row shows result and verdict. Phase 2 lists every prior score and each carried item at impact 4. Phase 3 lists the lowest process-health statement as a priority, not as an issue. The CSV downloads and opens</t>
-        </is>
-      </c>
-      <c r="H163" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I163" s="1"/>
-      <c r="J163" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K163" s="5"/>
-      <c r="L163" s="5"/>
-      <c r="M163" s="5"/>
-      <c r="N163" s="5"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-05</t>
-        </is>
-      </c>
-      <c r="B164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
-        </is>
-      </c>
-      <c r="C164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Archive the old cycle</t>
-        </is>
-      </c>
-      <c r="D164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M18-04 done</t>
-        </is>
-      </c>
-      <c r="F164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. On the Cycles card click "Archive &lt;name&gt;"</t>
-        </is>
-      </c>
-      <c r="G164" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The cycle is archived and the next one becomes current</t>
         </is>
       </c>
       <c r="H164" s="1" t="inlineStr">
@@ -11939,7 +11941,7 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M18-06</t>
+          <t xml:space="preserve">M18-05</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
@@ -11949,7 +11951,7 @@
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Run a quarterly review session</t>
+          <t xml:space="preserve">Archive the old cycle</t>
         </is>
       </c>
       <c r="D165" s="1" t="inlineStr">
@@ -11959,17 +11961,17 @@
       </c>
       <c r="E165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">End of cycle</t>
+          <t xml:space="preserve">M18-04 done</t>
         </is>
       </c>
       <c r="F165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Look on Sessions and on the space page for a way to schedule a quarterly review</t>
+          <t xml:space="preserve">1. On the Cycles card click "Archive &lt;name&gt;"</t>
         </is>
       </c>
       <c r="G165" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A quarterly review with 11 stages can be scheduled and run, then "The minutes" can be downloaded as Markdown and PDF</t>
+          <t xml:space="preserve">The cycle is archived and the next one becomes current</t>
         </is>
       </c>
       <c r="H165" s="1" t="inlineStr">
@@ -11977,11 +11979,7 @@
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I165" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Code review found no UI to create a session. If there is none, mark Blocked and log it</t>
-        </is>
-      </c>
+      <c r="I165" s="1"/>
       <c r="J165" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -11993,124 +11991,128 @@
       <c r="N165" s="5"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18-06</t>
+        </is>
+      </c>
+      <c r="B166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M18 Closing the cycle and scorecard</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run a quarterly review session</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">End of cycle</t>
+        </is>
+      </c>
+      <c r="F166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Look on Sessions and on the space page for a way to schedule a quarterly review</t>
+        </is>
+      </c>
+      <c r="G166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A quarterly review with 11 stages can be scheduled and run, then "The minutes" can be downloaded as Markdown and PDF</t>
+        </is>
+      </c>
+      <c r="H166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I166" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Code review found no UI to create a session. If there is none, mark Blocked and log it</t>
+        </is>
+      </c>
+      <c r="J166" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K166" s="5"/>
+      <c r="L166" s="5"/>
+      <c r="M166" s="5"/>
+      <c r="N166" s="5"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M19 Access and permissions: Check nobody sees or does more than their access allows. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B166" s="3"/>
-      <c r="C166" s="3"/>
-      <c r="D166" s="3"/>
-      <c r="E166" s="3"/>
-      <c r="F166" s="3"/>
-      <c r="G166" s="3"/>
-      <c r="H166" s="3"/>
-      <c r="I166" s="3"/>
-      <c r="J166" s="3"/>
-      <c r="K166" s="3"/>
-      <c r="L166" s="3"/>
-      <c r="M166" s="3"/>
-      <c r="N166" s="3"/>
-    </row>
-    <row r="167">
-      <c r="A167" s="1" t="inlineStr">
+      <c r="B167" s="3"/>
+      <c r="C167" s="3"/>
+      <c r="D167" s="3"/>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3"/>
+      <c r="G167" s="3"/>
+      <c r="H167" s="3"/>
+      <c r="I167" s="3"/>
+      <c r="J167" s="3"/>
+      <c r="K167" s="3"/>
+      <c r="L167" s="3"/>
+      <c r="M167" s="3"/>
+      <c r="N167" s="3"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M19-01</t>
         </is>
       </c>
-      <c r="B167" s="1" t="inlineStr">
+      <c r="B168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M19 Access and permissions</t>
         </is>
       </c>
-      <c r="C167" s="1" t="inlineStr">
+      <c r="C168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A member cannot open admin screens</t>
         </is>
       </c>
-      <c r="D167" s="1" t="inlineStr">
+      <c r="D168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Jonas</t>
         </is>
       </c>
-      <c r="E167" s="1" t="inlineStr">
+      <c r="E168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F167" s="1" t="inlineStr">
+      <c r="F168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open /admin/general
 2. Open /admin/agents</t>
         </is>
       </c>
-      <c r="G167" s="1" t="inlineStr">
+      <c r="G168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Both return a Not Found page. No admin data is shown</t>
         </is>
       </c>
-      <c r="H167" s="1" t="inlineStr">
+      <c r="H168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I167" s="1" t="inlineStr">
+      <c r="I168" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The product answers 404 on purpose, so the page's existence is not revealed</t>
         </is>
       </c>
-      <c r="J167" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K167" s="5"/>
-      <c r="L167" s="5"/>
-      <c r="M167" s="5"/>
-      <c r="N167" s="5"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M19-02</t>
-        </is>
-      </c>
-      <c r="B168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M19 Access and permissions</t>
-        </is>
-      </c>
-      <c r="C168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Signed-out visitors are sent to sign-in</t>
-        </is>
-      </c>
-      <c r="D168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nobody (signed out)</t>
-        </is>
-      </c>
-      <c r="E168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open /goals and /kpis</t>
-        </is>
-      </c>
-      <c r="G168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Redirected to /sign-in</t>
-        </is>
-      </c>
-      <c r="H168" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I168" s="1"/>
       <c r="J168" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12124,7 +12126,7 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-03</t>
+          <t xml:space="preserve">M19-02</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
@@ -12134,27 +12136,27 @@
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A goal you cannot see reads as not found</t>
+          <t xml:space="preserve">Signed-out visitors are sent to sign-in</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Nobody (signed out)</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The URL of a goal Jonas has no access to, or a made-up id</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open /goals/&lt;id&gt;</t>
+          <t xml:space="preserve">1. Open /goals and /kpis</t>
         </is>
       </c>
       <c r="G169" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"We could not find that, or it is not yours to see."</t>
+          <t xml:space="preserve">Redirected to /sign-in</t>
         </is>
       </c>
       <c r="H169" s="1" t="inlineStr">
@@ -12176,7 +12178,7 @@
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-04</t>
+          <t xml:space="preserve">M19-03</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
@@ -12186,33 +12188,32 @@
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert a member to a guest</t>
+          <t xml:space="preserve">A goal you cannot see reads as not found</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Amara</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">The URL of a goal Jonas has no access to, or a made-up id</t>
         </is>
       </c>
       <c r="F170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Amara's profile click "Convert to a guest"
-2. As Amara browse the work map, Goals and Spaces</t>
+          <t xml:space="preserve">1. Open /goals/&lt;id&gt;</t>
         </is>
       </c>
       <c r="G170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amara shows the badge "Guest" and sees less than before. Write down what Amara can still see</t>
+          <t xml:space="preserve">"We could not find that, or it is not yours to see."</t>
         </is>
       </c>
       <c r="H170" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I170" s="1"/>
@@ -12229,7 +12230,7 @@
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M19-05</t>
+          <t xml:space="preserve">M19-04</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
@@ -12239,29 +12240,28 @@
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erase a member</t>
+          <t xml:space="preserve">Convert a member to a guest</t>
         </is>
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, then Amara</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Test Leaver from M04-02</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On their profile click "Erase this member"
-2. Type their name to confirm
-3. Click "Download the erasure export"</t>
+          <t xml:space="preserve">1. On Amara's profile click "Convert to a guest"
+2. As Amara browse the work map, Goals and Spaces</t>
         </is>
       </c>
       <c r="G171" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The member is erased and the export downloads</t>
+          <t xml:space="preserve">Amara shows the badge "Guest" and sees less than before. Write down what Amara can still see</t>
         </is>
       </c>
       <c r="H171" s="1" t="inlineStr">
@@ -12269,11 +12269,7 @@
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I171" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Irreversible. Never use one of the seven personas</t>
-        </is>
-      </c>
+      <c r="I171" s="1"/>
       <c r="J171" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12285,125 +12281,131 @@
       <c r="N171" s="5"/>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M19-05</t>
+        </is>
+      </c>
+      <c r="B172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M19 Access and permissions</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erase a member</t>
+        </is>
+      </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Test Leaver from M04-02</t>
+        </is>
+      </c>
+      <c r="F172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On their profile click "Erase this member"
+2. Type their name to confirm
+3. Click "Download the erasure export"</t>
+        </is>
+      </c>
+      <c r="G172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The member is erased and the export downloads</t>
+        </is>
+      </c>
+      <c r="H172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I172" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Irreversible. Never use one of the seven personas</t>
+        </is>
+      </c>
+      <c r="J172" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K172" s="5"/>
+      <c r="L172" s="5"/>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M20 AI provider and copilot: Turn AI on and check it drafts while a person decides. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B172" s="3"/>
-      <c r="C172" s="3"/>
-      <c r="D172" s="3"/>
-      <c r="E172" s="3"/>
-      <c r="F172" s="3"/>
-      <c r="G172" s="3"/>
-      <c r="H172" s="3"/>
-      <c r="I172" s="3"/>
-      <c r="J172" s="3"/>
-      <c r="K172" s="3"/>
-      <c r="L172" s="3"/>
-      <c r="M172" s="3"/>
-      <c r="N172" s="3"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="1" t="inlineStr">
+      <c r="B173" s="3"/>
+      <c r="C173" s="3"/>
+      <c r="D173" s="3"/>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3"/>
+      <c r="G173" s="3"/>
+      <c r="H173" s="3"/>
+      <c r="I173" s="3"/>
+      <c r="J173" s="3"/>
+      <c r="K173" s="3"/>
+      <c r="L173" s="3"/>
+      <c r="M173" s="3"/>
+      <c r="N173" s="3"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M20-01</t>
         </is>
       </c>
-      <c r="B173" s="1" t="inlineStr">
+      <c r="B174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M20 AI provider and copilot</t>
         </is>
       </c>
-      <c r="C173" s="1" t="inlineStr">
+      <c r="C174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connect an AI provider</t>
         </is>
       </c>
-      <c r="D173" s="1" t="inlineStr">
+      <c r="D174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E173" s="1" t="inlineStr">
+      <c r="E174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An API key from Anthropic, OpenAI, Google, OpenRouter, or a local Ollama</t>
         </is>
       </c>
-      <c r="F173" s="1" t="inlineStr">
+      <c r="F174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, AI
 2. On the provider card tick "Use this provider" and click "Save"
 3. Paste the key and click "Store"</t>
         </is>
       </c>
-      <c r="G173" s="1" t="inlineStr">
+      <c r="G174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Key chip shows "verified". The header counts 1 configured</t>
         </is>
       </c>
-      <c r="H173" s="1" t="inlineStr">
+      <c r="H174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I173" s="1" t="inlineStr">
+      <c r="I174" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Use a key with a small spend limit. Never paste the key into the spreadsheet</t>
         </is>
       </c>
-      <c r="J173" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K173" s="5"/>
-      <c r="L173" s="5"/>
-      <c r="M173" s="5"/>
-      <c r="N173" s="5"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M20-02</t>
-        </is>
-      </c>
-      <c r="B174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M20 AI provider and copilot</t>
-        </is>
-      </c>
-      <c r="C174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A bad key is marked invalid</t>
-        </is>
-      </c>
-      <c r="D174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Click "Replace" and store a wrong key</t>
-        </is>
-      </c>
-      <c r="G174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Key chip shows "invalid"</t>
-        </is>
-      </c>
-      <c r="H174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I174" s="1"/>
       <c r="J174" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12417,7 +12419,7 @@
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-03</t>
+          <t xml:space="preserve">M20-02</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
@@ -12427,33 +12429,32 @@
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI buttons appear when AI is on</t>
+          <t xml:space="preserve">A bad key is marked invalid</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">None</t>
         </is>
       </c>
       <c r="F175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Cycle, phase 4
-2. Open a goal</t>
+          <t xml:space="preserve">1. Click "Replace" and store a wrong key</t>
         </is>
       </c>
       <c r="G175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Draft from an ambition", "Suggest a parent", "Suggest numbers" and "Suggest a fix" are visible</t>
+          <t xml:space="preserve">Key chip shows "invalid"</t>
         </is>
       </c>
       <c r="H175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I175" s="1"/>
@@ -12470,7 +12471,7 @@
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-04</t>
+          <t xml:space="preserve">M20-03</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
@@ -12480,7 +12481,7 @@
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI drafts, a person decides</t>
+          <t xml:space="preserve">AI buttons appear when AI is on</t>
         </is>
       </c>
       <c r="D176" s="1" t="inlineStr">
@@ -12490,19 +12491,18 @@
       </c>
       <c r="E176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-03 done</t>
+          <t xml:space="preserve">M20-01 done</t>
         </is>
       </c>
       <c r="F176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Draft from an ambition" and give one sentence
-2. Read the result without accepting it
-3. Reload</t>
+          <t xml:space="preserve">1. Open Cycle, phase 4
+2. Open a goal</t>
         </is>
       </c>
       <c r="G176" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A draft is proposed. Nothing is saved until accepted</t>
+          <t xml:space="preserve">"Draft from an ambition", "Suggest a parent", "Suggest numbers" and "Suggest a fix" are visible</t>
         </is>
       </c>
       <c r="H176" s="1" t="inlineStr">
@@ -12524,7 +12524,7 @@
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-05</t>
+          <t xml:space="preserve">M20-04</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot answers with sources</t>
+          <t xml:space="preserve">AI drafts, a person decides</t>
         </is>
       </c>
       <c r="D177" s="1" t="inlineStr">
@@ -12544,17 +12544,19 @@
       </c>
       <c r="E177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">M20-03 done</t>
         </is>
       </c>
       <c r="F177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the copilot and ask: which key results are at risk this cycle</t>
+          <t xml:space="preserve">1. Click "Draft from an ambition" and give one sentence
+2. Read the result without accepting it
+3. Reload</t>
         </is>
       </c>
       <c r="G177" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A streamed answer with "Sources". Any change is shown as "Proposed change" with "Undo"</t>
+          <t xml:space="preserve">A draft is proposed. Nothing is saved until accepted</t>
         </is>
       </c>
       <c r="H177" s="1" t="inlineStr">
@@ -12576,7 +12578,7 @@
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-06</t>
+          <t xml:space="preserve">M20-05</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
@@ -12586,27 +12588,27 @@
       </c>
       <c r="C178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Copilot does not leak private items</t>
+          <t xml:space="preserve">Copilot answers with sources</t>
         </is>
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara has a draft document</t>
+          <t xml:space="preserve">M20-01 done</t>
         </is>
       </c>
       <c r="F178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Ask the copilot about Sara's draft document</t>
+          <t xml:space="preserve">1. Open the copilot and ask: which key results are at risk this cycle</t>
         </is>
       </c>
       <c r="G178" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The answer does not show its content</t>
+          <t xml:space="preserve">A streamed answer with "Sources". Any change is shown as "Proposed change" with "Undo"</t>
         </is>
       </c>
       <c r="H178" s="1" t="inlineStr">
@@ -12628,7 +12630,7 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-07</t>
+          <t xml:space="preserve">M20-06</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
@@ -12638,32 +12640,32 @@
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Agents draft with AI on</t>
+          <t xml:space="preserve">Copilot does not leak private items</t>
         </is>
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Jonas</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-01 done</t>
+          <t xml:space="preserve">Sara has a draft document</t>
         </is>
       </c>
       <c r="F179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
+          <t xml:space="preserve">1. Ask the copilot about Sara's draft document</t>
         </is>
       </c>
       <c r="G179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chip shows "Drafting on"</t>
+          <t xml:space="preserve">The answer does not show its content</t>
         </is>
       </c>
       <c r="H179" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I179" s="1"/>
@@ -12680,7 +12682,7 @@
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M20-08</t>
+          <t xml:space="preserve">M20-07</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
@@ -12690,7 +12692,7 @@
       </c>
       <c r="C180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Removing the key returns to deterministic mode</t>
+          <t xml:space="preserve">Agents draft with AI on</t>
         </is>
       </c>
       <c r="D180" s="1" t="inlineStr">
@@ -12705,18 +12707,17 @@
       </c>
       <c r="F180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Remove the key"
-2. Draft an objective with bad wording</t>
+          <t xml:space="preserve">1. Open Admin, Agents and runs</t>
         </is>
       </c>
       <c r="G180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">AI buttons disappear. Quality checks still fire</t>
+          <t xml:space="preserve">Chip shows "Drafting on"</t>
         </is>
       </c>
       <c r="H180" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">High</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I180" s="1"/>
@@ -12731,128 +12732,123 @@
       <c r="N180" s="5"/>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="inlineStr">
+      <c r="A181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20-08</t>
+        </is>
+      </c>
+      <c r="B181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20 AI provider and copilot</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Removing the key returns to deterministic mode</t>
+        </is>
+      </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M20-01 done</t>
+        </is>
+      </c>
+      <c r="F181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click "Remove the key"
+2. Draft an objective with bad wording</t>
+        </is>
+      </c>
+      <c r="G181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">AI buttons disappear. Quality checks still fire</t>
+        </is>
+      </c>
+      <c r="H181" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I181" s="1"/>
+      <c r="J181" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K181" s="5"/>
+      <c r="L181" s="5"/>
+      <c r="M181" s="5"/>
+      <c r="N181" s="5"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email: Deliver mail and chat messages to real inboxes and apps. Needs M16 first. About 60 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B181" s="3"/>
-      <c r="C181" s="3"/>
-      <c r="D181" s="3"/>
-      <c r="E181" s="3"/>
-      <c r="F181" s="3"/>
-      <c r="G181" s="3"/>
-      <c r="H181" s="3"/>
-      <c r="I181" s="3"/>
-      <c r="J181" s="3"/>
-      <c r="K181" s="3"/>
-      <c r="L181" s="3"/>
-      <c r="M181" s="3"/>
-      <c r="N181" s="3"/>
-    </row>
-    <row r="182">
-      <c r="A182" s="1" t="inlineStr">
+      <c r="B182" s="3"/>
+      <c r="C182" s="3"/>
+      <c r="D182" s="3"/>
+      <c r="E182" s="3"/>
+      <c r="F182" s="3"/>
+      <c r="G182" s="3"/>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="J182" s="3"/>
+      <c r="K182" s="3"/>
+      <c r="L182" s="3"/>
+      <c r="M182" s="3"/>
+      <c r="N182" s="3"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21-01</t>
         </is>
       </c>
-      <c r="B182" s="1" t="inlineStr">
+      <c r="B183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email</t>
         </is>
       </c>
-      <c r="C182" s="1" t="inlineStr">
+      <c r="C183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Real email delivery</t>
         </is>
       </c>
-      <c r="D182" s="1" t="inlineStr">
+      <c r="D183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin, then Jonas</t>
         </is>
       </c>
-      <c r="E182" s="1" t="inlineStr">
+      <c r="E183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Server started with SMTP settings (OPENOKR_MAIL_TRANSPORT and friends), or Mailpit on localhost port 1025</t>
         </is>
       </c>
-      <c r="F182" s="1" t="inlineStr">
+      <c r="F183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Create a personal invitation for a spare email
 2. Jonas uses "Forgot your password?"</t>
         </is>
       </c>
-      <c r="G182" s="1" t="inlineStr">
+      <c r="G183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Both mails arrive with working links. The console mail banner on Admin, General is gone</t>
         </is>
       </c>
-      <c r="H182" s="1" t="inlineStr">
+      <c r="H183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I182" s="1" t="inlineStr">
+      <c r="I183" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Mailpit shows every mail at http://localhost:8025</t>
-        </is>
-      </c>
-      <c r="J182" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K182" s="5"/>
-      <c r="L182" s="5"/>
-      <c r="M182" s="5"/>
-      <c r="N182" s="5"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21-02</t>
-        </is>
-      </c>
-      <c r="B183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21 Chat channels and email</t>
-        </is>
-      </c>
-      <c r="C183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connect Slack</t>
-        </is>
-      </c>
-      <c r="D183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A Slack app with bot token, signing secret and workspace id. Events URL set to &lt;instance&gt;/api/channels/slack</t>
-        </is>
-      </c>
-      <c r="F183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open Admin, Channels, Slack
-2. Fill "Bot token", "Signing or webhook secret", "Provider workspace id"
-3. Click "Connect"</t>
-        </is>
-      </c>
-      <c r="G183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Status "connected"</t>
-        </is>
-      </c>
-      <c r="H183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I183" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The instance must be reachable from the internet (ngrok or a public host)</t>
         </is>
       </c>
       <c r="J183" s="5" t="inlineStr">
@@ -12868,7 +12864,7 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03</t>
+          <t xml:space="preserve">M21-02</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
@@ -12878,28 +12874,29 @@
       </c>
       <c r="C184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link a member's Slack account</t>
+          <t xml:space="preserve">Connect Slack</t>
         </is>
       </c>
       <c r="D184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-02 done</t>
+          <t xml:space="preserve">A Slack app with bot token, signing secret and workspace id. Events URL set to &lt;instance&gt;/api/channels/slack</t>
         </is>
       </c>
       <c r="F184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Account, Where to reach you, "Linked accounts", click "Get a code"
-2. Send the 6-digit code to the OpenOKR bot in Slack within ten minutes</t>
+          <t xml:space="preserve">1. Open Admin, Channels, Slack
+2. Fill "Bot token", "Signing or webhook secret", "Provider workspace id"
+3. Click "Connect"</t>
         </is>
       </c>
       <c r="G184" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The chip turns from "not linked" to "linked" with "Unlink"</t>
+          <t xml:space="preserve">Status "connected"</t>
         </is>
       </c>
       <c r="H184" s="1" t="inlineStr">
@@ -12907,7 +12904,11 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I184" s="1"/>
+      <c r="I184" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The instance must be reachable from the internet (ngrok or a public host)</t>
+        </is>
+      </c>
       <c r="J184" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12921,7 +12922,7 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-04</t>
+          <t xml:space="preserve">M21-03</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
@@ -12931,7 +12932,7 @@
       </c>
       <c r="C185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A nudge arrives in Slack</t>
+          <t xml:space="preserve">Link a member's Slack account</t>
         </is>
       </c>
       <c r="D185" s="1" t="inlineStr">
@@ -12941,18 +12942,18 @@
       </c>
       <c r="E185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03 done. Sara owes a check-in</t>
+          <t xml:space="preserve">M21-02 done</t>
         </is>
       </c>
       <c r="F185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set "Primary channel" to Slack and save
-2. Admin runs "Nudge queue"</t>
+          <t xml:space="preserve">1. Open Account, Where to reach you, "Linked accounts", click "Get a code"
+2. Send the 6-digit code to the OpenOKR bot in Slack within ten minutes</t>
         </is>
       </c>
       <c r="G185" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The message arrives in Slack. Admin, Channels, "Recent messages" shows sent</t>
+          <t xml:space="preserve">The chip turns from "not linked" to "linked" with "Unlink"</t>
         </is>
       </c>
       <c r="H185" s="1" t="inlineStr">
@@ -12960,11 +12961,7 @@
           <t xml:space="preserve">High</t>
         </is>
       </c>
-      <c r="I185" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"Send me a test" sends an email, not a Slack message. Do not use it to prove chat delivery</t>
-        </is>
-      </c>
+      <c r="I185" s="1"/>
       <c r="J185" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -12978,7 +12975,7 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-05</t>
+          <t xml:space="preserve">M21-04</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
@@ -12988,7 +12985,7 @@
       </c>
       <c r="C186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chat commands work</t>
+          <t xml:space="preserve">A nudge arrives in Slack</t>
         </is>
       </c>
       <c r="D186" s="1" t="inlineStr">
@@ -12998,26 +12995,30 @@
       </c>
       <c r="E186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-03 done</t>
+          <t xml:space="preserve">M21-03 done. Sara owes a check-in</t>
         </is>
       </c>
       <c r="F186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. In Slack type /okr help
-2. Type /okr checkin and follow the prompts</t>
+          <t xml:space="preserve">1. Set "Primary channel" to Slack and save
+2. Admin runs "Nudge queue"</t>
         </is>
       </c>
       <c r="G186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Help lists the commands. The check-in appears on the goal like one made in the browser</t>
+          <t xml:space="preserve">The message arrives in Slack. Admin, Channels, "Recent messages" shows sent</t>
         </is>
       </c>
       <c r="H186" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I186" s="1"/>
+          <t xml:space="preserve">High</t>
+        </is>
+      </c>
+      <c r="I186" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">"Send me a test" sends an email, not a Slack message. Do not use it to prove chat delivery</t>
+        </is>
+      </c>
       <c r="J186" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -13031,7 +13032,7 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-06</t>
+          <t xml:space="preserve">M21-05</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
@@ -13041,29 +13042,28 @@
       </c>
       <c r="C187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Microsoft Teams end to end</t>
+          <t xml:space="preserve">Chat commands work</t>
         </is>
       </c>
       <c r="D187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Sara</t>
+          <t xml:space="preserve">Sara</t>
         </is>
       </c>
       <c r="E187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A Teams app (deploy/teams manifest), client id and secret, tenant id</t>
+          <t xml:space="preserve">M21-03 done</t>
         </is>
       </c>
       <c r="F187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Connect Teams on Admin, Channels
-2. Sara links her account with a code
-3. Run "Nudge queue"</t>
+          <t xml:space="preserve">1. In Slack type /okr help
+2. Type /okr checkin and follow the prompts</t>
         </is>
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Connected, linked, and the nudge arrives in Teams</t>
+          <t xml:space="preserve">Help lists the commands. The check-in appears on the goal like one made in the browser</t>
         </is>
       </c>
       <c r="H187" s="1" t="inlineStr">
@@ -13085,30 +13085,84 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M21-06</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21 Chat channels and email</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microsoft Teams end to end</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Sara</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A Teams app (deploy/teams manifest), client id and secret, tenant id</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Connect Teams on Admin, Channels
+2. Sara links her account with a code
+3. Run "Nudge queue"</t>
+        </is>
+      </c>
+      <c r="G188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Connected, linked, and the nudge arrives in Teams</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I188" s="1"/>
+      <c r="J188" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K188" s="5"/>
+      <c r="L188" s="5"/>
+      <c r="M188" s="5"/>
+      <c r="N188" s="5"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M21-07</t>
         </is>
       </c>
-      <c r="B188" s="1" t="inlineStr">
+      <c r="B189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M21 Chat channels and email</t>
         </is>
       </c>
-      <c r="C188" s="1" t="inlineStr">
+      <c r="C189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">WhatsApp end to end</t>
         </is>
       </c>
-      <c r="D188" s="1" t="inlineStr">
+      <c r="D189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin, then Sara</t>
         </is>
       </c>
-      <c r="E188" s="1" t="inlineStr">
+      <c r="E189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Meta WhatsApp Business app, permanent token, app secret and verify token, phone number id</t>
         </is>
       </c>
-      <c r="F188" s="1" t="inlineStr">
+      <c r="F189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Connect WhatsApp on Admin, Channels
 2. Click "Sync from Meta" and map a template to a reminder
@@ -13116,63 +13170,9 @@
 4. Run "Nudge queue"</t>
         </is>
       </c>
-      <c r="G188" s="1" t="inlineStr">
+      <c r="G189" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connected, linked, and the reminder arrives on WhatsApp</t>
-        </is>
-      </c>
-      <c r="H188" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I188" s="1"/>
-      <c r="J188" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K188" s="5"/>
-      <c r="L188" s="5"/>
-      <c r="M188" s="5"/>
-      <c r="N188" s="5"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21-08</t>
-        </is>
-      </c>
-      <c r="B189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M21 Chat channels and email</t>
-        </is>
-      </c>
-      <c r="C189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Telegram end to end</t>
-        </is>
-      </c>
-      <c r="D189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin, then Sara</t>
-        </is>
-      </c>
-      <c r="E189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A BotFather token and a webhook secret</t>
-        </is>
-      </c>
-      <c r="F189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Connect Telegram on Admin, Channels
-2. Sara links her account with a code
-3. Run "Nudge queue"</t>
-        </is>
-      </c>
-      <c r="G189" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Connected, linked, and the nudge arrives in Telegram</t>
         </is>
       </c>
       <c r="H189" s="1" t="inlineStr">
@@ -13194,7 +13194,7 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M21-09</t>
+          <t xml:space="preserve">M21-08</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
@@ -13204,28 +13204,29 @@
       </c>
       <c r="C190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Disconnect a channel</t>
+          <t xml:space="preserve">Telegram end to end</t>
         </is>
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Admin, then Sara</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A connected channel</t>
+          <t xml:space="preserve">A BotFather token and a webhook secret</t>
         </is>
       </c>
       <c r="F190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Click "Disconnect"
-2. As Sara open Account, Where to reach you</t>
+          <t xml:space="preserve">1. Connect Telegram on Admin, Channels
+2. Sara links her account with a code
+3. Run "Nudge queue"</t>
         </is>
       </c>
       <c r="G190" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Status "not connected". Sara's option for that channel is disabled</t>
+          <t xml:space="preserve">Connected, linked, and the nudge arrives in Telegram</t>
         </is>
       </c>
       <c r="H190" s="1" t="inlineStr">
@@ -13245,52 +13246,105 @@
       <c r="N190" s="5"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
+      <c r="A191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21-09</t>
+        </is>
+      </c>
+      <c r="B191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M21 Chat channels and email</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Disconnect a channel</t>
+        </is>
+      </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A connected channel</t>
+        </is>
+      </c>
+      <c r="F191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Click "Disconnect"
+2. As Sara open Account, Where to reach you</t>
+        </is>
+      </c>
+      <c r="G191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status "not connected". Sara's option for that channel is disabled</t>
+        </is>
+      </c>
+      <c r="H191" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I191" s="1"/>
+      <c r="J191" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K191" s="5"/>
+      <c r="L191" s="5"/>
+      <c r="M191" s="5"/>
+      <c r="N191" s="5"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M22 Single sign-on and directory sync: Sign in through a company identity provider and sync the directory. Needs M04 first. About 45 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B191" s="3"/>
-      <c r="C191" s="3"/>
-      <c r="D191" s="3"/>
-      <c r="E191" s="3"/>
-      <c r="F191" s="3"/>
-      <c r="G191" s="3"/>
-      <c r="H191" s="3"/>
-      <c r="I191" s="3"/>
-      <c r="J191" s="3"/>
-      <c r="K191" s="3"/>
-      <c r="L191" s="3"/>
-      <c r="M191" s="3"/>
-      <c r="N191" s="3"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="1" t="inlineStr">
+      <c r="B192" s="3"/>
+      <c r="C192" s="3"/>
+      <c r="D192" s="3"/>
+      <c r="E192" s="3"/>
+      <c r="F192" s="3"/>
+      <c r="G192" s="3"/>
+      <c r="H192" s="3"/>
+      <c r="I192" s="3"/>
+      <c r="J192" s="3"/>
+      <c r="K192" s="3"/>
+      <c r="L192" s="3"/>
+      <c r="M192" s="3"/>
+      <c r="N192" s="3"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M22-01</t>
         </is>
       </c>
-      <c r="B192" s="1" t="inlineStr">
+      <c r="B193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M22 Single sign-on and directory sync</t>
         </is>
       </c>
-      <c r="C192" s="1" t="inlineStr">
+      <c r="C193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Add an OIDC provider and sign in with it</t>
         </is>
       </c>
-      <c r="D192" s="1" t="inlineStr">
+      <c r="D193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E192" s="1" t="inlineStr">
+      <c r="E193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An OIDC app at Google, Okta, Entra or Keycloak with the redirect URL registered</t>
         </is>
       </c>
-      <c r="F192" s="1" t="inlineStr">
+      <c r="F193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Single sign-on, "Add provider"
 2. Protocol OIDC, fill Provider ID, Display name, Discovery URL, Client ID, Client secret, email domain
@@ -13299,76 +13353,19 @@
 5. Sign out, use the new button on the sign-in page</t>
         </is>
       </c>
-      <c r="G192" s="1" t="inlineStr">
+      <c r="G193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Provider saved. It will take effect on the next instance restart." The sign-in page shows the provider button and sign-in works</t>
         </is>
       </c>
-      <c r="H192" s="1" t="inlineStr">
+      <c r="H193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I192" s="1" t="inlineStr">
+      <c r="I193" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Needs a restart, which needs server access</t>
-        </is>
-      </c>
-      <c r="J192" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K192" s="5"/>
-      <c r="L192" s="5"/>
-      <c r="M192" s="5"/>
-      <c r="N192" s="5"/>
-    </row>
-    <row r="193">
-      <c r="A193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22-02</t>
-        </is>
-      </c>
-      <c r="B193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
-        </is>
-      </c>
-      <c r="C193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enforce SSO for a domain</t>
-        </is>
-      </c>
-      <c r="D193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M22-01 done</t>
-        </is>
-      </c>
-      <c r="F193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Tick "Enforce SSO for the email domains listed above" and save, restart
-2. Try password sign-in with an address on that domain</t>
-        </is>
-      </c>
-      <c r="G193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Password sign-in is refused for that domain</t>
-        </is>
-      </c>
-      <c r="H193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
-        </is>
-      </c>
-      <c r="I193" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Do not enforce on the Admin's own domain, or you lock yourself out</t>
         </is>
       </c>
       <c r="J193" s="5" t="inlineStr">
@@ -13384,7 +13381,7 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-03</t>
+          <t xml:space="preserve">M22-02</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
@@ -13394,7 +13391,7 @@
       </c>
       <c r="C194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SAML provider</t>
+          <t xml:space="preserve">Enforce SSO for a domain</t>
         </is>
       </c>
       <c r="D194" s="1" t="inlineStr">
@@ -13404,27 +13401,30 @@
       </c>
       <c r="E194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A SAML IdP</t>
+          <t xml:space="preserve">M22-01 done</t>
         </is>
       </c>
       <c r="F194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Add a SAML 2.0 provider with Sign-on URL, Issuer and Signing certificate
-2. Copy the "Assertion consumer service" URL into the IdP
-3. Restart and sign in</t>
+          <t xml:space="preserve">1. Tick "Enforce SSO for the email domains listed above" and save, restart
+2. Try password sign-in with an address on that domain</t>
         </is>
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sign-in through SAML works</t>
+          <t xml:space="preserve">Password sign-in is refused for that domain</t>
         </is>
       </c>
       <c r="H194" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
-        </is>
-      </c>
-      <c r="I194" s="1"/>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I194" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Do not enforce on the Admin's own domain, or you lock yourself out</t>
+        </is>
+      </c>
       <c r="J194" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -13438,7 +13438,7 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-04</t>
+          <t xml:space="preserve">M22-03</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="C195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">SCIM token and user push</t>
+          <t xml:space="preserve">SAML provider</t>
         </is>
       </c>
       <c r="D195" s="1" t="inlineStr">
@@ -13458,19 +13458,19 @@
       </c>
       <c r="E195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An IdP that supports SCIM 2.0</t>
+          <t xml:space="preserve">A SAML IdP</t>
         </is>
       </c>
       <c r="F195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Directory sync, click "Generate SCIM token"
-2. Configure the IdP with the "SCIM endpoint" and token
-3. Assign a user in the IdP, then unassign</t>
+          <t xml:space="preserve">1. Add a SAML 2.0 provider with Sign-on URL, Issuer and Signing certificate
+2. Copy the "Assertion consumer service" URL into the IdP
+3. Restart and sign in</t>
         </is>
       </c>
       <c r="G195" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">"Copy this token now. It will not be shown again." The user appears in People, then shows as suspended after unassign</t>
+          <t xml:space="preserve">Sign-in through SAML works</t>
         </is>
       </c>
       <c r="H195" s="1" t="inlineStr">
@@ -13492,7 +13492,7 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M22-05</t>
+          <t xml:space="preserve">M22-04</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
@@ -13502,33 +13502,34 @@
       </c>
       <c r="C196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Require a second factor for everyone</t>
+          <t xml:space="preserve">SCIM token and user push</t>
         </is>
       </c>
       <c r="D196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Jonas</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">An IdP that supports SCIM 2.0</t>
         </is>
       </c>
       <c r="F196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Tick "Require a second factor for everybody in this workspace" on Admin, General and save
-2. Jonas signs in</t>
+          <t xml:space="preserve">1. Open Admin, Directory sync, click "Generate SCIM token"
+2. Configure the IdP with the "SCIM endpoint" and token
+3. Assign a user in the IdP, then unassign</t>
         </is>
       </c>
       <c r="G196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jonas is asked to set up a second factor before continuing. Untick afterwards</t>
+          <t xml:space="preserve">"Copy this token now. It will not be shown again." The user appears in People, then shows as suspended after unassign</t>
         </is>
       </c>
       <c r="H196" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I196" s="1"/>
@@ -13543,52 +13544,105 @@
       <c r="N196" s="5"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
+      <c r="A197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22-05</t>
+        </is>
+      </c>
+      <c r="B197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M22 Single sign-on and directory sync</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Require a second factor for everyone</t>
+        </is>
+      </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Jonas</t>
+        </is>
+      </c>
+      <c r="E197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Tick "Require a second factor for everybody in this workspace" on Admin, General and save
+2. Jonas signs in</t>
+        </is>
+      </c>
+      <c r="G197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jonas is asked to set up a second factor before continuing. Untick afterwards</t>
+        </is>
+      </c>
+      <c r="H197" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I197" s="1"/>
+      <c r="J197" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K197" s="5"/>
+      <c r="L197" s="5"/>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export: Bring data in from spreadsheets and FlowyTeam, and take it out. Needs M07 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B197" s="3"/>
-      <c r="C197" s="3"/>
-      <c r="D197" s="3"/>
-      <c r="E197" s="3"/>
-      <c r="F197" s="3"/>
-      <c r="G197" s="3"/>
-      <c r="H197" s="3"/>
-      <c r="I197" s="3"/>
-      <c r="J197" s="3"/>
-      <c r="K197" s="3"/>
-      <c r="L197" s="3"/>
-      <c r="M197" s="3"/>
-      <c r="N197" s="3"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="1" t="inlineStr">
+      <c r="B198" s="3"/>
+      <c r="C198" s="3"/>
+      <c r="D198" s="3"/>
+      <c r="E198" s="3"/>
+      <c r="F198" s="3"/>
+      <c r="G198" s="3"/>
+      <c r="H198" s="3"/>
+      <c r="I198" s="3"/>
+      <c r="J198" s="3"/>
+      <c r="K198" s="3"/>
+      <c r="L198" s="3"/>
+      <c r="M198" s="3"/>
+      <c r="N198" s="3"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23-01</t>
         </is>
       </c>
-      <c r="B198" s="1" t="inlineStr">
+      <c r="B199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export</t>
         </is>
       </c>
-      <c r="C198" s="1" t="inlineStr">
+      <c r="C199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Import goals from a CSV</t>
         </is>
       </c>
-      <c r="D198" s="1" t="inlineStr">
+      <c r="D199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E198" s="1" t="inlineStr">
+      <c r="E199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A CSV with 3 goals (title, level, champion email)</t>
         </is>
       </c>
-      <c r="F198" s="1" t="inlineStr">
+      <c r="F199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Import
 2. Pick goals in "What is in the file", choose the file, click "Read the file"
@@ -13596,61 +13650,9 @@
 4. Click "Import &lt;n&gt; rows"</t>
         </is>
       </c>
-      <c r="G198" s="1" t="inlineStr">
+      <c r="G199" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Preview counts Read, To create, To update, Skipped. After import: "Imported. Run the same file again and it writes nothing new." The goals are on the work map</t>
-        </is>
-      </c>
-      <c r="H198" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I198" s="1"/>
-      <c r="J198" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K198" s="5"/>
-      <c r="L198" s="5"/>
-      <c r="M198" s="5"/>
-      <c r="N198" s="5"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23-02</t>
-        </is>
-      </c>
-      <c r="B199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23 Import and export</t>
-        </is>
-      </c>
-      <c r="C199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Importing the same file twice writes nothing</t>
-        </is>
-      </c>
-      <c r="D199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M23-01 done</t>
-        </is>
-      </c>
-      <c r="F199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Import the same file again</t>
-        </is>
-      </c>
-      <c r="G199" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preview shows 0 to create</t>
         </is>
       </c>
       <c r="H199" s="1" t="inlineStr">
@@ -13672,7 +13674,7 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-03</t>
+          <t xml:space="preserve">M23-02</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
@@ -13682,7 +13684,7 @@
       </c>
       <c r="C200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A bad row is reported, not dropped silently</t>
+          <t xml:space="preserve">Importing the same file twice writes nothing</t>
         </is>
       </c>
       <c r="D200" s="1" t="inlineStr">
@@ -13692,22 +13694,22 @@
       </c>
       <c r="E200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV with one row missing its title</t>
+          <t xml:space="preserve">M23-01 done</t>
         </is>
       </c>
       <c r="F200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Import it</t>
+          <t xml:space="preserve">1. Import the same file again</t>
         </is>
       </c>
       <c r="G200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">That row is counted as Skipped with its reason</t>
+          <t xml:space="preserve">Preview shows 0 to create</t>
         </is>
       </c>
       <c r="H200" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I200" s="1"/>
@@ -13724,7 +13726,7 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-04</t>
+          <t xml:space="preserve">M23-03</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
@@ -13734,7 +13736,7 @@
       </c>
       <c r="C201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Import KPI records from an xlsx file</t>
+          <t xml:space="preserve">A bad row is reported, not dropped silently</t>
         </is>
       </c>
       <c r="D201" s="1" t="inlineStr">
@@ -13744,22 +13746,22 @@
       </c>
       <c r="E201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An xlsx of KPI records</t>
+          <t xml:space="preserve">A CSV with one row missing its title</t>
         </is>
       </c>
       <c r="F201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Import with kpi-records</t>
+          <t xml:space="preserve">1. Import it</t>
         </is>
       </c>
       <c r="G201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Values appear in the KPI grid</t>
+          <t xml:space="preserve">That row is counted as Skipped with its reason</t>
         </is>
       </c>
       <c r="H201" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I201" s="1"/>
@@ -13776,7 +13778,7 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M23-05</t>
+          <t xml:space="preserve">M23-04</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
@@ -13786,7 +13788,7 @@
       </c>
       <c r="C202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export the workspace</t>
+          <t xml:space="preserve">Import KPI records from an xlsx file</t>
         </is>
       </c>
       <c r="D202" s="1" t="inlineStr">
@@ -13796,22 +13798,22 @@
       </c>
       <c r="E202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">None</t>
+          <t xml:space="preserve">An xlsx of KPI records</t>
         </is>
       </c>
       <c r="F202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Admin, Import use "Export workspace" with "Include files"</t>
+          <t xml:space="preserve">1. Import with kpi-records</t>
         </is>
       </c>
       <c r="G202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">An archive file downloads</t>
+          <t xml:space="preserve">Values appear in the KPI grid</t>
         </is>
       </c>
       <c r="H202" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I202" s="1"/>
@@ -13828,30 +13830,82 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M23-05</t>
+        </is>
+      </c>
+      <c r="B203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M23 Import and export</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Export the workspace</t>
+        </is>
+      </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On Admin, Import use "Export workspace" with "Include files"</t>
+        </is>
+      </c>
+      <c r="G203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">An archive file downloads</t>
+        </is>
+      </c>
+      <c r="H203" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I203" s="1"/>
+      <c r="J203" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K203" s="5"/>
+      <c r="L203" s="5"/>
+      <c r="M203" s="5"/>
+      <c r="N203" s="5"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M23-06</t>
         </is>
       </c>
-      <c r="B203" s="1" t="inlineStr">
+      <c r="B204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M23 Import and export</t>
         </is>
       </c>
-      <c r="C203" s="1" t="inlineStr">
+      <c r="C204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">FlowyTeam import from the command line</t>
         </is>
       </c>
-      <c r="D203" s="1" t="inlineStr">
+      <c r="D204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin (server access)</t>
         </is>
       </c>
-      <c r="E203" s="1" t="inlineStr">
+      <c r="E204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">A FlowyTeam MySQL copy and the company id</t>
         </is>
       </c>
-      <c r="F203" s="1" t="inlineStr">
+      <c r="F204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Run pnpm import:flowyteam with --source, --company, --workspace, --as, without --write
 2. Read the dry-run report
@@ -13859,78 +13913,78 @@
 4. Open the work map and People</t>
         </is>
       </c>
-      <c r="G203" s="1" t="inlineStr">
+      <c r="G204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The dry run writes nothing. The real run imports people, spaces, cycles, objectives and KPIs, visible in the UI</t>
         </is>
       </c>
-      <c r="H203" s="1" t="inlineStr">
+      <c r="H204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I203" s="1" t="inlineStr">
+      <c r="I204" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Technical step. Skip unless a FlowyTeam source is available</t>
         </is>
       </c>
-      <c r="J203" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K203" s="5"/>
-      <c r="L203" s="5"/>
-      <c r="M203" s="5"/>
-      <c r="N203" s="5"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="3" t="inlineStr">
+      <c r="J204" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K204" s="5"/>
+      <c r="L204" s="5"/>
+      <c r="M204" s="5"/>
+      <c r="N204" s="5"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents: Reach the product from scripts, the command line and outside AI agents. Needs M11 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B204" s="3"/>
-      <c r="C204" s="3"/>
-      <c r="D204" s="3"/>
-      <c r="E204" s="3"/>
-      <c r="F204" s="3"/>
-      <c r="G204" s="3"/>
-      <c r="H204" s="3"/>
-      <c r="I204" s="3"/>
-      <c r="J204" s="3"/>
-      <c r="K204" s="3"/>
-      <c r="L204" s="3"/>
-      <c r="M204" s="3"/>
-      <c r="N204" s="3"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="1" t="inlineStr">
+      <c r="B205" s="3"/>
+      <c r="C205" s="3"/>
+      <c r="D205" s="3"/>
+      <c r="E205" s="3"/>
+      <c r="F205" s="3"/>
+      <c r="G205" s="3"/>
+      <c r="H205" s="3"/>
+      <c r="I205" s="3"/>
+      <c r="J205" s="3"/>
+      <c r="K205" s="3"/>
+      <c r="L205" s="3"/>
+      <c r="M205" s="3"/>
+      <c r="N205" s="3"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24-01</t>
         </is>
       </c>
-      <c r="B205" s="1" t="inlineStr">
+      <c r="B206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C205" s="1" t="inlineStr">
+      <c r="C206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Create and revoke an API token</t>
         </is>
       </c>
-      <c r="D205" s="1" t="inlineStr">
+      <c r="D206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E205" s="1" t="inlineStr">
+      <c r="E206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">None</t>
         </is>
       </c>
-      <c r="F205" s="1" t="inlineStr">
+      <c r="F206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Account, API tokens
 2. Click "Create token" with no name, then with no scope
@@ -13938,67 +13992,14 @@
 4. Click "Revoke"</t>
         </is>
       </c>
-      <c r="G205" s="1" t="inlineStr">
+      <c r="G206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">"Give the token a name." and "Choose at least one scope, or the token could reach nothing." The token shows once, is listed, then revoked</t>
         </is>
       </c>
-      <c r="H205" s="1" t="inlineStr">
+      <c r="H206" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I205" s="1"/>
-      <c r="J205" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K205" s="5"/>
-      <c r="L205" s="5"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="5"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M24-02</t>
-        </is>
-      </c>
-      <c r="B206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
-        </is>
-      </c>
-      <c r="C206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Use the token, then use it after revoking</t>
-        </is>
-      </c>
-      <c r="D206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sara (technical)</t>
-        </is>
-      </c>
-      <c r="E206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A token from M24-01 before revoking</t>
-        </is>
-      </c>
-      <c r="F206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Call a GET endpoint from docs/api/reference.md with the token
-2. Revoke it and call again</t>
-        </is>
-      </c>
-      <c r="G206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">First call succeeds. After revoke it is refused</t>
-        </is>
-      </c>
-      <c r="H206" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Medium</t>
         </is>
       </c>
       <c r="I206" s="1"/>
@@ -14015,30 +14016,83 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">M24-02</t>
+        </is>
+      </c>
+      <c r="B207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Use the token, then use it after revoking</t>
+        </is>
+      </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara (technical)</t>
+        </is>
+      </c>
+      <c r="E207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A token from M24-01 before revoking</t>
+        </is>
+      </c>
+      <c r="F207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Call a GET endpoint from docs/api/reference.md with the token
+2. Revoke it and call again</t>
+        </is>
+      </c>
+      <c r="G207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First call succeeds. After revoke it is refused</t>
+        </is>
+      </c>
+      <c r="H207" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I207" s="1"/>
+      <c r="J207" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K207" s="5"/>
+      <c r="L207" s="5"/>
+      <c r="M207" s="5"/>
+      <c r="N207" s="5"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">M24-03</t>
         </is>
       </c>
-      <c r="B207" s="1" t="inlineStr">
+      <c r="B208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C207" s="1" t="inlineStr">
+      <c r="C208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Command-line login by device approval</t>
         </is>
       </c>
-      <c r="D207" s="1" t="inlineStr">
+      <c r="D208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara (technical)</t>
         </is>
       </c>
-      <c r="E207" s="1" t="inlineStr">
+      <c r="E208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The okr command line</t>
         </is>
       </c>
-      <c r="F207" s="1" t="inlineStr">
+      <c r="F208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Run okr login --url &lt;instance&gt;
 2. Open the printed link, check "Scopes it asked for"
@@ -14046,54 +14100,54 @@
 4. Repeat and click "Refuse"</t>
         </is>
       </c>
-      <c r="G207" s="1" t="inlineStr">
+      <c r="G208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Authorise: the terminal prints Saved profile. Refuse: the login fails</t>
         </is>
       </c>
-      <c r="H207" s="1" t="inlineStr">
+      <c r="H208" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I207" s="1"/>
-      <c r="J207" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K207" s="5"/>
-      <c r="L207" s="5"/>
-      <c r="M207" s="5"/>
-      <c r="N207" s="5"/>
-    </row>
-    <row r="208">
-      <c r="A208" s="1" t="inlineStr">
+      <c r="I208" s="1"/>
+      <c r="J208" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K208" s="5"/>
+      <c r="L208" s="5"/>
+      <c r="M208" s="5"/>
+      <c r="N208" s="5"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24-04</t>
         </is>
       </c>
-      <c r="B208" s="1" t="inlineStr">
+      <c r="B209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M24 API tokens, CLI and external agents</t>
         </is>
       </c>
-      <c r="C208" s="1" t="inlineStr">
+      <c r="C209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Connect an external AI agent (MCP)</t>
         </is>
       </c>
-      <c r="D208" s="1" t="inlineStr">
+      <c r="D209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sara</t>
         </is>
       </c>
-      <c r="E208" s="1" t="inlineStr">
+      <c r="E209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">An MCP client such as Claude Desktop, and a public HTTPS URL for the instance</t>
         </is>
       </c>
-      <c r="F208" s="1" t="inlineStr">
+      <c r="F209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Add a remote MCP server &lt;instance&gt;/api/mcp
 2. On "Connect an agent" pick the workspace and click "Connect"
@@ -14101,134 +14155,82 @@
 4. Open Account, Connected agents and click "Revoke"</t>
         </is>
       </c>
-      <c r="G208" s="1" t="inlineStr">
+      <c r="G209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The agent lists only goals Sara may see. After revoke it loses access</t>
         </is>
       </c>
-      <c r="H208" s="1" t="inlineStr">
+      <c r="H209" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Medium</t>
         </is>
       </c>
-      <c r="I208" s="1"/>
-      <c r="J208" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K208" s="5"/>
-      <c r="L208" s="5"/>
-      <c r="M208" s="5"/>
-      <c r="N208" s="5"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="3" t="inlineStr">
+      <c r="I209" s="1"/>
+      <c r="J209" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K209" s="5"/>
+      <c r="L209" s="5"/>
+      <c r="M209" s="5"/>
+      <c r="N209" s="5"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M25 Audit trail and workspace state: Check the audit trail recorded the sensitive actions from earlier modules. Needs M11 first. About 15 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B209" s="3"/>
-      <c r="C209" s="3"/>
-      <c r="D209" s="3"/>
-      <c r="E209" s="3"/>
-      <c r="F209" s="3"/>
-      <c r="G209" s="3"/>
-      <c r="H209" s="3"/>
-      <c r="I209" s="3"/>
-      <c r="J209" s="3"/>
-      <c r="K209" s="3"/>
-      <c r="L209" s="3"/>
-      <c r="M209" s="3"/>
-      <c r="N209" s="3"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="1" t="inlineStr">
+      <c r="B210" s="3"/>
+      <c r="C210" s="3"/>
+      <c r="D210" s="3"/>
+      <c r="E210" s="3"/>
+      <c r="F210" s="3"/>
+      <c r="G210" s="3"/>
+      <c r="H210" s="3"/>
+      <c r="I210" s="3"/>
+      <c r="J210" s="3"/>
+      <c r="K210" s="3"/>
+      <c r="L210" s="3"/>
+      <c r="M210" s="3"/>
+      <c r="N210" s="3"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M25-01</t>
         </is>
       </c>
-      <c r="B210" s="1" t="inlineStr">
+      <c r="B211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">M25 Audit trail and workspace state</t>
         </is>
       </c>
-      <c r="C210" s="1" t="inlineStr">
+      <c r="C211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The audit trail records sensitive actions</t>
         </is>
       </c>
-      <c r="D210" s="1" t="inlineStr">
+      <c r="D211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Admin</t>
         </is>
       </c>
-      <c r="E210" s="1" t="inlineStr">
+      <c r="E211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Earlier modules done (suspend, override publish)</t>
         </is>
       </c>
-      <c r="F210" s="1" t="inlineStr">
+      <c r="F211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">1. Open Admin, Audit trail
 2. Filter "Action" by people.suspend</t>
         </is>
       </c>
-      <c r="G210" s="1" t="inlineStr">
+      <c r="G211" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">The suspend of Tomas and the publish override are listed with who did them</t>
-        </is>
-      </c>
-      <c r="H210" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">High</t>
-        </is>
-      </c>
-      <c r="I210" s="1"/>
-      <c r="J210" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K210" s="5"/>
-      <c r="L210" s="5"/>
-      <c r="M210" s="5"/>
-      <c r="N210" s="5"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M25-02</t>
-        </is>
-      </c>
-      <c r="B211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M25 Audit trail and workspace state</t>
-        </is>
-      </c>
-      <c r="C211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify the audit chain</t>
-        </is>
-      </c>
-      <c r="D211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">None</t>
-        </is>
-      </c>
-      <c r="F211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Click "Verify the audit chain"</t>
-        </is>
-      </c>
-      <c r="G211" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">"The chain is intact. &lt;n&gt; rows checked"</t>
         </is>
       </c>
       <c r="H211" s="1" t="inlineStr">
@@ -14250,7 +14252,7 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M25-03</t>
+          <t xml:space="preserve">M25-02</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
@@ -14260,7 +14262,7 @@
       </c>
       <c r="C212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Export the audit trail</t>
+          <t xml:space="preserve">Verify the audit chain</t>
         </is>
       </c>
       <c r="D212" s="1" t="inlineStr">
@@ -14275,17 +14277,17 @@
       </c>
       <c r="F212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Set From and To, click "Export as CSV"</t>
+          <t xml:space="preserve">1. Click "Verify the audit chain"</t>
         </is>
       </c>
       <c r="G212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">A CSV downloads. An empty range says "The export came back empty."</t>
+          <t xml:space="preserve">"The chain is intact. &lt;n&gt; rows checked"</t>
         </is>
       </c>
       <c r="H212" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Low</t>
+          <t xml:space="preserve">High</t>
         </is>
       </c>
       <c r="I212" s="1"/>
@@ -14302,7 +14304,7 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M25-04</t>
+          <t xml:space="preserve">M25-03</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
@@ -14312,12 +14314,12 @@
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Read-only workspace</t>
+          <t xml:space="preserve">Export the audit trail</t>
         </is>
       </c>
       <c r="D213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin, then Sara</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E213" s="1" t="inlineStr">
@@ -14327,19 +14329,17 @@
       </c>
       <c r="F213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On Admin, General, card "State", click "Set to read only"
-2. Sara tries to post a check-in
-3. Admin clicks "Return to active"</t>
+          <t xml:space="preserve">1. Set From and To, click "Export as CSV"</t>
         </is>
       </c>
       <c r="G213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara can read but every write is refused with a message. After return to active, writes work</t>
+          <t xml:space="preserve">A CSV downloads. An empty range says "The export came back empty."</t>
         </is>
       </c>
       <c r="H213" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Medium</t>
+          <t xml:space="preserve">Low</t>
         </is>
       </c>
       <c r="I213" s="1"/>
@@ -14354,81 +14354,83 @@
       <c r="N213" s="5"/>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="inlineStr">
+      <c r="A214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25-04</t>
+        </is>
+      </c>
+      <c r="B214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M25 Audit trail and workspace state</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Read-only workspace</t>
+        </is>
+      </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin, then Sara</t>
+        </is>
+      </c>
+      <c r="E214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">None</t>
+        </is>
+      </c>
+      <c r="F214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. On Admin, General, card "State", click "Set to read only"
+2. Sara tries to post a check-in
+3. Admin clicks "Return to active"</t>
+        </is>
+      </c>
+      <c r="G214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sara can read but every write is refused with a message. After return to active, writes work</t>
+        </is>
+      </c>
+      <c r="H214" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medium</t>
+        </is>
+      </c>
+      <c r="I214" s="1"/>
+      <c r="J214" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K214" s="5"/>
+      <c r="L214" s="5"/>
+      <c r="M214" s="5"/>
+      <c r="N214" s="5"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">M26 Cloud operator console: Check the managed-cloud operator console. Needs M04 first. About 30 min. Full workflow on the Module Guide sheet.</t>
         </is>
       </c>
-      <c r="B214" s="3"/>
-      <c r="C214" s="3"/>
-      <c r="D214" s="3"/>
-      <c r="E214" s="3"/>
-      <c r="F214" s="3"/>
-      <c r="G214" s="3"/>
-      <c r="H214" s="3"/>
-      <c r="I214" s="3"/>
-      <c r="J214" s="3"/>
-      <c r="K214" s="3"/>
-      <c r="L214" s="3"/>
-      <c r="M214" s="3"/>
-      <c r="N214" s="3"/>
-    </row>
-    <row r="215">
-      <c r="A215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M26-01</t>
-        </is>
-      </c>
-      <c r="B215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">M26 Cloud operator console</t>
-        </is>
-      </c>
-      <c r="C215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Operator console is off on a self-hosted instance</t>
-        </is>
-      </c>
-      <c r="D215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Admin</t>
-        </is>
-      </c>
-      <c r="E215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OPENOKR_CLOUD not set</t>
-        </is>
-      </c>
-      <c r="F215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1. Open /operator and /admin/plan</t>
-        </is>
-      </c>
-      <c r="G215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Both return Not Found</t>
-        </is>
-      </c>
-      <c r="H215" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Low</t>
-        </is>
-      </c>
-      <c r="I215" s="1"/>
-      <c r="J215" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Not Run</t>
-        </is>
-      </c>
-      <c r="K215" s="5"/>
-      <c r="L215" s="5"/>
-      <c r="M215" s="5"/>
-      <c r="N215" s="5"/>
+      <c r="B215" s="3"/>
+      <c r="C215" s="3"/>
+      <c r="D215" s="3"/>
+      <c r="E215" s="3"/>
+      <c r="F215" s="3"/>
+      <c r="G215" s="3"/>
+      <c r="H215" s="3"/>
+      <c r="I215" s="3"/>
+      <c r="J215" s="3"/>
+      <c r="K215" s="3"/>
+      <c r="L215" s="3"/>
+      <c r="M215" s="3"/>
+      <c r="N215" s="3"/>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02</t>
+          <t xml:space="preserve">M26-01</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr">
@@ -14438,27 +14440,27 @@
       </c>
       <c r="C216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator sees every workspace</t>
+          <t xml:space="preserve">Operator console is off on a self-hosted instance</t>
         </is>
       </c>
       <c r="D216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator</t>
+          <t xml:space="preserve">Admin</t>
         </is>
       </c>
       <c r="E216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator (docs/install/cloud.md)</t>
+          <t xml:space="preserve">OPENOKR_CLOUD not set</t>
         </is>
       </c>
       <c r="F216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open /operator</t>
+          <t xml:space="preserve">1. Open /operator and /admin/plan</t>
         </is>
       </c>
       <c r="G216" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Table with Workspace, State, Plan, Region, Members, Goals, Storage</t>
+          <t xml:space="preserve">Both return Not Found</t>
         </is>
       </c>
       <c r="H216" s="1" t="inlineStr">
@@ -14466,11 +14468,7 @@
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I216" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Technical setup. Skip unless testing the managed cloud</t>
-        </is>
-      </c>
+      <c r="I216" s="1"/>
       <c r="J216" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -14484,7 +14482,7 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-03</t>
+          <t xml:space="preserve">M26-02</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
@@ -14494,29 +14492,27 @@
       </c>
       <c r="C217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suspend a workspace from the console</t>
+          <t xml:space="preserve">Operator sees every workspace</t>
         </is>
       </c>
       <c r="D217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator, then Sara</t>
+          <t xml:space="preserve">Operator</t>
         </is>
       </c>
       <c r="E217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02 done</t>
+          <t xml:space="preserve">OPENOKR_CLOUD=true and an operator granted with pnpm cloud:operator (docs/install/cloud.md)</t>
         </is>
       </c>
       <c r="F217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the workspace, choose "Suspended", write a reason, click "Apply to Northwind Labs"
-2. Sara tries to edit
-3. Return it to Active</t>
+          <t xml:space="preserve">1. Open /operator</t>
         </is>
       </c>
       <c r="G217" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sara can read only while suspended</t>
+          <t xml:space="preserve">Table with Workspace, State, Plan, Region, Members, Goals, Storage</t>
         </is>
       </c>
       <c r="H217" s="1" t="inlineStr">
@@ -14524,7 +14520,11 @@
           <t xml:space="preserve">Low</t>
         </is>
       </c>
-      <c r="I217" s="1"/>
+      <c r="I217" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technical setup. Skip unless testing the managed cloud</t>
+        </is>
+      </c>
       <c r="J217" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Not Run</t>
@@ -14538,7 +14538,7 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-04</t>
+          <t xml:space="preserve">M26-03</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
@@ -14548,12 +14548,12 @@
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support access needs the admin's approval</t>
+          <t xml:space="preserve">Suspend a workspace from the console</t>
         </is>
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator, then Admin</t>
+          <t xml:space="preserve">Operator, then Sara</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -14563,13 +14563,14 @@
       </c>
       <c r="F218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Operator writes "Why you need to be in there" and clicks "Ask to come in"
-2. Admin opens Admin, Support access, picks Read only for 1 hour, clicks "Let them in"</t>
+          <t xml:space="preserve">1. Open the workspace, choose "Suspended", write a reason, click "Apply to Northwind Labs"
+2. Sara tries to edit
+3. Return it to Active</t>
         </is>
       </c>
       <c r="G218" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The request waits under "Waiting for you". After approval the operator can read the workspace for one hour</t>
+          <t xml:space="preserve">Sara can read only while suspended</t>
         </is>
       </c>
       <c r="H218" s="1" t="inlineStr">
@@ -14591,7 +14592,7 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-05</t>
+          <t xml:space="preserve">M26-04</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
@@ -14601,12 +14602,12 @@
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instance banner</t>
+          <t xml:space="preserve">Support access needs the admin's approval</t>
         </is>
       </c>
       <c r="D219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator</t>
+          <t xml:space="preserve">Operator, then Admin</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -14616,14 +14617,13 @@
       </c>
       <c r="F219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. On /operator/instance, "Say something": message, Tone Warning, a stop time, "People can dismiss it"
-2. Click "Show this message"
-3. Sara opens the app and dismisses it</t>
+          <t xml:space="preserve">1. Operator writes "Why you need to be in there" and clicks "Ask to come in"
+2. Admin opens Admin, Support access, picks Read only for 1 hour, clicks "Let them in"</t>
         </is>
       </c>
       <c r="G219" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Every user sees the banner. Dismissing hides it for Sara</t>
+          <t xml:space="preserve">The request waits under "Waiting for you". After approval the operator can read the workspace for one hour</t>
         </is>
       </c>
       <c r="H219" s="1" t="inlineStr">
@@ -14645,7 +14645,7 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-06</t>
+          <t xml:space="preserve">M26-05</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
@@ -14655,7 +14655,7 @@
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operator sets a plan, and a downgrade below the headcount is refused</t>
+          <t xml:space="preserve">Instance banner</t>
         </is>
       </c>
       <c r="D220" s="1" t="inlineStr">
@@ -14665,18 +14665,19 @@
       </c>
       <c r="E220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-02 done, and cloud.plans holds a plan with fewer seats than Northwind Labs has people</t>
+          <t xml:space="preserve">M26-02 done</t>
         </is>
       </c>
       <c r="F220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open the workspace, under "Plan and seats" pick the small plan, write a reason, click "Set the plan for Northwind Labs"
-2. Pick a larger plan, or type a seat count above the headcount, and apply again</t>
+          <t xml:space="preserve">1. On /operator/instance, "Say something": message, Tone Warning, a stop time, "People can dismiss it"
+2. Click "Show this message"
+3. Sara opens the app and dismisses it</t>
         </is>
       </c>
       <c r="G220" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The first is refused naming the seats the plan has and the seats in use. The second is applied and the Tenant facts show the new plan and seats</t>
+          <t xml:space="preserve">Every user sees the banner. Dismissing hides it for Sara</t>
         </is>
       </c>
       <c r="H220" s="1" t="inlineStr">
@@ -14698,7 +14699,7 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-07</t>
+          <t xml:space="preserve">M26-06</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
@@ -14708,29 +14709,28 @@
       </c>
       <c r="C221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Administrator sees who holds a seat and changes plan</t>
+          <t xml:space="preserve">Operator sets a plan, and a downgrade below the headcount is refused</t>
         </is>
       </c>
       <c r="D221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Admin</t>
+          <t xml:space="preserve">Operator</t>
         </is>
       </c>
       <c r="E221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">M26-07 done</t>
+          <t xml:space="preserve">M26-02 done, and cloud.plans holds a plan with fewer seats than Northwind Labs has people</t>
         </is>
       </c>
       <c r="F221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Open Admin, Plan and seats
-2. Read the list under "Who holds a seat"
-3. Under "Move to" pick another plan and click "Change plan"</t>
+          <t xml:space="preserve">1. Open the workspace, under "Plan and seats" pick the small plan, write a reason, click "Set the plan for Northwind Labs"
+2. Pick a larger plan, or type a seat count above the headcount, and apply again</t>
         </is>
       </c>
       <c r="G221" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">The list names every person and invitation the seat count counts, and no guest or agent. The plan changes, or is refused naming both numbers when it has too few seats</t>
+          <t xml:space="preserve">The first is refused naming the seats the plan has and the seats in use. The second is applied and the Tenant facts show the new plan and seats</t>
         </is>
       </c>
       <c r="H221" s="1" t="inlineStr">
@@ -14749,9 +14749,63 @@
       <c r="M221" s="5"/>
       <c r="N221" s="5"/>
     </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07</t>
+        </is>
+      </c>
+      <c r="B222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26 Cloud operator console</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Administrator sees who holds a seat and changes plan</t>
+        </is>
+      </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admin</t>
+        </is>
+      </c>
+      <c r="E222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">M26-07 done</t>
+        </is>
+      </c>
+      <c r="F222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1. Open Admin, Plan and seats
+2. Read the list under "Who holds a seat"
+3. Under "Move to" pick another plan and click "Change plan"</t>
+        </is>
+      </c>
+      <c r="G222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The list names every person and invitation the seat count counts, and no guest or agent. The plan changes, or is refused naming both numbers when it has too few seats</t>
+        </is>
+      </c>
+      <c r="H222" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Low</t>
+        </is>
+      </c>
+      <c r="I222" s="1"/>
+      <c r="J222" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Not Run</t>
+        </is>
+      </c>
+      <c r="K222" s="5"/>
+      <c r="L222" s="5"/>
+      <c r="M222" s="5"/>
+      <c r="N222" s="5"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N221"/>
-  <conditionalFormatting sqref="J2:J221">
+  <autoFilter ref="A1:N222"/>
+  <conditionalFormatting sqref="J2:J222">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Pass">
       <formula>NOT(ISERROR(SEARCH("Pass",J2)))</formula>
     </cfRule>
@@ -14769,10 +14823,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J221">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J222">
       <formula1>"Not Run,Pass,Fail,Error,Blocked,N/A"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H221">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H222">
       <formula1>"High,Medium,Low"</formula1>
     </dataValidation>
   </dataValidations>
